--- a/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0027.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0027.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Các Resonators trong đội mất 1% HP mỗi 2 giây. &lt;color=#ffb04a&gt;Resonance Skill DMG&lt;/color&gt; được khuếch đại thêm 10%.</t>
+          <t>Các Resonator trong đội mất 1% HP mỗi 2 giây. &lt;color=#ffb04a&gt;Sát Thương Resonance Skill&lt;/color&gt; được khuếch đại thêm 10%.</t>
         </is>
       </c>
     </row>
@@ -640,8 +640,8 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Glacio DMG và Spectro tăng 10%.
-Khi bị kỹ năng của Resonator đánh trúng, kẻ địch trong trạng thái &lt;color=#ffb04a&gt;Mistune&lt;/color&gt; sẽ chịu một lần &lt;color=#ffb04a&gt;Tune Break DMG&lt;/color&gt; và thoát khỏi trạng thái &lt;color=#ffb04a&gt;Mistune&lt;/color&gt;.</t>
+          <t>DMG Glacio và Spectro tăng 10%.
+Khi bị kỹ năng của Resonator đánh trúng, kẻ địch trong trạng thái &lt;color=#ffb04a&gt;Mistune&lt;/color&gt; sẽ chịu một lần &lt;color=#ffb04a&gt;DMG Tune Break&lt;/color&gt; và thoát khỏi trạng thái &lt;color=#ffb04a&gt;Mistune&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       <c r="M4" t="inlineStr">
         <is>
           <t>Tăng 10% Sát Thương Hợp Thể và Điện.
-Khi bị kỹ năng của Resonator đánh trúng, kẻ địch trong trạng thái &lt;color=#ffb04a&gt;Mistune&lt;/color&gt; sẽ chịu một lần &lt;color=#ffb04a&gt;Tune Break DMG&lt;/color&gt; rồi thoát khỏi trạng thái &lt;color=#ffb04a&gt;Mistune&lt;/color&gt;.</t>
+Khi bị kỹ năng của Resonator đánh trúng, kẻ địch trong trạng thái &lt;color=#ffb04a&gt;Mistune&lt;/color&gt; sẽ chịu một lần &lt;color=#ffb04a&gt;Sát Thương Vỡ Nhịp&lt;/color&gt; rồi thoát khỏi trạng thái &lt;color=#ffb04a&gt;Mistune&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -774,8 +774,8 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Aero DMG và Havoc tăng 10%.
-Khi bị kỹ năng của Resonator đánh trúng, kẻ địch trong trạng thái &lt;color=#ffb04a&gt;Mistune&lt;/color&gt; sẽ chịu một lần &lt;color=#ffb04a&gt;Tune Break DMG&lt;/color&gt; và thoát khỏi trạng thái &lt;color=#ffb04a&gt;Mistune&lt;/color&gt;.</t>
+          <t>DMG Aero và Havoc tăng 10%.
+Khi bị kỹ năng của Resonator đánh trúng, kẻ địch trong trạng thái &lt;color=#ffb04a&gt;Mistune&lt;/color&gt; sẽ chịu một lần &lt;color=#ffb04a&gt;DMG Phá Tune&lt;/color&gt; và thoát khỏi trạng thái &lt;color=#ffb04a&gt;Mistune&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       <c r="M6" t="inlineStr">
         <is>
           <t>Mỗi lần gây Sát Thương Hợp Đồng, Sát Thương Hợp Đồng sẽ được Khuếch Đại thêm 4% trong 15 giây, tối đa 5 lần cộng dồn.
-Khi bị kỹ năng của Resonator đánh trúng, kẻ địch trong trạng thái &lt;color=#ffb04a&gt;Mistune&lt;/color&gt; sẽ chịu một lần &lt;color=#ffb04a&gt;Tune Break DMG&lt;/color&gt; rồi thoát khỏi trạng thái &lt;color=#ffb04a&gt;Mistune&lt;/color&gt;.</t>
+Khi bị kỹ năng của Resonator đánh trúng, kẻ địch trong trạng thái &lt;color=#ffb04a&gt;Mistune&lt;/color&gt; sẽ chịu một lần &lt;color=#ffb04a&gt;Sát Thương Phá Nhịp&lt;/color&gt; rồi thoát khỏi trạng thái &lt;color=#ffb04a&gt;Mistune&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -908,8 +908,8 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Mỗi lần gây sát thương bằng Đòn Đánh Basic, sát thương toàn thuộc tính sẽ tăng 2% trong 15 giây, tối đa cộng dồn 10 lần.
-Khi bị kỹ năng của Resonator tấn công, kẻ địch trong trạng thái &lt;color=#ffb04a&gt;Mistune&lt;/color&gt; sẽ chịu một lần &lt;color=#ffb04a&gt;Tune Break DMG&lt;/color&gt; và thoát khỏi trạng thái &lt;color=#ffb04a&gt;Mistune&lt;/color&gt;.</t>
+          <t>Mỗi lần gây DMG bằng Đòn Đánh Cơ Bản, DMG toàn thuộc tính sẽ tăng 2% trong 15 giây, tối đa cộng dồn 10 lần.
+Khi bị kỹ năng của Resonator tấn công, kẻ địch trong trạng thái &lt;color=#ffb04a&gt;Mistune&lt;/color&gt; sẽ chịu một lần &lt;color=#ffb04a&gt;Sát Thương Phá Nhịp&lt;/color&gt; và thoát khỏi trạng thái &lt;color=#ffb04a&gt;Mistune&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -975,8 +975,8 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Sát thương Heavy Attack được Khuếch đại thêm 10%.
-Khi bị kỹ năng của Resonator đánh trúng, kẻ địch trong trạng thái &lt;color=#ffb04a&gt;Mistune&lt;/color&gt; sẽ chịu một lần &lt;color=#ffb04a&gt;Tune Break DMG&lt;/color&gt; và thoát khỏi trạng thái &lt;color=#ffb04a&gt;Mistune&lt;/color&gt;.</t>
+          <t>DMG Heavy Attack được Khuếch đại thêm 10%.
+Khi bị kỹ năng của Resonator đánh trúng, kẻ địch trong trạng thái &lt;color=#ffb04a&gt;Mistune&lt;/color&gt; sẽ chịu một lần &lt;color=#ffb04a&gt;DMG Phá Tune&lt;/color&gt; và thoát khỏi trạng thái &lt;color=#ffb04a&gt;Mistune&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Mỗi khi Resonators trong đội gây &lt;color=#ffb04a&gt;Basic Attack DMG&lt;/color&gt; 6 lần, một vụ nổ Lửa sẽ được kích hoạt, gây 600% Fusion DMG lên kẻ địch xung quanh.</t>
+          <t>Mỗi khi các Resonator trong đội gây &lt;color=#ffb04a&gt;DMG Basic Attack&lt;/color&gt; 6 lần, một vụ nổ Lửa sẽ được kích hoạt, gây 600% DMG Fusion lên kẻ địch xung quanh.</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Tốc độ &lt;color=#ffb04a&gt;Energy Regen&lt;/color&gt; tăng 50%, và &lt;color=#ffb04a&gt;Resonance Liberation DMG&lt;/color&gt; được Khuếch Đại thêm 10%.</t>
+          <t>Tốc độ &lt;color=#ffb04a&gt;Hồi Phục Năng Lượng&lt;/color&gt; tăng 50%, và &lt;color=#ffb04a&gt;Sát Thương Giải Cứu Cộng Hưởng&lt;/color&gt; được Khuếch Đại thêm 10%.</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Mỗi khi Resonators trong đội đạt đủ số lần &lt;color=#ffb04a&gt;Coordinated Attack&lt;/color&gt;, một trận Mưa Lửa sẽ được thi triển, gây 600% Fusion DMG lên kẻ địch xung quanh.</t>
+          <t>Mỗi khi Resonator trong đội đạt đủ số lần &lt;color=#ffb04a&gt;Tấn Công Phối Hợp&lt;/color&gt;, một trận Mưa Lửa sẽ được thi triển, gây 600% Sát Thương Fusion lên kẻ địch xung quanh.</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1303,7 @@
       <c r="M13" t="inlineStr">
         <is>
           <t>Sát thương nhận vào của kẻ địch tăng 50%.
-Tất cả Token đều có &lt;color=#ffb04a&gt;unlimited uses&lt;/color&gt; khi ở trong Infinite Torrents.</t>
+Tất cả Token đều có &lt;color=#ffb04a&gt;số lần sử dụng không giới hạn&lt;/color&gt; khi ở trong Infinite Torrents.</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Khi thực hiện &lt;color=#ffb04a&gt;Mid-air&lt;/color&gt;, Resonator gây 600% Fusion DMG lên kẻ địch xung quanh. 
+          <t>Khi thực hiện &lt;color=#ffb04a&gt;Tấn Công Giữa Không Trung&lt;/color&gt;, Resonator gây 600% Sát Thương Fusion lên kẻ địch xung quanh. 
 Hồi chiêu: 3 giây</t>
         </is>
       </c>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng &lt;color=#ffb04a&gt;Echo Skill&lt;/color&gt;, Crit. DMG tăng thêm 40% trong 15 giây.</t>
+          <t>Sau khi sử dụng &lt;color=#ffb04a&gt;Kỹ Năng Echo&lt;/color&gt;, Crit. DMG tăng thêm 40% trong 15 giây.</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Khi sử dụng &lt;color=#ffb04a&gt;Echo Skill&lt;/color&gt;, Resonator gây 1000% Electro DMG lên kẻ địch xung quanh.</t>
+          <t>Khi sử dụng &lt;color=#ffb04a&gt;Kỹ Năng Echo&lt;/color&gt;, Resonator gây 1000% Sát Thương Electro lên kẻ địch xung quanh.</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       <c r="M17" t="inlineStr">
         <is>
           <t>Crit. DMG mà kẻ địch phải chịu tăng 60%.
-Tất cả Token có &lt;color=#ffb04a&gt;unlimited uses&lt;/color&gt; khi ở trong Infinite Torrents.</t>
+Tất cả Token có &lt;color=#ffb04a&gt;số lần sử dụng không giới hạn&lt;/color&gt; khi ở trong Infinite Torrents.</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Kích hoạt trạng thái Sóng Cháy, &lt;color=#fee388&gt;Crit. Rate is increased to 100%&lt;/color&gt;.</t>
+          <t>Kích hoạt trạng thái Sóng Cháy, &lt;color=#fee388&gt;Crit. Rate tăng lên 100%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Kích hoạt trạng thái Sóng Cháy, &lt;color=#fee388&gt;Resonance Energy is restored to 100%&lt;/color&gt;.</t>
+          <t>Kích hoạt trạng thái Sóng Cháy, &lt;color=#fee388&gt;Resonance Energy được hồi đầy 100%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -1845,22 +1845,22 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>[Whimpering Wastes]
-Tại Whimpering Wastes, kỹ năng của ngươi sẽ được thử thách qua nhiều giai đoạn. Hoàn thành mỗi giai đoạn sẽ mang lại điểm thưởng. Dồn điểm để đổi lấy phần thưởng tương ứng.
+          <t>[Vùng Đất Than Thở]
+Tại Vùng Đất Than Thở, kỹ năng của ngươi sẽ được thử thách qua nhiều giai đoạn. Hoàn thành mỗi giai đoạn sẽ mang lại điểm thưởng. Dồn điểm để đổi lấy phần thưởng tương ứng.
 [Vùng Nước]
-Whimpering Wastes gồm ba khu vực: &lt;color=#c19f51&gt;[Forbidden Waters], [Respawning Waters: Chasm], [Respawning Waters: Torrents]&lt;/color&gt;. Hoàn thành tất cả thử thách trong khu vực trước để mở khóa khu vực tiếp theo.
+Vùng Đất Than Thở gồm ba khu vực: &lt;color=#c19f51&gt;[Vùng Nước Cấm], [Vùng Nước Tái Sinh: Vực Sâu], [Vùng Nước Tái Sinh: Dòng Xiết]&lt;/color&gt;. Hoàn thành tất cả thử thách trong khu vực trước để mở khóa khu vực tiếp theo.
 [Ấn Tín]
-Mỗi đội tại Whimpering Wastes phải trang bị Ấn Tín để nhận hiệu ứng đặc biệt trong chiến đấu. Hoàn thành một thử thách sẽ tiêu hao một lần sử dụng Ấn Tín. Số lần sử dụng có thể phục hồi bằng cách [Đặt Lại] thử thách.
+Mỗi đội tại Vùng Đất Than Thở phải trang bị Ấn Tín để nhận hiệu ứng đặc biệt trong chiến đấu. Hoàn thành một thử thách sẽ tiêu hao một lần sử dụng Ấn Tín. Số lần sử dụng có thể phục hồi bằng cách [Đặt Lại] thử thách.
 [Hiệu Ứng Khu Vực]
-Whimpering Wastes có những hiệu ứng môi trường và kẻ địch đặc biệt.
+Vùng Đất Than Thở có những hiệu ứng môi trường và kẻ địch đặc biệt.
 [Chu Kỳ Tái Sinh]
-Rewards của [Forbidden Waters] chỉ có thể nhận một lần. Tuy nhiên, &lt;color=#c19f51&gt;the challenges and rewards of [Respawning Waters: Chasm] and [Respawning Waters: Torrents] will reset periodically&lt;/color&gt; với nội dung và hiệu ứng khác nhau. Khi chu kỳ làm mới, tiến độ của ngươi sẽ bị xóa, và ngươi có thể thử thách lại để nhận thưởng.
+Phần thưởng của [Vùng Nước Cấm] chỉ có thể nhận một lần. Tuy nhiên, &lt;color=#c19f51&gt;các thử thách và phần thưởng của [Vùng Nước Tái Sinh: Vực Sâu] và [Vùng Nước Tái Sinh: Dòng Xiết] sẽ được làm mới định kỳ&lt;/color&gt; với nội dung và hiệu ứng khác nhau. Khi chu kỳ làm mới, tiến độ của ngươi sẽ bị xóa, và ngươi có thể thử thách lại để nhận thưởng.
 [Đồng Bộ Hóa Kỷ Lục]
 Trong chu kỳ trước, nếu ngươi:
-- Đạt kết quả không thấp hơn S ở Stage 7 và Giai Đoạn 8 của [Vùng Nước Tái Sinh: Vực Sâu].
+- Đạt kết quả không thấp hơn S ở Giai Đoạn 7 và Giai Đoạn 8 của [Vùng Nước Tái Sinh: Vực Sâu].
 - Đạt tổng điểm không dưới 15.000 ở [Vùng Nước Tái Sinh: Vực Sâu].
 - Đạt không dưới 4.500 điểm ở [Vùng Nước Tái Sinh: Dòng Xiết].
-Đội hình và Ấn Tín của ngươi từ chu kỳ trước sẽ được sử dụng để tự động vượt qua Stage 7 và Giai Đoạn 8 trong chu kỳ hiện tại của [Vùng Nước Tái Sinh: Vực Sâu].
+Đội hình và Ấn Tín của ngươi từ chu kỳ trước sẽ được sử dụng để tự động vượt qua Giai Đoạn 7 và Giai Đoạn 8 trong chu kỳ hiện tại của [Vùng Nước Tái Sinh: Vực Sâu].
 Nếu Ấn Tín sử dụng trong chu kỳ trước đã hết hạn, hệ thống sẽ thay thế bằng Ấn Tín không giới hạn sử dụng có độ hiếm cao nhất mà ngươi đã mở khóa.
 [Lửa Đỏ]
 Ngươi có thể tích lũy Lửa Đỏ trong chiến đấu tại [Vùng Nước Tái Sinh: Vực Sâu] và [Vùng Nước Tái Sinh: Dòng Xiết]. Khi thanh Lửa Đỏ đầy, ngươi sẽ bước vào trạng thái Sóng Lửa Mạnh mẽ.</t>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Buff List (Thay đổi theo Cấp Combat của bạn)</t>
+          <t>Danh sách Hiệu ứng (Thay đổi theo Cấp Chiến Đấu của bạn)</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Tracking mục tiêu. Hãy đi theo chỉ dẫn.</t>
+          <t>Đang theo dõi mục tiêu. Hãy đi theo chỉ dẫn.</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Kháng Aero</t>
+          <t>Kháng Gió</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Fusion RES</t>
+          <t>Kháng Hợp Thể</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Increase Aero RES 20%</t>
+          <t>Tăng Kháng Aero 20%</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Increase Electro RES thêm 20%.</t>
+          <t>Tăng Kháng Electro thêm 20%.</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Increase Kháng Hệ Fusion 20%</t>
+          <t>Tăng Kháng Hệ Fusion 20%</t>
         </is>
       </c>
     </row>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Increase Kháng Hệ Glacio 20%</t>
+          <t>Tăng Kháng Hệ Glacio 20%</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Increase Kháng Hệ Havoc 20%</t>
+          <t>Tăng Kháng Hệ Havoc 20%</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Increase Spectro RES thêm 20%.</t>
+          <t>Tăng Kháng Spectro thêm 20%.</t>
         </is>
       </c>
     </row>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Không có Resonance Beacon gần đây để Fast Travel</t>
+          <t>Không thể Dịch Chuyển Nhanh đến Điểm Cộng Hưởng gần đây</t>
         </is>
       </c>
     </row>
@@ -3034,8 +3034,8 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Những câu chuyện thiêng từ kinh thư vỡ nát. Add một &lt;color=#e7a60b&gt;Request slot&lt;/color&gt; và giảm chi phí làm mới Requests.
-&lt;color=#929292&gt;These stories of humanity uniting against the sea and the abyss seem to be the origins of some legends recorded in the Order's Codex.&lt;/color&gt;</t>
+          <t>Những câu chuyện thiêng từ kinh thư vỡ nát. Thêm một &lt;color=#e7a60b&gt;ô Yêu Cầu&lt;/color&gt; và giảm chi phí làm mới Yêu Cầu.
+&lt;color=#929292&gt;Những câu chuyện về nhân loại đoàn kết chống lại biển cả và vực thẳm này dường như là nguồn gốc của một số truyền thuyết được ghi lại trong Bộ Kinh của Giáo Đoàn.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -3101,8 +3101,8 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Những câu chuyện thiêng từ kinh thư vỡ nát. Add một &lt;color=#e7a60b&gt;Request slot&lt;/color&gt; và giảm thêm chi phí làm mới Requests.
-&lt;color=#929292&gt;These stories of humanity uniting against the sea and the abyss seem to be the origins of some legends recorded in the Order's Codex.&lt;/color&gt;</t>
+          <t>Những câu chuyện thiêng từ kinh thư vỡ nát. Thêm một &lt;color=#e7a60b&gt;ô Yêu Cầu&lt;/color&gt; và giảm thêm chi phí làm mới Yêu Cầu.
+&lt;color=#929292&gt;Những câu chuyện về nhân loại đoàn kết chống lại biển cả và vực thẳm này dường như là nguồn gốc của một số truyền thuyết được ghi lại trong Bộ Kinh của Giáo Đoàn.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -3168,8 +3168,8 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Những câu chuyện thiêng từ kinh thư vỡ nát. Add một &lt;color=#e7a60b&gt;Request slot&lt;/color&gt; và giảm thêm chi phí làm mới Requests.
-&lt;color=#929292&gt;These stories of humanity uniting against the sea and the abyss seem to be the origins of some legends recorded in the Order's Codex.&lt;/color&gt;</t>
+          <t>Những câu chuyện thiêng từ kinh thư vỡ nát. Thêm một &lt;color=#e7a60b&gt;ô Yêu Cầu&lt;/color&gt; và giảm thêm chi phí làm mới Yêu Cầu.
+&lt;color=#929292&gt;Những câu chuyện về nhân loại đoàn kết chống lại biển cả và vực thẳm này dường như là nguồn gốc của một số truyền thuyết được ghi lại trong Bộ Kinh của Giáo Đoàn.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -3235,8 +3235,8 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Nghiên cứu Hướng dẫn Fishing Rinascita sẽ giúp cậu trở thành một ngư dân lão luyện, kiếm được nhiều &lt;color=#e7a60b&gt;Fishery Coins&lt;/color&gt; hơn từ các &lt;color=#e7a60b&gt;Requests&lt;/color&gt;.
-&lt;color=#929292&gt;True fishing skill is the backbone of any fisher's reputation.&lt;/color&gt;</t>
+          <t>Nghiên cứu Hướng dẫn Câu cá Rinascita sẽ giúp cậu trở thành một ngư dân lão luyện, kiếm được nhiều &lt;color=#e7a60b&gt;Đồng Tiền Câu Cá&lt;/color&gt; hơn từ các &lt;color=#e7a60b&gt;Yêu Cầu&lt;/color&gt;.
+&lt;color=#929292&gt;Kỹ năng câu cá chính là nền tảng danh tiếng của bất kỳ ngư dân nào.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -3302,8 +3302,8 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Những diễn giải ban đầu về kinh thư vỡ vụn tìm thấy ở Quần đảo Riccioli. Increase cơ hội bắt được &lt;color=#e7a60b&gt;Mutants&lt;/color&gt;.
-&lt;color=#929292&gt;The locations mentioned casually in the scripture are said to yield more valuable sea life.&lt;/color&gt;</t>
+          <t>Những diễn giải ban đầu về kinh thư vỡ vụn tìm thấy ở Quần đảo Riccioli. Tăng cơ hội bắt được &lt;color=#e7a60b&gt;Đột Biến Thể&lt;/color&gt;.
+&lt;color=#929292&gt;Những địa điểm được nhắc đến thoáng qua trong kinh thư được cho là nơi cho ra nhiều sinh vật biển quý hiếm.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -3369,8 +3369,8 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Những diễn giải sâu hơn về bộ kinh thánh rời rạc tìm thấy ở Quần đảo Riccioli. Increase cơ hội bắt được &lt;color=#e7a60b&gt;Mutants&lt;/color&gt;
-&lt;color=#929292&gt;The scripture mentions a noble being that grants catches to the islanders, though its definition of "catches" seems to differ from that of humans.&lt;/color&gt;</t>
+          <t>Những diễn giải sâu hơn về bộ kinh thánh rời rạc tìm thấy ở Quần đảo Riccioli. Tăng cơ hội bắt được &lt;color=#e7a60b&gt;Đột Biến Thể&lt;/color&gt;
+&lt;color=#929292&gt;Bộ kinh nhắc đến một sinh vật cao quý ban tặng "mẻ săn" cho cư dân đảo, dù định nghĩa "mẻ săn" của nó có vẻ khác với con người.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -3436,8 +3436,8 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Nghiên cứu sâu sắc về kinh thư vỡ nát. Increase cơ hội bắt được &lt;color=#e7a60b&gt;Mutants&lt;/color&gt;.
-&lt;color=#929292&gt;"...Both fish and fishers serve as offerings. That which gazeth upon us is not the abyss, but countless eyes."&lt;/color&gt;</t>
+          <t>Nghiên cứu sâu sắc về kinh thư vỡ nát. Tăng cơ hội bắt được &lt;color=#e7a60b&gt;Biến Dị Thể&lt;/color&gt;.
+&lt;color=#929292&gt;"...Cả ngư dân lẫn cá đều là vật hiến tế. Cái nhìn chúng ta không phải vực thẳm, mà là vô số con mắt."&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -3503,8 +3503,8 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Đèn tàu cải tiến giúp giảm Cooldown chiêu của &lt;color=#e7a60b&gt;Nautical Light&lt;/color&gt;.
-&lt;color=#929292&gt;Dim as the light may be, it's enough to pierce through the mist and darkness.&lt;/color&gt;</t>
+          <t>Đèn tàu cải tiến giúp giảm thời gian hồi chiêu của &lt;color=#e7a60b&gt;Nautical Light&lt;/color&gt;.
+&lt;color=#929292&gt;Dù ánh sáng có mờ nhạt, nhưng vẫn đủ để xuyên qua màn sương và bóng tối.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -3570,8 +3570,8 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Đèn tàu cải tiến giúp giảm Cooldown chiêu của &lt;color=#e7a60b&gt;Nautical Light&lt;/color&gt;.
-&lt;color=#929292&gt;Cảm ơn to its upgraded power unit, it's now more efficient and durable.&lt;/color&gt;</t>
+          <t>Đèn tàu cải tiến giúp giảm thời gian hồi chiêu của &lt;color=#e7a60b&gt;Nautical Light&lt;/color&gt;.
+&lt;color=#929292&gt;Nhờ bộ nguồn được nâng cấp, đèn giờ đây hoạt động hiệu quả và bền bỉ hơn.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -3637,8 +3637,8 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Đèn tàu cải tiến giúp giảm Cooldown chiêu của &lt;color=#e7a60b&gt;Nautical Light&lt;/color&gt;.
-&lt;color=#929292&gt;Its newly added capacitor ensures both stable power and flexible usage.&lt;/color&gt;</t>
+          <t>Đèn tàu cải tiến giúp giảm thời gian hồi chiêu của &lt;color=#e7a60b&gt;Nautical Light&lt;/color&gt;.
+&lt;color=#929292&gt;Bộ tụ điện mới bổ sung đảm bảo nguồn điện ổn định và linh hoạt.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -3704,8 +3704,8 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Huấn luyện đặc biệt dành cho Gondola. Huấn luyện Rachel để giảm Cooldown chiêu &lt;color=#e7a60b&gt;Acceleration&lt;/color&gt;.
-&lt;color=#929292&gt;Just like humans, Gondolas can grow stronger with regular training.&lt;/color&gt;</t>
+          <t>Huấn luyện đặc biệt dành cho Gondola. Huấn luyện Rachel để giảm thời gian hồi chiêu &lt;color=#e7a60b&gt;Tăng Tốc&lt;/color&gt;.
+&lt;color=#929292&gt;Giống như con người, Gondola cũng có thể trở nên mạnh mẽ hơn qua luyện tập thường xuyên.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -3771,8 +3771,8 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Huấn luyện đặc biệt dành cho Gondola. Huấn luyện Rachel để giảm thêm Cooldown chiêu &lt;color=#e7a60b&gt;Acceleration&lt;/color&gt;.
-&lt;color=#929292&gt;Just like humans, Gondolas can grow stronger with regular training.&lt;/color&gt;</t>
+          <t>Huấn luyện đặc biệt dành cho Gondola. Huấn luyện Rachel để giảm thêm thời gian hồi chiêu &lt;color=#e7a60b&gt;Tăng Tốc&lt;/color&gt;.
+&lt;color=#929292&gt;Giống như con người, Gondola cũng có thể trở nên mạnh mẽ hơn qua luyện tập thường xuyên.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -3838,8 +3838,8 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Huấn luyện đặc biệt dành cho Gondola. Huấn luyện Rachel để giảm thêm Cooldown chiêu &lt;color=#e7a60b&gt;Acceleration&lt;/color&gt;.
-&lt;color=#929292&gt;Just like humans, Gondolas can grow stronger with regular training.&lt;/color&gt;</t>
+          <t>Huấn luyện đặc biệt dành cho Gondola. Huấn luyện Rachel để giảm thêm thời gian hồi chiêu &lt;color=#e7a60b&gt;Tăng Tốc&lt;/color&gt;.
+&lt;color=#929292&gt;Giống như con người, Gondola cũng có thể trở nên mạnh mẽ hơn qua luyện tập thường xuyên.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Kỹ năng đang trong Cooldown</t>
+          <t>Kỹ năng đang hồi</t>
         </is>
       </c>
     </row>
@@ -3973,11 +3973,11 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Resonators Hỗ Trợ Giấc Mơ Hiện Tại: &lt;color=#ffd12f&gt;Phoebe, Jinhsi, Shorekeeper, and Verina&lt;/color&gt;. Hãy sử dụng ít nhất một Resonators Hỗ Trợ Giấc Mơ để &lt;color=#ffd12f&gt;gain a 150% Point Bonus!&lt;/color&gt;
+          <t>Resonator Hỗ Trợ Giấc Mơ Hiện Tại: &lt;color=#ffd12f&gt;Phoebe, Jinhsi, Shorekeeper và Verina&lt;/color&gt;. Hãy sử dụng ít nhất một Resonator Hỗ Trợ Giấc Mơ để &lt;color=#ffd12f&gt;nhận thưởng điểm gấp 150%!&lt;/color&gt;
 Hiệu ứng Hỗ Trợ Giấc Mơ Hiện Tại:
-- Tất cả Resonators trong đội &lt;color=#ffd12f&gt;gain 30% Spectro DMG Bonus.&lt;/color&gt;
-- Đánh trúng mục tiêu bằng Basic Attack sẽ nhận được 20 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần. &lt;color=#ffd12f&gt;Casting Resonance Skill grants 50 Dreamscape Energy, and healing a Resonator with Resonance Skill grants another 50 Dreamscape Energy. This effect can be triggered once every 10s. Damaging a target affected by Spectro Frazzle grants 30 Dreamscape Energy. This effect can be triggered once every second.&lt;/color&gt;
-- Khi Năng Lượng Giấc Mơ đạt 500, bạn sẽ bước vào trạng thái Lucid Dream. Trong trạng thái này, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonators trong đội sẽ tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Một số Ảo Ảnh sẽ được tăng cường trong trạng thái này. Lucid Dream kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.</t>
+- Tất cả Resonator trong đội &lt;color=#ffd12f&gt;nhận thêm 30% Sát Thương Spectro.&lt;/color&gt;
+- Đánh trúng mục tiêu bằng Đòn Cơ Bản sẽ nhận được 20 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần. &lt;color=#ffd12f&gt;Sử dụng Resonance Skill sẽ nhận được 50 Năng Lượng Giấc Mơ, và hồi máu cho Resonator bằng Resonance Skill sẽ nhận thêm 50 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi 10 giây một lần. Gây DMG lên mục tiêu bị ảnh hưởng bởi Spectro Frazzle sẽ nhận được 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.&lt;/color&gt;
+- Khi Năng Lượng Giấc Mơ đạt 500, bạn sẽ bước vào trạng thái Giấc Mơ Sáng Suốt. Trong trạng thái này, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonator trong đội sẽ tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Một số Ảo Ảnh sẽ được tăng cường trong trạng thái này. Giấc Mơ Sáng Suốt kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.</t>
         </is>
       </c>
     </row>
@@ -4046,11 +4046,11 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Resonators Hỗ Trợ Giấc Mơ Hiện Tại: &lt;color=#ffd12f&gt;Carlotta, Zhezhi, Lingyang, Sanhua, and Youhu&lt;/color&gt;. Hãy sử dụng ít nhất một Resonators Hỗ Trợ Giấc Mơ để &lt;color=#ffd12f&gt;gain a 150% Point Bonus!&lt;/color&gt;
+          <t>Resonator Hỗ Trợ Giấc Mơ Hiện Tại: &lt;color=#ffd12f&gt;Carlotta, Zhezhi, Lingyang, Sanhua và Youhu&lt;/color&gt;. Hãy sử dụng ít nhất một Resonator Hỗ Trợ Giấc Mơ để &lt;color=#ffd12f&gt;nhận thưởng 150% Điểm!&lt;/color&gt;
 Hiệu ứng Hỗ Trợ Giấc Mơ Hiện Tại:
-- Tất cả Resonators trong đội &lt;color=#ffd12f&gt;gain 30% Glacio DMG Bonus.&lt;/color&gt;
-- Tấn công mục tiêu bằng Basic Attack sẽ nhận được 20 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần. &lt;color=#ffd12f&gt;Casting Resonance Liberation grants 100 Dreamscape Energy. This effect can be triggered once every 10s. Dealing Glacio DMG grants 30 Dreamscape Energy. This effect can be triggered once every second.&lt;/color&gt;
-- Khi Năng Lượng Giấc Mơ đạt 500, sẽ bước vào trạng thái Lucid Dream. Trong trạng thái này, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Một số Ẩn Dụ sẽ được tăng cường trong trạng thái này. Lucid Dream kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.</t>
+- Tất cả Resonator trong đội &lt;color=#ffd12f&gt;nhận thêm 30% Sát Thương Glacio.&lt;/color&gt;
+- Tấn công mục tiêu bằng Đòn Cơ Bản sẽ nhận được 20 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần. &lt;color=#ffd12f&gt;Sử dụng Resonance Liberation sẽ nhận được 100 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi 10 giây một lần. Gây Sát Thương Glacio sẽ nhận được 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.&lt;/color&gt;
+- Khi Năng Lượng Giấc Mơ đạt 500, sẽ bước vào trạng thái Giấc Mơ Sáng Suốt. Trong trạng thái này, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Một số Ẩn Dụ sẽ được tăng cường trong trạng thái này. Giấc Mơ Sáng Suốt kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.</t>
         </is>
       </c>
     </row>
@@ -4120,12 +4120,12 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Resonators Hỗ Trợ Giấc Mơ Hiện Tại: &lt;color=#ffd12f&gt;Camellya, Roccia, Danjin, and Baizhi&lt;/color&gt;. Hãy sử dụng ít nhất một Resonators Hỗ Trợ Giấc Mơ để &lt;color=#ffd12f&gt;gain a 150% Point Bonus!&lt;/color&gt;
+          <t>Resonator Hỗ Trợ Giấc Mơ Hiện Tại: &lt;color=#ffd12f&gt;Camellya, Roccia, Danjin và Baizhi&lt;/color&gt;. Hãy sử dụng ít nhất một Resonator Hỗ Trợ Giấc Mơ để &lt;color=#ffd12f&gt;nhận thưởng 150% Điểm!&lt;/color&gt;
 Hiệu ứng Hỗ Trợ Giấc Mơ Hiện Tại:
-- Tất cả Resonators trong đội &lt;color=#ffd12f&gt;gain 30% Havoc DMG Bonus.&lt;/color&gt;
-- Tấn công mục tiêu bằng Basic Attack sẽ nhận được 20 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
-- &lt;color=#ffd12f&gt;Casting Heavy Attack grants 10 Dreamscape Energy. This effect can be triggered once every 10s. Dealing Havoc DMG grants 30 Dreamscape Energy. This effect can be triggered once every second.&lt;/color&gt;
-- Khi Năng Lượng Giấc Mơ đạt 500, sẽ bước vào trạng thái Lucid Dream. Trong trạng thái này, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Một số Ẩn Dụ sẽ được tăng cường trong trạng thái này. Lucid Dream kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.</t>
+- Tất cả Resonator trong đội &lt;color=#ffd12f&gt;nhận thêm 30% Sát Thương Havoc.&lt;/color&gt;
+- Tấn công mục tiêu bằng Đòn Cơ Bản sẽ nhận được 20 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
+- &lt;color=#ffd12f&gt;Sử dụng Đòn Nặng sẽ nhận được 10 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi 10 giây một lần. Gây Sát Thương Havoc sẽ nhận được 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.&lt;/color&gt;
+- Khi Năng Lượng Giấc Mơ đạt 500, sẽ bước vào trạng thái Giấc Mơ Sáng Suốt. Trong trạng thái này, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Một số Ẩn Dụ sẽ được tăng cường trong trạng thái này. Giấc Mơ Sáng Suốt kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.</t>
         </is>
       </c>
     </row>
@@ -4194,11 +4194,11 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Resonators Current Dreamscape Aid: &lt;color=#ffd12f&gt;Brant, Changli, Encore, Chixia, and Mortefi&lt;/color&gt;. Sử dụng ít nhất một Resonators Hỗ Trợ Giấc Mộng để &lt;color=#ffd12f&gt;gain a 150% Point Bonus!&lt;/color&gt;
-Hiệu ứng Current Dreamscape Aid:
-- Tất cả Resonators trong đội &lt;color=#ffd12f&gt;gain 30% Fusion DMG Bonus.&lt;/color&gt;
-- Đánh trúng mục tiêu bằng Basic Attack sẽ nhận được 20 Năng Lượng Giấc Mộng. Hiệu ứng này có thể kích hoạt mỗi giây một lần. &lt;color=#ffd12f&gt;Casting Intro Skill grants 100 Dreamscape Energy. This effect can be triggered once every 10s. Dealing Fusion DMG grants 30 Dreamscape Energy. This effect can be triggered once every second.&lt;/color&gt;
-- Khi Năng Lượng Giấc Mộng đạt 500, sẽ bước vào trạng thái Lucid Dream. Trong trạng thái này, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Một số Ẩn Dụ sẽ được tăng cường trong trạng thái này. Lucid Dream kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mộng khi kết thúc.</t>
+          <t>Resonator Hỗ Trợ Giấc Mộng Hiện Tại: &lt;color=#ffd12f&gt;Brant, Changli, Encore, Chixia và Mortefi&lt;/color&gt;. Sử dụng ít nhất một Resonator Hỗ Trợ Giấc Mộng để &lt;color=#ffd12f&gt;nhận thêm 150% Điểm Thưởng!&lt;/color&gt;
+Hiệu ứng Hỗ Trợ Giấc Mộng Hiện Tại:
+- Tất cả Resonator trong đội &lt;color=#ffd12f&gt;nhận thêm 30% Sát Thương Fusion.&lt;/color&gt;
+- Đánh trúng mục tiêu bằng Đòn Cơ Bản sẽ nhận được 20 Năng Lượng Giấc Mộng. Hiệu ứng này có thể kích hoạt mỗi giây một lần. &lt;color=#ffd12f&gt;Sử dụng Kỹ Năng Khởi Động sẽ nhận được 100 Năng Lượng Giấc Mộng. Hiệu ứng này có thể kích hoạt mỗi 10 giây một lần. Gây Sát Thương Fusion sẽ nhận được 30 Năng Lượng Giấc Mộng. Hiệu ứng này có thể kích hoạt mỗi giây một lần.&lt;/color&gt;
+- Khi Năng Lượng Giấc Mộng đạt 500, sẽ bước vào trạng thái Giấc Mơ Sáng Suốt. Trong trạng thái này, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Một số Ẩn Dụ sẽ được tăng cường trong trạng thái này. Giấc Mơ Sáng Suốt kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mộng khi kết thúc.</t>
         </is>
       </c>
     </row>
@@ -4267,11 +4267,11 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Resonators hỗ trợ Giấc Mơ Hiện Tại: &lt;color=#ffd12f&gt;Jinhsi, Phoebe, Shorekeeper, and Verina&lt;/color&gt;. Hãy sử dụng ít nhất một Resonators hỗ trợ Giấc Mơ để &lt;color=#ffd12f&gt;gain a 150% Point Bonus!&lt;/color&gt;
+          <t>Resonator hỗ trợ Giấc Mơ Hiện Tại: &lt;color=#ffd12f&gt;Jinhsi, Phoebe, Shorekeeper và Verina&lt;/color&gt;. Hãy sử dụng ít nhất một Resonator hỗ trợ Giấc Mơ để &lt;color=#ffd12f&gt;nhận thưởng Điểm gấp 150%!&lt;/color&gt;
 Hiệu ứng hỗ trợ Giấc Mơ hiện tại:
-- Tất cả Resonators trong đội &lt;color=#ffd12f&gt;gain 30% Spectro DMG Bonus.&lt;/color&gt;
-- Đánh trúng mục tiêu bằng Basic Attack sẽ hồi 20 Năng Lượng Giấc Mơ. Hiệu ứng này kích hoạt mỗi giây một lần. &lt;color=#ffd12f&gt;Casting Resonance Skill grants 100 Dreamscape Energy. This effect can be triggered once every 10s. Dealing Spectro DMG grants 30 Dreamscape Energy. This effect can be triggered once every second.&lt;/color&gt;
-- Khi Năng Lượng Giấc Mơ đạt 500, sẽ bước vào trạng thái Lucid Dream. Trong trạng thái này, Crit. Rate và Energy Regen của tất cả Resonators trong đội tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Một số Ẩn Dụ sẽ được tăng cường trong trạng thái này. Lucid Dream kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.</t>
+- Tất cả Resonator trong đội &lt;color=#ffd12f&gt;nhận thêm 30% Sát Thương Spectro.&lt;/color&gt;
+- Đánh trúng mục tiêu bằng Đòn Cơ Bản sẽ hồi 20 Năng Lượng Giấc Mơ. Hiệu ứng này kích hoạt mỗi giây một lần. &lt;color=#ffd12f&gt;Sử dụng Resonance Skill sẽ hồi 100 Năng Lượng Giấc Mơ. Hiệu ứng này kích hoạt mỗi 10 giây một lần. Gây Sát Thương Spectro sẽ hồi 30 Năng Lượng Giấc Mơ. Hiệu ứng này kích hoạt mỗi giây một lần.&lt;/color&gt;
+- Khi Năng Lượng Giấc Mơ đạt 500, sẽ bước vào trạng thái Giấc Mơ Sáng Suốt. Trong trạng thái này, Crit. Rate và Hồi Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Một số Ẩn Dụ sẽ được tăng cường trong trạng thái này. Giấc Mơ Sáng Suốt kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.</t>
         </is>
       </c>
     </row>
@@ -4340,11 +4340,11 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Resonators Hỗ Trợ Giấc Mơ Hiện Tại: &lt;color=#ffd12f&gt;Jiyan, Jianxin, Mortefi, Yangyang, and Aalto&lt;/color&gt;. Hãy sử dụng ít nhất một Resonators Hỗ Trợ Giấc Mơ để &lt;color=#ffd12f&gt;gain a 150% Point Bonus!&lt;/color&gt;
+          <t>Resonator Hỗ Trợ Giấc Mơ Hiện Tại: &lt;color=#ffd12f&gt;Jiyan, Jianxin, Mortefi, Yangyang và Aalto&lt;/color&gt;. Hãy sử dụng ít nhất một Resonator Hỗ Trợ Giấc Mơ để &lt;color=#ffd12f&gt;nhận thưởng điểm gấp 150%!&lt;/color&gt;
 Hiệu ứng Hỗ Trợ Giấc Mơ Hiện Tại:
-- Tất cả Resonators trong đội &lt;color=#ffd12f&gt;gain 30% Aero DMG Bonus.&lt;/color&gt;
-- Đánh trúng mục tiêu bằng Basic Attack sẽ nhận được 20 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần. &lt;color=#ffd12f&gt;Casting Resonance Liberation grants 100 Dreamscape Energy. This effect can be triggered once every 10s. Dealing Aero DMG grants 30 Dreamscape Energy. This effect can be triggered once every second.&lt;/color&gt;
-- Khi Năng Lượng Giấc Mơ đạt 500, bạn sẽ bước vào trạng thái Lucid Dream. Trong trạng thái này, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonators trong đội sẽ tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Một số Ảo Ảnh sẽ được tăng cường trong trạng thái này. Lucid Dream kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.</t>
+- Tất cả Resonator trong đội &lt;color=#ffd12f&gt;nhận thêm 30% Sát Thương Aero.&lt;/color&gt;
+- Đánh trúng mục tiêu bằng Đòn Cơ Bản sẽ nhận được 20 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần. &lt;color=#ffd12f&gt;Sử dụng Resonance Liberation sẽ nhận được 100 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi 10 giây một lần. Gây Sát Thương Aero sẽ nhận được 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.&lt;/color&gt;
+- Khi Năng Lượng Giấc Mơ đạt 500, bạn sẽ bước vào trạng thái Giấc Mơ Sáng Suốt. Trong trạng thái này, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonator trong đội sẽ tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Một số Ảo Ảnh sẽ được tăng cường trong trạng thái này. Giấc Mơ Sáng Suốt kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.</t>
         </is>
       </c>
     </row>
@@ -4413,11 +4413,11 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Resonators Hỗ Trợ Giấc Mơ Hiện Tại: &lt;color=#ffd12f&gt;Xiangli Yao, Yinlin, Calcharo, and Yuanwu&lt;/color&gt;. Hãy sử dụng ít nhất một Resonators Hỗ Trợ Giấc Mơ để nhận thêm 150% Điểm Bonus!
+          <t>Resonator Hỗ Trợ Giấc Mơ Hiện Tại: &lt;color=#ffd12f&gt;Xiangli Yao, Yinlin, Calcharo, và Yuanwu&lt;/color&gt;. Hãy sử dụng ít nhất một Resonator Hỗ Trợ Giấc Mơ để nhận thêm 150% Điểm Thưởng!
 Hiệu ứng Hỗ Trợ Giấc Mơ Hiện Tại:
-- Tất cả Resonators trong đội &lt;color=#ffd12f&gt;gain 30% Electro DMG Bonus&lt;/color&gt;.
-- Đánh trúng mục tiêu bằng Basic Attack sẽ hồi 20 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần. &lt;color=#ffd12f&gt;Casting Intro Skill grants 100 Dreamscape Energy. This effect can be triggered once every 10s. Dealing Electro DMG grants 30 Dreamscape Energy. This effect can be triggered once every second.&lt;/color&gt;
-- Khi Năng Lượng Giấc Mơ đạt 500, bạn sẽ bước vào trạng thái Lucid Dream. Trong trạng thái này, Crit. Rate và Energy Regen của tất cả Resonators trong đội tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Một số Ảo Giác sẽ được tăng cường trong trạng thái này. Lucid Dream kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.</t>
+- Tất cả Resonator trong đội &lt;color=#ffd12f&gt;nhận thêm 30% Tăng Sát Thương Electro&lt;/color&gt;.
+- Đánh trúng mục tiêu bằng Đòn Cơ Bản sẽ hồi 20 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần. &lt;color=#ffd12f&gt;Sử dụng Kỹ Năng Khởi Động sẽ hồi 100 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi 10 giây một lần. Gây Sát Thương Electro sẽ hồi 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.&lt;/color&gt;
+- Khi Năng Lượng Giấc Mơ đạt 500, bạn sẽ bước vào trạng thái Giấc Mơ Sáng Suốt. Trong trạng thái này, Crit. Rate và Hồi Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Một số Ảo Giác sẽ được tăng cường trong trạng thái này. Giấc Mơ Sáng Suốt kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.</t>
         </is>
       </c>
     </row>
@@ -4486,11 +4486,11 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Resonators Hỗ Trợ Giấc Mơ Hiện Tại: &lt;color=#ffd12f&gt;Camellya, Roccia, Danjin, Baizhi, and Cantarella&lt;/color&gt;. Hãy sử dụng ít nhất một Resonators Hỗ Trợ Giấc Mơ để &lt;color=#ffd12f&gt;gain a 150% Point Bonus!&lt;/color&gt;
+          <t>Resonator Hỗ Trợ Giấc Mơ Hiện Tại: &lt;color=#ffd12f&gt;Camellya, Roccia, Danjin, Baizhi và Cantarella&lt;/color&gt;. Hãy sử dụng ít nhất một Resonator Hỗ Trợ Giấc Mơ để &lt;color=#ffd12f&gt;nhận thưởng 150% Điểm!&lt;/color&gt;
 Hiệu ứng Hỗ Trợ Giấc Mơ Hiện Tại:
-- Tất cả Resonators trong đội &lt;color=#ffd12f&gt;gain 30% Havoc DMG Bonus&lt;/color&gt;
-- Tấn công mục tiêu bằng Basic Attack sẽ nhận được 20 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần. &lt;color=#ffd12f&gt;Hitting a target with Heavy Attack grants 10 Dreamscape Energy. This effect can be triggered once every second. Dealing Havoc DMG grants 30 Dreamscape Energy. This effect can be triggered once every second.&lt;/color&gt;
-- Khi Năng Lượng Giấc Mơ đạt 500, sẽ bước vào trạng thái Lucid Dream. Trong trạng thái này, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Một số Ẩn Dụ sẽ được tăng cường trong trạng thái này. Lucid Dream kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.</t>
+- Tất cả Resonator trong đội &lt;color=#ffd12f&gt;nhận thêm 30% Sát Thương Havoc.&lt;/color&gt;
+- Tấn công mục tiêu bằng Đòn Cơ Bản sẽ nhận được 20 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần. &lt;color=#ffd12f&gt;Tấn công mục tiêu bằng Đòn Nặng sẽ nhận được 10 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần. Gây Sát Thương Havoc sẽ nhận được 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.&lt;/color&gt;
+- Khi Năng Lượng Giấc Mơ đạt 500, sẽ bước vào trạng thái Giấc Mơ Sáng Suốt. Trong trạng thái này, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Một số Ẩn Dụ sẽ được tăng cường trong trạng thái này. Giấc Mơ Sáng Suốt kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.</t>
         </is>
       </c>
     </row>
@@ -4559,11 +4559,11 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Resonators Hỗ Trợ Giấc Mơ Hiện Tại: &lt;color=#ffd12f&gt;Zani, Jinhsi, Phoebe, Shorekeeper, and Verina&lt;/color&gt;. Hãy sử dụng ít nhất một Resonators Hỗ Trợ Giấc Mơ để &lt;color=#ffd12f&gt;gain a 150% Point Bonus!&lt;/color&gt;
+          <t>Resonator Hỗ Trợ Giấc Mơ Hiện Tại: &lt;color=#ffd12f&gt;Zani, Jinhsi, Phoebe, Shorekeeper, và Verina&lt;/color&gt;. Hãy sử dụng ít nhất một Resonator Hỗ Trợ Giấc Mơ để &lt;color=#ffd12f&gt;nhận thêm 150% Điểm Thưởng!&lt;/color&gt;
 Hiệu ứng Hỗ Trợ Giấc Mơ Hiện Tại:
-- Tất cả Resonators trong đội &lt;color=#ffd12f&gt;gain 30% Spectro DMG Bonus.&lt;/color&gt;
-- Đánh trúng mục tiêu bằng Basic Attack sẽ hồi 20 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần. &lt;color=#ffd12f&gt;Casting Resonance Skill grants 100 Dreamscape Energy. This effect can be triggered once every 10s. Dealing Spectro DMG grants 30 Dreamscape Energy. This effect can be triggered once every second.&lt;/color&gt;
-- Khi Năng Lượng Giấc Mơ đạt 500, bạn sẽ bước vào trạng thái Lucid Dream. Trong trạng thái này, Crit. Rate và Energy Regen của tất cả Resonators trong đội tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Một số Ảo Giác sẽ được tăng cường trong trạng thái này. Lucid Dream kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.</t>
+- Tất cả Resonator trong đội &lt;color=#ffd12f&gt;nhận thêm 30% Tăng Sát Thương Spectro.&lt;/color&gt;
+- Đánh trúng mục tiêu bằng Đòn Cơ Bản sẽ hồi 20 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần. &lt;color=#ffd12f&gt;Sử dụng Resonance Skill sẽ hồi 100 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi 10 giây một lần. Gây Sát Thương Spectro sẽ hồi 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.&lt;/color&gt;
+- Khi Năng Lượng Giấc Mơ đạt 500, bạn sẽ bước vào trạng thái Giấc Mơ Sáng Suốt. Trong trạng thái này, Crit. Rate và Hồi Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Một số Ảo Giác sẽ được tăng cường trong trạng thái này. Giấc Mơ Sáng Suốt kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.</t>
         </is>
       </c>
     </row>
@@ -4632,11 +4632,11 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Resonators Current Dreamscape Aid: &lt;color=#ffd12f&gt;Brant, Changli, Encore, Chixia, and Mortefi&lt;/color&gt;. Sử dụng ít nhất một Resonators Hỗ Trợ Giấc Mộng để &lt;color=#ffd12f&gt;gain a 150% Point Bonus!&lt;/color&gt;
-Hiệu ứng Current Dreamscape Aid:
-- Tất cả Resonators trong đội &lt;color=#ffd12f&gt;gain 30% Fusion DMG Bonus.&lt;/color&gt; 
-- &lt;color=#ffd12f&gt;Dealing Fusion DMG grants 30 Dreamscape Energy. This effect can be triggered once every second.&lt;/color&gt; 
-- Khi Năng Lượng Giấc Mộng đạt 500, sẽ bước vào trạng thái Lucid Dream. Trong trạng thái này, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Một số Ẩn Dụ sẽ được tăng cường trong trạng thái này. Lucid Dream kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mộng khi kết thúc.</t>
+          <t>Resonator Hỗ Trợ Giấc Mộng Hiện Tại: &lt;color=#ffd12f&gt;Brant, Changli, Encore, Chixia và Mortefi&lt;/color&gt;. Sử dụng ít nhất một Resonator Hỗ Trợ Giấc Mộng để &lt;color=#ffd12f&gt;nhận thêm 150% Điểm Thưởng!&lt;/color&gt;
+Hiệu ứng Hỗ Trợ Giấc Mộng Hiện Tại:
+- Tất cả Resonator trong đội &lt;color=#ffd12f&gt;nhận thêm 30% Sát Thương Fusion.&lt;/color&gt; 
+- &lt;color=#ffd12f&gt;Gây Sát Thương Fusion sẽ nhận được 30 Năng Lượng Giấc Mộng. Hiệu ứng này có thể kích hoạt mỗi giây một lần.&lt;/color&gt; 
+- Khi Năng Lượng Giấc Mộng đạt 500, sẽ bước vào trạng thái Giấc Mơ Sáng Suốt. Trong trạng thái này, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Một số Ẩn Dụ sẽ được tăng cường trong trạng thái này. Giấc Mơ Sáng Suốt kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mộng khi kết thúc.</t>
         </is>
       </c>
     </row>
@@ -4705,11 +4705,11 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Resonators Current Dreamscape Aid: &lt;color=#ffd12f&gt;Camellya, Roccia, Danjin, Baizhi, and Cantarella&lt;/color&gt;. Sử dụng ít nhất một Resonators Hỗ Trợ Giấc Mộng để &lt;color=#ffd12f&gt;gain a 150% Point Bonus!&lt;/color&gt;
-Hiệu ứng Current Dreamscape Aid:
-- Tất cả Resonators trong đội &lt;color=#ffd12f&gt;gain 30% Havoc DMG Bonus.&lt;/color&gt; 
-- &lt;color=#ffd12f&gt;Dealing Havoc DMG grants 30 Dreamscape Energy. This effect can be triggered once every second.&lt;/color&gt; 
-- Khi Năng Lượng Giấc Mộng đạt 500, sẽ bước vào trạng thái Lucid Dream. Trong trạng thái này, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Một số Ẩn Dụ sẽ được tăng cường trong trạng thái này. Lucid Dream kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mộng khi kết thúc.</t>
+          <t>Resonator Hỗ Trợ Giấc Mộng Hiện Tại: &lt;color=#ffd12f&gt;Camellya, Roccia, Danjin, Baizhi và Cantarella&lt;/color&gt;. Sử dụng ít nhất một Resonator Hỗ Trợ Giấc Mộng để &lt;color=#ffd12f&gt;nhận thêm 150% Điểm Thưởng!&lt;/color&gt;
+Hiệu ứng Hỗ Trợ Giấc Mộng Hiện Tại:
+- Tất cả Resonator trong đội &lt;color=#ffd12f&gt;nhận thêm 30% Sát Thương Havoc.&lt;/color&gt; 
+- &lt;color=#ffd12f&gt;Gây Sát Thương Havoc sẽ nhận được 30 Năng Lượng Giấc Mộng. Hiệu ứng này có thể kích hoạt mỗi giây một lần.&lt;/color&gt; 
+- Khi Năng Lượng Giấc Mộng đạt 500, sẽ bước vào trạng thái Giấc Mơ Sáng Suốt. Trong trạng thái này, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Một số Ẩn Dụ sẽ được tăng cường trong trạng thái này. Giấc Mơ Sáng Suốt kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mộng khi kết thúc.</t>
         </is>
       </c>
     </row>
@@ -4778,11 +4778,11 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Resonators hỗ trợ Giấc Mơ Hiện Tại: &lt;color=#ffd12f&gt;Cartethyia, Ciaccona, Jiyan, Jianxin, Yangyang, and Aalto&lt;/color&gt;. Hãy sử dụng ít nhất một Resonators hỗ trợ Giấc Mơ để &lt;color=#ffd12f&gt;gain a 150% Point Bonus!&lt;/color&gt;
+          <t>Resonator hỗ trợ Giấc Mơ Hiện Tại: &lt;color=#ffd12f&gt;Cartethyia, Ciaccona, Jiyan, Jianxin, Yangyang và Aalto&lt;/color&gt;. Hãy sử dụng ít nhất một Resonator hỗ trợ Giấc Mơ để &lt;color=#ffd12f&gt;nhận thưởng Điểm gấp 150%!&lt;/color&gt;
 Hiệu ứng hỗ trợ Giấc Mơ hiện tại:
-- Tất cả Resonators trong đội &lt;color=#ffd12f&gt;gain 30% Aero DMG Bonus.&lt;/color&gt;
-- &lt;color=#ffd12f&gt;Dealing Aero DMG grants 30 Dreamscape Energy. This effect can be triggered once every second.&lt;/color&gt;
-- Khi Năng Lượng Giấc Mơ đạt 500, sẽ bước vào trạng thái Lucid Dream. Trong trạng thái này, Crit. Rate và Energy Regen của tất cả Resonators trong đội tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Một số Ẩn Dụ sẽ được tăng cường trong trạng thái này. Lucid Dream kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.</t>
+- Tất cả Resonator trong đội &lt;color=#ffd12f&gt;nhận thêm 30% Sát Thương Aero.&lt;/color&gt;
+- &lt;color=#ffd12f&gt;Gây Sát Thương Aero sẽ hồi 30 Năng Lượng Giấc Mơ. Hiệu ứng này kích hoạt mỗi giây một lần.&lt;/color&gt;
+- Khi Năng Lượng Giấc Mơ đạt 500, sẽ bước vào trạng thái Giấc Mơ Sáng Suốt. Trong trạng thái này, Crit. Rate và Hồi Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Một số Ẩn Dụ sẽ được tăng cường trong trạng thái này. Giấc Mơ Sáng Suốt kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.</t>
         </is>
       </c>
     </row>
@@ -4851,11 +4851,11 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Resonators Hỗ Trợ Giấc Mơ Hiện Tại: &lt;color=#ffd12f&gt;Xiangli Yao, Yinlin, Calcharo, and Yuanwu&lt;/color&gt;. Hãy sử dụng ít nhất một Resonators Hỗ Trợ Giấc Mơ để &lt;color=#ffd12f&gt;gain a 150% Point Bonus!&lt;/color&gt;
+          <t>Resonator Hỗ Trợ Giấc Mơ Hiện Tại: &lt;color=#ffd12f&gt;Xiangli Yao, Yinlin, Calcharo, và Yuanwu&lt;/color&gt;. Hãy sử dụng ít nhất một Resonator Hỗ Trợ Giấc Mơ để &lt;color=#ffd12f&gt;nhận thêm 150% Điểm Thưởng!&lt;/color&gt;
 Hiệu ứng Hỗ Trợ Giấc Mơ Hiện Tại:
-- Tất cả Resonators trong đội &lt;color=#ffd12f&gt;gain 30% Electro DMG Bonus.&lt;/color&gt;
-- &lt;color=#ffd12f&gt;Dealing Electro DMG grants 30 Dreamscape Energy. This effect can be triggered once every second.&lt;/color&gt;
-- Khi Năng Lượng Giấc Mơ đạt 500, bạn sẽ bước vào trạng thái Lucid Dream. Trong trạng thái này, Crit. Rate và Energy Regen của tất cả Resonators trong đội tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Một số Ảo Giác sẽ được tăng cường trong trạng thái này. Lucid Dream kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.</t>
+- Tất cả Resonator trong đội &lt;color=#ffd12f&gt;nhận thêm 30% Tăng Sát Thương Electro.&lt;/color&gt;
+- &lt;color=#ffd12f&gt;Gây Sát Thương Electro sẽ hồi 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.&lt;/color&gt;
+- Khi Năng Lượng Giấc Mơ đạt 500, bạn sẽ bước vào trạng thái Giấc Mơ Sáng Suốt. Trong trạng thái này, Crit. Rate và Hồi Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Một số Ảo Giác sẽ được tăng cường trong trạng thái này. Giấc Mơ Sáng Suốt kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.</t>
         </is>
       </c>
     </row>
@@ -4924,11 +4924,11 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Resonators hỗ trợ Giấc Mơ Hiện Tại: &lt;color=#ffd12f&gt;Carlotta, Zhezhi, Lingyang, Sanhua, and Youhu&lt;/color&gt;. Hãy sử dụng ít nhất một Resonators hỗ trợ Giấc Mơ để &lt;color=#ffd12f&gt;gain a 150% Point Bonus!&lt;/color&gt;
+          <t>Resonator hỗ trợ Giấc Mơ Hiện Tại: &lt;color=#ffd12f&gt;Carlotta, Zhezhi, Lingyang, Sanhua và Youhu&lt;/color&gt;. Hãy sử dụng ít nhất một Resonator hỗ trợ Giấc Mơ để &lt;color=#ffd12f&gt;nhận thưởng Điểm gấp 150%!&lt;/color&gt;
 Hiệu ứng hỗ trợ Giấc Mơ hiện tại:
-- Tất cả Resonators trong đội &lt;color=#ffd12f&gt;gain 30% Glacio DMG Bonus.&lt;/color&gt;
-- &lt;color=#ffd12f&gt;Dealing Glacio DMG grants 30 Dreamscape Energy. This effect can be triggered once every second.&lt;/color&gt;
-- Khi Năng Lượng Giấc Mơ đạt 500, sẽ bước vào trạng thái Lucid Dream. Trong trạng thái này, Crit. Rate và Energy Regen của tất cả Resonators trong đội tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Một số Ẩn Dụ sẽ được tăng cường trong trạng thái này. Lucid Dream kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.</t>
+- Tất cả Resonator trong đội &lt;color=#ffd12f&gt;nhận thêm 30% Sát Thương Glacio.&lt;/color&gt;
+- &lt;color=#ffd12f&gt;Gây Sát Thương Glacio sẽ hồi 30 Năng Lượng Giấc Mơ. Hiệu ứng này kích hoạt mỗi giây một lần.&lt;/color&gt;
+- Khi Năng Lượng Giấc Mơ đạt 500, sẽ bước vào trạng thái Giấc Mơ Sáng Suốt. Trong trạng thái này, Crit. Rate và Hồi Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Một số Ẩn Dụ sẽ được tăng cường trong trạng thái này. Giấc Mơ Sáng Suốt kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.</t>
         </is>
       </c>
     </row>
@@ -4997,11 +4997,11 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Resonators hỗ trợ Giấc Mơ Hiện Tại: &lt;color=#ffd12f&gt;Cartethyia, Ciaccona, Jiyan, Jianxin, Yangyang, and Aalto&lt;/color&gt;. Hãy sử dụng ít nhất một Resonators hỗ trợ Giấc Mơ để &lt;color=#ffd12f&gt;gain a 150% Point Bonus!&lt;/color&gt;
+          <t>Resonator hỗ trợ Giấc Mơ Hiện Tại: &lt;color=#ffd12f&gt;Cartethyia, Ciaccona, Jiyan, Jianxin, Yangyang và Aalto&lt;/color&gt;. Hãy sử dụng ít nhất một Resonator hỗ trợ Giấc Mơ để &lt;color=#ffd12f&gt;nhận thưởng Điểm gấp 150%!&lt;/color&gt;
 Hiệu ứng hỗ trợ Giấc Mơ hiện tại:
-- Tất cả Resonators trong đội &lt;color=#ffd12f&gt;gain 30% Aero DMG Bonus.&lt;/color&gt;
-- &lt;color=#ffd12f&gt;Dealing Aero DMG grants 30 Dreamscape Energy. This effect can be triggered once every second.&lt;/color&gt;
-- Khi Năng Lượng Giấc Mơ đạt 500, sẽ bước vào trạng thái Lucid Dream. Trong trạng thái này, Crit. Rate và Energy Regen của tất cả Resonators trong đội tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Một số Ẩn Dụ sẽ được tăng cường trong trạng thái này. Lucid Dream kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.</t>
+- Tất cả Resonator trong đội &lt;color=#ffd12f&gt;nhận thêm 30% Sát Thương Aero.&lt;/color&gt;
+- &lt;color=#ffd12f&gt;Gây Sát Thương Aero sẽ hồi 30 Năng Lượng Giấc Mơ. Hiệu ứng này kích hoạt mỗi giây một lần.&lt;/color&gt;
+- Khi Năng Lượng Giấc Mơ đạt 500, sẽ bước vào trạng thái Giấc Mơ Sáng Suốt. Trong trạng thái này, Crit. Rate và Hồi Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Một số Ẩn Dụ sẽ được tăng cường trong trạng thái này. Giấc Mơ Sáng Suốt kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.</t>
         </is>
       </c>
     </row>
@@ -5070,11 +5070,11 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Resonators Hỗ Trợ Giấc Mơ Hiện Tại: &lt;color=#ffd12f&gt;Lupa, Brant, Changli, Encore, Chixia, and Mortefi&lt;/color&gt;. Hãy sử dụng ít nhất một Resonators Hỗ Trợ Giấc Mơ để &lt;color=#ffd12f&gt;gain a 150% Point Bonus!&lt;/color&gt;
+          <t>Resonator Hỗ Trợ Giấc Mơ Hiện Tại: &lt;color=#ffd12f&gt;Lupa, Brant, Changli, Encore, Chixia và Mortefi&lt;/color&gt;. Hãy sử dụng ít nhất một Resonator Hỗ Trợ Giấc Mơ để &lt;color=#ffd12f&gt;nhận thưởng điểm gấp 150%!&lt;/color&gt;
 Hiệu ứng Hỗ Trợ Giấc Mơ Hiện Tại:
-- Tất cả Resonators trong đội &lt;color=#ffd12f&gt;gain 30% Fusion DMG Bonus.&lt;/color&gt;
-- &lt;color=#ffd12f&gt;Dealing Fusion DMG grants 30 Dreamscape Energy. This effect can be triggered once every second.&lt;/color&gt;
-- Khi Năng Lượng Giấc Mơ đạt 500, bạn sẽ bước vào trạng thái Lucid Dream. Trong trạng thái này, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonators trong đội sẽ tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Một số Ảo Ảnh sẽ được tăng cường trong trạng thái này. Lucid Dream kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.</t>
+- Tất cả Resonator trong đội &lt;color=#ffd12f&gt;nhận thêm 30% Sát Thương Fusion.&lt;/color&gt;
+- &lt;color=#ffd12f&gt;Gây Sát Thương Fusion sẽ nhận được 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.&lt;/color&gt;
+- Khi Năng Lượng Giấc Mơ đạt 500, bạn sẽ bước vào trạng thái Giấc Mơ Sáng Suốt. Trong trạng thái này, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonator trong đội sẽ tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Một số Ảo Ảnh sẽ được tăng cường trong trạng thái này. Giấc Mơ Sáng Suốt kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.</t>
         </is>
       </c>
     </row>
@@ -5141,8 +5141,8 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Summon Sentry Construct và tạo trường phòng thủ kéo dài {0} giây.
-Trong trường này, tất cả Resonators trong đội sẽ nhận &lt;color=#ffd12f&gt;Shield&lt;/color&gt; mỗi {4} giây dựa trên {1} HP tối đa của người triệu hồi và tăng khả năng kháng gián đoạn trong {2} giây. Kích hoạt lại hiệu ứng sẽ làm mới thời gian.
+          <t>Triệu hồi Sentry Construct và tạo trường phòng thủ kéo dài {0} giây.
+Trong trường này, tất cả Resonator trong đội sẽ nhận &lt;color=#ffd12f&gt;Khiên&lt;/color&gt; mỗi {4} giây dựa trên {1} HP tối đa của người triệu hồi và tăng khả năng kháng gián đoạn trong {2} giây. Kích hoạt lại hiệu ứng sẽ làm mới thời gian.
 Hồi chiêu: {3} giây.</t>
         </is>
       </c>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Summon Lorelei và &lt;color=#ffd12f&gt;restore&lt;/color&gt; {0} HP tối đa cho tất cả Resonators trong đội ở gần. Hiệu ứng này có thể kích hoạt tối đa {1} lần. Resonators được hồi phục sẽ giảm {2} sát thương nhận vào trong {3} giây.
+          <t>Triệu hồi Lorelei và &lt;color=#ffd12f&gt;hồi phục&lt;/color&gt; {0} HP tối đa cho tất cả Resonator trong đội ở gần. Hiệu ứng này có thể kích hoạt tối đa {1} lần. Resonator được hồi phục sẽ giảm {2} DMG nhận vào trong {3} giây.
 Hồi chiêu: {4} giây</t>
         </is>
       </c>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Summon Hecate để &lt;color=#ffd12f&gt;control the target&lt;/color&gt; trong {0} giây và khôi phục {1} Concerto Energy cho tất cả Resonators gần đó trong đội.
+          <t>Triệu hồi Hecate để &lt;color=#ffd12f&gt;kiểm soát mục tiêu&lt;/color&gt; trong {0} giây và khôi phục {1} Concerto Energy cho tất cả Resonator gần đó trong đội.
 Hồi chiêu: {2} giây</t>
         </is>
       </c>
@@ -5344,8 +5344,8 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Summon Dragon Than Khóc để tạo ra Vực Sầu, tồn tại trong 10 giây, liên tục gây {0} &lt;color=#ffd12f&gt;Fusion DMG&lt;/color&gt; lên kẻ địch trong phạm vi.
-Gây sát thương lên kẻ địch bằng Kỹ Năng Echo này sẽ ban thêm {1} Tăng Sát Thương Basic Attack và Heavy Attack cho tất cả Resonators trong đội ở gần, kích hoạt mỗi giây một lần, tối đa {2} lần.
+          <t>Triệu hồi Rồng Than Khóc để tạo ra Vực Sầu, tồn tại trong 10 giây, liên tục gây {0} &lt;color=#ffd12f&gt;Sát Thương Hỏa&lt;/color&gt; lên kẻ địch trong phạm vi.
+Gây DMG lên kẻ địch bằng Kỹ Năng Echo này sẽ ban thêm {1} Tăng Sát Thương Đòn Cơ Bản và Đòn Nặng cho tất cả Resonator trong đội ở gần, kích hoạt mỗi giây một lần, tối đa {2} lần.
 Hồi chiêu: {3} giây</t>
         </is>
       </c>
@@ -5413,9 +5413,9 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Biến thành Fallacy of Không Return và thực hiện liên tiếp các đòn tấn công về phía trước, gây tổng cộng {0} &lt;color=#ffd12f&gt;Spectro DMG&lt;/color&gt;.
-Gây sát thương lên kẻ địch bằng Kỹ Năng Echo này sẽ giảm Cooldown chiêu Resonance Skill {1} cho tất cả Resonators trong đội ở gần và tăng {2} Sát Thương Resonance Skill trong {4} giây, có thể tích lũy tối đa {3} lần. Kích hoạt lại hiệu ứng sẽ làm mới thời gian.
-Hồi chiêu: {5} giây</t>
+          <t>Biến hình thành Ảo Tưởng Vô Hồi và thực hiện liên tiếp các đòn tấn công về phía trước, gây tổng cộng {0} &lt;color=#ffd12f&gt;Sát Thương Spectro&lt;/color&gt;.
+Gây DMG lên kẻ địch bằng Kỹ Năng Tiếng Vọng này sẽ giảm Thời gian hồi chiêu Resonance Skill {1} cho tất cả Resonator trong đội ở gần và tăng {2} Sát Thương Resonance Skill trong {4} giây, có thể tích lũy tối đa {3} lần. Kích hoạt lại hiệu ứng sẽ làm mới thời gian.
+Thời gian hồi: {5} giây</t>
         </is>
       </c>
     </row>
@@ -5481,8 +5481,8 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Summon một Hocus Pocus giải phóng Nốt Tăng Cường 3 lần. Mỗi lần, tất cả Resonators trong đội gần đó nhận được {0} &lt;color=#ffd12f&gt;Resonance Energy&lt;/color&gt; và {1} Tăng Sát Thương Resonance Liberation trong {2} giây, đồng thời giảm {3} giây Hồi chiêu Resonance Liberation.
-Hồi chiêu: {4} giây</t>
+          <t>Triệu hồi một Hocus Pocus giải phóng Nốt Tăng Cường 3 lần. Mỗi lần, tất cả Resonator trong đội gần đó nhận được {0} &lt;color=#ffd12f&gt;Resonance Energy&lt;/color&gt; và {1} Tăng Sát Thương Resonance Liberation trong {2} giây, đồng thời giảm {3} giây Thời gian hồi Resonance Liberation.
+Thời gian hồi: {4} giây</t>
         </is>
       </c>
     </row>
@@ -5551,10 +5551,10 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Summon Fae Ignis tấn công, gây {0} &lt;color=#ffd12f&gt;Havoc DMG&lt;/color&gt; và áp đặt &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=1} &lt;color=#ffd12f&gt;Panic&lt;/color&gt; lên mục tiêu. Nếu mục tiêu đã có từ 70 lớp &lt;color=#ffd12f&gt;Panic&lt;/color&gt; trở lên, đòn tấn công vẫn gây sát thương tương tự nhưng chỉ áp đặt 30 lớp &lt;color=#ffd12f&gt;Panic&lt;/color&gt;.
-Khi mục tiêu mang Panic chịu sát thương, chúng nhận thêm &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=2} &lt;color=#ffd12f&gt;Panic&lt;/color&gt;. Hiệu ứng này kích hoạt mỗi giây một lần.
-Khi mục tiêu nhận đủ 100 lớp &lt;color=#ffd12f&gt;Panic&lt;/color&gt;, gây Sát Thương Vibration Strength bằng 100.00% Vibration Strength Tối Đa và Hóa Đá mục tiêu. Tất cả sát thương thuộc tính mà mục tiêu chịu trong hiệu ứng này đều chắc chắn trở thành Crit. DMG, đồng thời Kháng Sát Thương của chúng giảm {3}. Kích hoạt hiệu ứng này sẽ xóa toàn bộ lớp &lt;color=#ffd12f&gt;Panic&lt;/color&gt;.
-Mục tiêu sẽ không nhận thêm lớp &lt;color=#ffd12f&gt;Panic&lt;/color&gt; khi bị Hóa Đá.
+          <t>Triệu hồi Fae Ignis tấn công, gây {0} &lt;color=#ffd12f&gt;Sát Thương Hỗn Loạn&lt;/color&gt; và áp đặt &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=1} &lt;color=#ffd12f&gt;Hoảng Loạn&lt;/color&gt; lên mục tiêu. Nếu mục tiêu đã có từ 70 lớp &lt;color=#ffd12f&gt;Hoảng Loạn&lt;/color&gt; trở lên, đòn tấn công vẫn gây DMG tương tự nhưng chỉ áp đặt 30 lớp &lt;color=#ffd12f&gt;Hoảng Loạn&lt;/color&gt;.
+Khi mục tiêu mang Hoảng Loạn chịu DMG, chúng nhận thêm &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=2} &lt;color=#ffd12f&gt;Hoảng Loạn&lt;/color&gt;. Hiệu ứng này kích hoạt mỗi giây một lần.
+Khi mục tiêu nhận đủ 100 lớp &lt;color=#ffd12f&gt;Hoảng Loạn&lt;/color&gt;, gây Sát Thương Độ Rung bằng 100.00% Độ Rung Tối Đa và Hóa Đá mục tiêu. Tất cả DMG thuộc tính mà mục tiêu chịu trong hiệu ứng này đều chắc chắn trở thành Crit. DMG, đồng thời Kháng Sát Thương của chúng giảm {3}. Kích hoạt hiệu ứng này sẽ xóa toàn bộ lớp &lt;color=#ffd12f&gt;Hoảng Loạn&lt;/color&gt;.
+Mục tiêu sẽ không nhận thêm lớp &lt;color=#ffd12f&gt;Hoảng Loạn&lt;/color&gt; khi bị Hóa Đá.
 Hồi chiêu: {4} giây</t>
         </is>
       </c>
@@ -5623,9 +5623,9 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Biến thành Chop Chop trong {0} giây, gây {1} &lt;color=#ffd12f&gt;Fusion DMG&lt;/color&gt;. Gây sát thương lên kẻ địch sẽ làm mới thời gian Biến Hình Echo, tối đa {2} giây, và áp dụng &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; &lt;color=#ffd12f&gt;Panic&lt;/color&gt; {Cus:Sap,S=cấp P=cấp SapTag=3} lên mục tiêu. Hiệu ứng này có thể kích hoạt mỗi giây một lần trên mỗi mục tiêu. Thời gian Biến Hình Echo sẽ không được làm mới khi Resonator không ở trên chiến trường.
-Khi mục tiêu nhận đủ 100 cấp &lt;color=#ffd12f&gt;Panic&lt;/color&gt;, cạn kiệt Năng Lượng Rung Động của mục tiêu bằng 100.00% Năng Lượng Rung Động tối đa và Làm Choáng mục tiêu. Sát thương nhận vào khi bị Làm Choáng chắc chắn là Crit. DMG, và Kháng Sát Thương tất cả thuộc tính của mục tiêu giảm {4}. Kích hoạt hiệu ứng này sẽ xóa toàn bộ cấp &lt;color=#ffd12f&gt;Panic&lt;/color&gt;.
-Mục tiêu sẽ không nhận thêm cấp &lt;color=#ffd12f&gt;Panic&lt;/color&gt; khi đang bị Làm Choáng.
+          <t>Biến hình thành Chop Chop trong {0} giây, gây {1} &lt;color=#ffd12f&gt;Sát Thương Fusion&lt;/color&gt;. Gây DMG lên kẻ địch sẽ làm mới thời gian Biến Hình Echo, tối đa {2} giây, và áp dụng &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; &lt;color=#ffd12f&gt;Hoảng Loạn&lt;/color&gt; {Cus:Sap,S=cấp P=cấp SapTag=3} lên mục tiêu. Hiệu ứng này có thể kích hoạt mỗi giây một lần trên mỗi mục tiêu. Thời gian Biến Hình Echo sẽ không được làm mới khi Resonator không ở trên chiến trường.
+Khi mục tiêu nhận đủ 100 cấp &lt;color=#ffd12f&gt;Hoảng Loạn&lt;/color&gt;, cạn kiệt Năng Lượng Rung Động của mục tiêu bằng 100.00% Năng Lượng Rung Động tối đa và Làm Choáng mục tiêu. DMG nhận vào khi bị Làm Choáng chắc chắn là Crit. DMG, và Kháng Sát Thương tất cả thuộc tính của mục tiêu giảm {4}. Kích hoạt hiệu ứng này sẽ xóa toàn bộ cấp &lt;color=#ffd12f&gt;Hoảng Loạn&lt;/color&gt;.
+Mục tiêu sẽ không nhận thêm cấp &lt;color=#ffd12f&gt;Hoảng Loạn&lt;/color&gt; khi đang bị Làm Choáng.
 Hồi chiêu: {5} giây</t>
         </is>
       </c>
@@ -5693,8 +5693,8 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Summon Rương Bắt Chước liên tục nhả ra đồng tiền vàng. Khi nhặt lên, đồng tiền sẽ &lt;color=#ffd12f&gt;hồi phục&lt;/color&gt; {0} HP và {1} Stamina cho Resonators, đồng thời áp dụng &lt;color=#ffd12f&gt;Hăng Hái&lt;/color&gt; cho tất cả Resonators trong đội ở gần trong {2} giây.
-Nhận &lt;color=#ffd12f&gt;Hăng Hái&lt;/g&gt; làm tăng Tấn Công thêm {3} và Movement Speed thêm {4}. Khi có hơn 6 lớp &lt;color=#ffd12f&gt;Hăng Hái&lt;/color&gt;, Resonators sẽ được tăng thêm {5} Tấn Công, {6} Movement Speed và {7} sát thương gây ra lên mục tiêu Bị Cố Định.
+          <t>Triệu hồi Rương Bắt Chước liên tục nhả ra đồng tiền vàng. Khi nhặt lên, đồng tiền sẽ &lt;color=#ffd12f&gt;hồi phục&lt;/color&gt; {0} HP và {1} Thể Lực cho Resonator, đồng thời áp dụng &lt;color=#ffd12f&gt;Hăng Hái&lt;/color&gt; cho tất cả Resonator trong đội ở gần trong {2} giây.
+Nhận &lt;color=#ffd12f&gt;Hăng Hái&lt;/color&gt; làm tăng ATK thêm {3} và Tốc Độ Di Chuyển thêm {4}. Khi có hơn 6 lớp &lt;color=#ffd12f&gt;Hăng Hái&lt;/color&gt;, Resonator sẽ được tăng thêm {5} ATK, {6} Tốc Độ Di Chuyển và {7} DMG gây ra lên mục tiêu Bị Cố Định.
 Hồi chiêu: {8} giây</t>
         </is>
       </c>
@@ -5825,7 +5825,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Thời gian Buff:</t>
+          <t>Thời gian Hiệu ứng:</t>
         </is>
       </c>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Đóng góp DMG:</t>
+          <t>Đóng Góp Sát Thương:</t>
         </is>
       </c>
     </row>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Thời gian CC:</t>
+          <t>Thời gian Hiệu ứng CC:</t>
         </is>
       </c>
     </row>
@@ -6021,8 +6021,8 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Mỗi khi Resonators thực hiện &lt;color=#b72924ff&gt;Dash&lt;/color&gt;, kẻ địch nhận 1 tầng hiệu ứng sau: &lt;color=#b72924ff&gt;ATK is increased by 10%&lt;/color&gt;, tối đa &lt;color=#b72924ff&gt;10&lt;/color&gt; tầng.
-Mỗi lần &lt;color=#5cc96aff&gt;successful Dodge&lt;/color&gt; sẽ loại bỏ &lt;color=#5cc96aff&gt;3&lt;/color&gt; tầng.</t>
+          <t>Mỗi khi Resonator thực hiện &lt;color=#b72924ff&gt;Đột Kích&lt;/color&gt;, kẻ địch nhận 1 tầng hiệu ứng sau: &lt;color=#b72924ff&gt;ATK tăng 10%&lt;/color&gt;, tối đa &lt;color=#b72924ff&gt;10&lt;/color&gt; tầng.
+Mỗi lần &lt;color=#5cc96aff&gt;Né tránh thành công&lt;/color&gt; sẽ loại bỏ &lt;color=#5cc96aff&gt;3&lt;/color&gt; tầng.</t>
         </is>
       </c>
     </row>
@@ -6087,7 +6087,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Kẻ địch &lt;color=#b72924ff&gt;Dying enemies&lt;/color&gt; để lại một bẫy lửa cháy trong &lt;color=#b72924ff&gt;10s&lt;/color&gt;. Resonators bị mắc kẹt trong đó sẽ nhận &lt;color=#b72924ff&gt;1 tầng Fusion Burst&lt;/color&gt; mỗi &lt;color=#b72924ff&gt;0.5s&lt;/color&gt;. (Khi đạt 10 tầng, Fusion Burst sẽ phát nổ, gây sát thương lên Resonators.)</t>
+          <t>Kẻ địch &lt;color=#b72924ff&gt;hấp hối&lt;/color&gt; để lại một bẫy lửa cháy trong &lt;color=#b72924ff&gt;10 giây&lt;/color&gt;. Resonator bị mắc kẹt trong đó sẽ nhận &lt;color=#b72924ff&gt;1 tầng Fusion Burst&lt;/color&gt; mỗi &lt;color=#b72924ff&gt;0.5 giây&lt;/color&gt;. (Khi đạt 10 tầng, Fusion Burst sẽ phát nổ, gây sát thương lên Resonator.)</t>
         </is>
       </c>
     </row>
@@ -6152,7 +6152,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Mỗi &lt;color=#b72924ff&gt;Meteorite&lt;/color&gt;, &lt;color=#b72924ff&gt;20s&lt;/color&gt; sẽ trút xuống Resonators, gây sát thương bằng &lt;color=#b72924ff&gt;5% of their current HP&lt;/color&gt; và để lại &lt;color=#b72924ff&gt;a burning trap&lt;/color&gt; trong &lt;color=#b72924ff&gt;10s&lt;/color&gt;. Resonators đứng trong bẫy sẽ nhận &lt;color=#b72924ff&gt;1&lt;/color&gt; tầng Fusion Burst mỗi &lt;color=#b72924ff&gt;1s&lt;/color&gt;. (Khi đạt 10 tầng, Fusion Burst sẽ phát nổ, gây sát thương cho Resonators.)</t>
+          <t>Mỗi &lt;color=#b72924ff&gt;20 giây&lt;/color&gt;, &lt;color=#b72924ff&gt;Thiên Thạch&lt;/color&gt; sẽ trút xuống Resonator, gây sát thương bằng &lt;color=#b72924ff&gt;5% HP hiện tại&lt;/color&gt; và để lại &lt;color=#b72924ff&gt;bẫy lửa&lt;/color&gt; trong &lt;color=#b72924ff&gt;10 giây&lt;/color&gt;. Resonator đứng trong bẫy sẽ nhận &lt;color=#b72924ff&gt;1&lt;/color&gt; tầng Fusion Burst mỗi &lt;color=#b72924ff&gt;1 giây&lt;/color&gt;. (Khi đạt 10 tầng, Fusion Burst sẽ phát nổ, gây sát thương cho Resonator.)</t>
         </is>
       </c>
     </row>
@@ -6217,7 +6217,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Mỗi &lt;color=#b72924ff&gt;Meteorite&lt;/color&gt;, &lt;color=#b72924ff&gt;20s&lt;/color&gt; sẽ trút xuống Resonators, gây sát thương bằng &lt;color=#b72924ff&gt;10% of their current HP&lt;/color&gt; và để lại &lt;color=#b72924ff&gt;a burning trap&lt;/color&gt; trong &lt;color=#b72924ff&gt;10s&lt;/color&gt;. Resonators đứng trong bẫy sẽ nhận &lt;color=#b72924ff&gt;1&lt;/color&gt; tầng Fusion Burst mỗi &lt;color=#b72924ff&gt;0.75s&lt;/color&gt;. (Khi đạt 10 tầng, Fusion Burst sẽ phát nổ, gây sát thương cho Resonators.)</t>
+          <t>Mỗi &lt;color=#b72924ff&gt;20 giây&lt;/color&gt;, &lt;color=#b72924ff&gt;Thiên Thạch&lt;/color&gt; sẽ trút xuống Resonator, gây sát thương bằng &lt;color=#b72924ff&gt;10% HP hiện tại&lt;/color&gt; và để lại &lt;color=#b72924ff&gt;bẫy lửa&lt;/color&gt; trong &lt;color=#b72924ff&gt;10 giây&lt;/color&gt;. Resonator đứng trong bẫy sẽ nhận &lt;color=#b72924ff&gt;1&lt;/color&gt; tầng Fusion Burst mỗi &lt;color=#b72924ff&gt;0,75 giây&lt;/color&gt;. (Khi đạt 10 tầng, Fusion Burst sẽ phát nổ, gây sát thương cho Resonator.)</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Mỗi &lt;color=#b72924ff&gt;Meteorite&lt;/color&gt;, &lt;color=#b72924ff&gt;20s&lt;/color&gt; sẽ trút xuống Resonators, gây sát thương bằng &lt;color=#b72924ff&gt;20% of their current HP&lt;/color&gt; và để lại &lt;color=#b72924ff&gt;a burning trap&lt;/color&gt; trong &lt;color=#b72924ff&gt;10s&lt;/color&gt;. Resonators đứng trong bẫy sẽ nhận &lt;color=#b72924ff&gt;1&lt;/color&gt; tầng Fusion Burst mỗi &lt;color=#b72924ff&gt;0.5s&lt;/color&gt;. (Khi đạt 10 tầng, Fusion Burst sẽ phát nổ, gây sát thương cho Resonators.)</t>
+          <t>Mỗi &lt;color=#b72924ff&gt;20 giây&lt;/color&gt;, &lt;color=#b72924ff&gt;Thiên Thạch&lt;/color&gt; sẽ trút xuống Resonator, gây sát thương bằng &lt;color=#b72924ff&gt;20% HP hiện tại&lt;/color&gt; và để lại &lt;color=#b72924ff&gt;bẫy lửa&lt;/color&gt; trong &lt;color=#b72924ff&gt;10 giây&lt;/color&gt;. Resonator đứng trong bẫy sẽ nhận &lt;color=#b72924ff&gt;1&lt;/color&gt; tầng Fusion Burst mỗi &lt;color=#b72924ff&gt;0,5 giây&lt;/color&gt;. (Khi đạt 10 tầng, Fusion Burst sẽ phát nổ, gây sát thương cho Resonator.)</t>
         </is>
       </c>
     </row>
@@ -6347,7 +6347,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Resonators chịu sát thương bằng &lt;color=#b72924ff&gt;1%&lt;/color&gt; HP tối đa &lt;color=#b72924ff&gt;every second&lt;/color&gt;. &lt;color=#5cc96aff&gt;Defeating an enemy&lt;/color&gt; sẽ hồi phục &lt;color=#5cc96aff&gt;50%&lt;/color&gt; HP tối đa.</t>
+          <t>Resonator chịu sát thương bằng &lt;color=#b72924ff&gt;1%&lt;/color&gt; HP tối đa &lt;color=#b72924ff&gt;mỗi giây&lt;/color&gt;. &lt;color=#5cc96aff&gt;Tiêu diệt kẻ địch&lt;/color&gt; sẽ hồi phục &lt;color=#5cc96aff&gt;50%&lt;/color&gt; HP tối đa.</t>
         </is>
       </c>
     </row>
@@ -6412,7 +6412,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Resonators chịu sát thương bằng &lt;color=#b72924ff&gt;2%&lt;/color&gt; HP tối đa &lt;color=#b72924ff&gt;every second&lt;/color&gt;. &lt;color=#5cc96aff&gt;Defeating an enemy&lt;/color&gt; sẽ hồi phục &lt;color=#5cc96aff&gt;50%&lt;/color&gt; HP tối đa.</t>
+          <t>Resonator chịu sát thương bằng &lt;color=#b72924ff&gt;2%&lt;/color&gt; HP tối đa &lt;color=#b72924ff&gt;mỗi giây&lt;/color&gt;. &lt;color=#5cc96aff&gt;Tiêu diệt kẻ địch&lt;/color&gt; sẽ hồi phục &lt;color=#5cc96aff&gt;50%&lt;/color&gt; HP tối đa.</t>
         </is>
       </c>
     </row>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Resonators chịu sát thương bằng &lt;color=#b72924ff&gt;3%&lt;/color&gt; HP tối đa &lt;color=#b72924ff&gt;every second&lt;/color&gt;. &lt;color=#5cc96aff&gt;Defeating an enemy&lt;/color&gt; sẽ hồi phục &lt;color=#5cc96aff&gt;50%&lt;/color&gt; HP tối đa.</t>
+          <t>Resonator chịu sát thương bằng &lt;color=#b72924ff&gt;3%&lt;/color&gt; HP tối đa &lt;color=#b72924ff&gt;mỗi giây&lt;/color&gt;. &lt;color=#5cc96aff&gt;Tiêu diệt kẻ địch&lt;/color&gt; sẽ hồi phục &lt;color=#5cc96aff&gt;50%&lt;/color&gt; HP tối đa.</t>
         </is>
       </c>
     </row>
@@ -6542,7 +6542,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Các Resonators mất HP bằng &lt;color=#b72924ff&gt;10%&lt;/color&gt; HP hiện tại và hồi 5 Resonance Energy sau khi &lt;color=#b72924ff&gt;casting Resonance Skill&lt;/color&gt;. Hiệu ứng này chỉ kích hoạt một lần mỗi giây.</t>
+          <t>Các Resonator mất HP bằng &lt;color=#b72924ff&gt;10%&lt;/color&gt; HP hiện tại và hồi 5 Resonance Energy sau khi &lt;color=#b72924ff&gt;sử dụng Resonance Skill&lt;/color&gt;. Hiệu ứng này chỉ kích hoạt một lần mỗi giây.</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Các Resonators mất HP bằng &lt;color=#b72924ff&gt;20%&lt;/color&gt; HP hiện tại và hồi 5 Resonance Energy sau khi &lt;color=#b72924ff&gt;casting Resonance Skill&lt;/color&gt;. Hiệu ứng này chỉ kích hoạt một lần mỗi giây.</t>
+          <t>Các Resonator mất HP bằng &lt;color=#b72924ff&gt;20%&lt;/color&gt; HP hiện tại và hồi 5 Resonance Energy sau khi &lt;color=#b72924ff&gt;sử dụng Resonance Skill&lt;/color&gt;. Hiệu ứng này chỉ kích hoạt một lần mỗi giây.</t>
         </is>
       </c>
     </row>
@@ -6672,7 +6672,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Kẻ địch &lt;color=#b72924ff&gt;Dying enemies&lt;/color&gt; gây sát thương lên Resonators gần đó bằng &lt;color=#b72924ff&gt;20%&lt;/color&gt; HP tối đa của họ.</t>
+          <t>Kẻ địch &lt;color=#b72924ff&gt;hấp hối&lt;/color&gt; gây sát thương lên Resonator gần đó bằng &lt;color=#b72924ff&gt;20%&lt;/color&gt; HP tối đa của họ.</t>
         </is>
       </c>
     </row>
@@ -6737,7 +6737,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Kẻ địch &lt;color=#b72924ff&gt;Dying enemies&lt;/color&gt; gây sát thương lên Resonators gần đó bằng &lt;color=#b72924ff&gt;40%&lt;/color&gt; HP tối đa của họ.</t>
+          <t>Kẻ địch &lt;color=#b72924ff&gt;hấp hối&lt;/color&gt; gây sát thương lên Resonator gần đó bằng &lt;color=#b72924ff&gt;40%&lt;/color&gt; HP tối đa của họ.</t>
         </is>
       </c>
     </row>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Kẻ địch &lt;color=#b72924ff&gt;ATK is increased by 15%&lt;/color&gt;. Khi tấn công trúng Resonators, gây &lt;color=#b72924ff&gt;1&lt;/color&gt; lớp &lt;color=#b72924ff&gt;Fusion Burst&lt;/color&gt;. Hiệu ứng này có thể kích hoạt mỗi &lt;color=#b72924ff&gt;1s&lt;/color&gt;. Gây sát thương lên kẻ địch bị &lt;color=#5cc96aff&gt;Spectro Frazzle&lt;/color&gt; hoặc &lt;color=#5cc96aff&gt;Aero Erosion&lt;/color&gt; sẽ loại bỏ &lt;color=#5cc96aff&gt;2&lt;/color&gt; lớp &lt;color=#5cc96aff&gt;Fusion Burst&lt;/color&gt;. Hiệu ứng này có thể kích hoạt mỗi 0.5 giây.</t>
+          <t>Kẻ địch &lt;color=#b72924ff&gt;ATK tăng 15%&lt;/color&gt;. Khi tấn công trúng Resonator, gây &lt;color=#b72924ff&gt;1&lt;/color&gt; lớp &lt;color=#b72924ff&gt;Fusion Burst&lt;/color&gt;. Hiệu ứng này có thể kích hoạt mỗi &lt;color=#b72924ff&gt;1 giây&lt;/color&gt;. Gây sát thương lên kẻ địch bị &lt;color=#5cc96aff&gt;Spectro Frazzle&lt;/color&gt; hoặc &lt;color=#5cc96aff&gt;Aero Erosion&lt;/color&gt; sẽ loại bỏ &lt;color=#5cc96aff&gt;2&lt;/color&gt; lớp &lt;color=#5cc96aff&gt;Fusion Burst&lt;/color&gt;. Hiệu ứng này có thể kích hoạt mỗi 0.5 giây.</t>
         </is>
       </c>
     </row>
@@ -6867,7 +6867,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Kẻ địch &lt;color=#b72924ff&gt;ATK is increased by 15%&lt;/color&gt;. Khi tấn công trúng Resonators, gây &lt;color=#b72924ff&gt;2&lt;/color&gt; lớp &lt;color=#b72924ff&gt;Fusion Burst&lt;/color&gt;. Hiệu ứng này có thể kích hoạt mỗi &lt;color=#b72924ff&gt;1s&lt;/color&gt;. Gây sát thương lên kẻ địch bị &lt;color=#5cc96aff&gt;Spectro Frazzle&lt;/color&gt; hoặc &lt;color=#5cc96aff&gt;Aero Erosion&lt;/color&gt; sẽ loại bỏ &lt;color=#5cc96aff&gt;2&lt;/color&gt; lớp &lt;color=#5cc96aff&gt;Fusion Burst&lt;/color&gt;. Hiệu ứng này có thể kích hoạt mỗi 0.5 giây.</t>
+          <t>Kẻ địch &lt;color=#b72924ff&gt;ATK tăng 15%&lt;/color&gt;. Khi tấn công trúng Resonator, gây &lt;color=#b72924ff&gt;2&lt;/color&gt; lớp &lt;color=#b72924ff&gt;Fusion Burst&lt;/color&gt;. Hiệu ứng này có thể kích hoạt mỗi &lt;color=#b72924ff&gt;1 giây&lt;/color&gt;. Gây sát thương lên kẻ địch bị &lt;color=#5cc96aff&gt;Spectro Frazzle&lt;/color&gt; hoặc &lt;color=#5cc96aff&gt;Aero Erosion&lt;/color&gt; sẽ loại bỏ &lt;color=#5cc96aff&gt;2&lt;/color&gt; lớp &lt;color=#5cc96aff&gt;Fusion Burst&lt;/color&gt;. Hiệu ứng này có thể kích hoạt mỗi 0.5 giây.</t>
         </is>
       </c>
     </row>
@@ -6933,8 +6933,8 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Mỗi khi Resonators thực hiện &lt;color=#b72924ff&gt;Dash&lt;/color&gt;, kẻ địch nhận 1 tầng hiệu ứng sau: &lt;color=#b72924ff&gt;ATK is increased by 10%&lt;/color&gt;, tối đa &lt;color=#b72924ff&gt;10&lt;/color&gt; tầng.
-Mỗi lần &lt;color=#5cc96aff&gt;successful Counterattack&lt;/color&gt; sẽ loại bỏ &lt;color=#5cc96aff&gt;3&lt;/color&gt; tầng.</t>
+          <t>Mỗi khi Resonator thực hiện &lt;color=#b72924ff&gt;Đột Kích&lt;/color&gt;, kẻ địch nhận 1 tầng hiệu ứng sau: &lt;color=#b72924ff&gt;ATK tăng 10%&lt;/color&gt;, tối đa &lt;color=#b72924ff&gt;10&lt;/color&gt; tầng.
+Mỗi lần &lt;color=#5cc96aff&gt;Phản Đòn thành công&lt;/color&gt; sẽ loại bỏ &lt;color=#5cc96aff&gt;3&lt;/color&gt; tầng.</t>
         </is>
       </c>
     </row>
@@ -6999,7 +6999,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Kẻ địch sẽ &lt;color=#b72924ff&gt;Knockback&lt;/color&gt; và gây một lượng Sát Thương nhất định lên Resonators xung quanh sau khi nhận &lt;color=#b72924ff&gt;20&lt;/color&gt; đòn liên tiếp trong vòng &lt;color=#b72924ff&gt;5s&lt;/color&gt;.</t>
+          <t>Kẻ địch sẽ &lt;color=#b72924ff&gt;Bật Lùi&lt;/color&gt; và gây một lượng Sát Thương nhất định lên các Resonator xung quanh sau khi nhận &lt;color=#b72924ff&gt;20&lt;/color&gt; đòn liên tiếp trong vòng &lt;color=#b72924ff&gt;5 giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -7064,7 +7064,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Kẻ địch &lt;color=#b72924ff&gt;max HP is increased by 20%&lt;/color&gt;. &lt;color=#5cc96aff&gt;Counterattacks&lt;/color&gt;, &lt;color=#5cc96aff&gt;Dodge Counters&lt;/color&gt; và &lt;color=#5cc96aff&gt;Intro Skills&lt;/color&gt; gây &lt;color=#5cc96aff&gt;additional damage&lt;/color&gt; lên kẻ địch.</t>
+          <t>Kẻ địch &lt;color=#b72924ff&gt;tăng 20% HP tối đa&lt;/color&gt;. &lt;color=#5cc96aff&gt;Phản Đòn&lt;/color&gt;, &lt;color=#5cc96aff&gt;Dodge Counter Tránh&lt;/color&gt; và &lt;color=#5cc96aff&gt;Kỹ Năng Khởi Động&lt;/color&gt; gây &lt;color=#5cc96aff&gt;sát thương bổ sung&lt;/color&gt; lên kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -7129,7 +7129,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Kẻ địch &lt;color=#b72924ff&gt;max HP is increased by 40%&lt;/color&gt;. &lt;color=#5cc96aff&gt;Counterattacks&lt;/color&gt;, &lt;color=#5cc96aff&gt;Dodge Counters&lt;/color&gt; và &lt;color=#5cc96aff&gt;Intro Skills&lt;/color&gt; gây &lt;color=#5cc96aff&gt;additional damage&lt;/color&gt; lên kẻ địch.</t>
+          <t>Kẻ địch &lt;color=#b72924ff&gt;tăng 40% HP tối đa&lt;/color&gt;. &lt;color=#5cc96aff&gt;Phản Đòn&lt;/color&gt;, &lt;color=#5cc96aff&gt;Dodge Counter Tránh&lt;/color&gt; và &lt;color=#5cc96aff&gt;Kỹ Năng Khởi Động&lt;/color&gt; gây &lt;color=#5cc96aff&gt;sát thương bổ sung&lt;/color&gt; lên kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -7194,7 +7194,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Kẻ địch &lt;color=#b72924ff&gt;max HP is increased by 100%&lt;/color&gt;. &lt;color=#5cc96aff&gt;Counterattacks&lt;/color&gt;, &lt;color=#5cc96aff&gt;Dodge Counters&lt;/color&gt; và &lt;color=#5cc96aff&gt;Intro Skills&lt;/color&gt; gây &lt;color=#5cc96aff&gt;additional damage&lt;/color&gt; lên kẻ địch.</t>
+          <t>Kẻ địch &lt;color=#b72924ff&gt;tăng 100% HP tối đa&lt;/color&gt;. &lt;color=#5cc96aff&gt;Phản Đòn&lt;/color&gt;, &lt;color=#5cc96aff&gt;Dodge Counter Tránh&lt;/color&gt; và &lt;color=#5cc96aff&gt;Kỹ Năng Khởi Động&lt;/color&gt; gây &lt;color=#5cc96aff&gt;sát thương bổ sung&lt;/color&gt; lên kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>&lt;color=#b72924ff&gt;max HP is reduced to 80%&lt;/color&gt;. Khi Cấp Giao Hưởng đạt từ &lt;color=#5cc96aff&gt;S&lt;/color&gt; trở lên, &lt;color=#5cc96aff&gt;HP will not drop below 1%&lt;/color&gt;.</t>
+          <t>&lt;color=#b72924ff&gt;HP tối đa của Resonator giảm xuống còn 80%&lt;/color&gt;. Khi Cấp Giao Hưởng đạt từ &lt;color=#5cc96aff&gt;S&lt;/color&gt; trở lên, &lt;color=#5cc96aff&gt;HP của Resonator sẽ không giảm dưới 1%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -7324,7 +7324,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>&lt;color=#b72924ff&gt;max HP is reduced to 50%&lt;/color&gt;. Khi Cấp Giao Hưởng đạt từ &lt;color=#5cc96aff&gt;S&lt;/color&gt; trở lên, &lt;color=#5cc96aff&gt;HP will not drop below 1%&lt;/color&gt;.</t>
+          <t>&lt;color=#b72924ff&gt;HP tối đa của Resonator giảm xuống còn 50%&lt;/color&gt;. Khi Cấp Giao Hưởng đạt từ &lt;color=#5cc96aff&gt;S&lt;/color&gt; trở lên, &lt;color=#5cc96aff&gt;HP của Resonator sẽ không giảm dưới 1%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -7389,7 +7389,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>&lt;color=#b72924ff&gt;max HP is reduced to 10%&lt;/color&gt;. Khi Cấp Giao Hưởng đạt từ &lt;color=#5cc96aff&gt;S&lt;/color&gt; trở lên, &lt;color=#5cc96aff&gt;HP will not drop below 1%&lt;/color&gt;.</t>
+          <t>&lt;color=#b72924ff&gt;HP tối đa của Resonator giảm xuống còn 10%&lt;/color&gt;. Khi Cấp Giao Hưởng đạt từ &lt;color=#5cc96aff&gt;S&lt;/color&gt; trở lên, &lt;color=#5cc96aff&gt;HP của Resonator sẽ không giảm dưới 1%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -7455,8 +7455,8 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Khi kẻ địch không chịu sát thương trong &lt;color=#b72924ff&gt;5s&lt;/color&gt;, chúng nhận &lt;color=#b72924ff&gt;3&lt;/color&gt; tầng hiệu ứng sau: Lần sát thương tiếp theo chịu sẽ &lt;color=#b72924ff&gt;reduced by 100%&lt;/color&gt;.
-Khi Resonators không chịu sát thương trong &lt;color=#5cc96aff&gt;5s&lt;/color&gt;, họ nhận &lt;color=#5cc96aff&gt;1&lt;/color&gt; tầng hiệu ứng sau: Lần sát thương tiếp theo chịu sẽ giảm &lt;color=#5cc96aff&gt;100%&lt;/color&gt;.</t>
+          <t>Khi kẻ địch không chịu sát thương trong &lt;color=#b72924ff&gt;5 giây&lt;/color&gt;, chúng nhận &lt;color=#b72924ff&gt;3&lt;/color&gt; tầng hiệu ứng sau: Lần sát thương tiếp theo chịu sẽ &lt;color=#b72924ff&gt;giảm 100%&lt;/color&gt;.
+Khi Resonator không chịu sát thương trong &lt;color=#5cc96aff&gt;5 giây&lt;/color&gt;, họ nhận &lt;color=#5cc96aff&gt;1&lt;/color&gt; tầng hiệu ứng sau: Lần sát thương tiếp theo chịu sẽ giảm &lt;color=#5cc96aff&gt;100%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -7521,7 +7521,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Kẻ địch nhận &lt;color=#b72924ff&gt;shield&lt;/color&gt; tương đương &lt;color=#b72924ff&gt;their Level x300&lt;/color&gt;.</t>
+          <t>Kẻ địch nhận &lt;color=#b72924ff&gt;lá chắn&lt;/color&gt; tương đương &lt;color=#b72924ff&gt;Cấp độ x300&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Kẻ địch nhận &lt;color=#b72924ff&gt;shield&lt;/color&gt; tương đương &lt;color=#b72924ff&gt;their Level x600&lt;/color&gt;.</t>
+          <t>Kẻ địch nhận &lt;color=#b72924ff&gt;lá chắn&lt;/color&gt; tương đương &lt;color=#b72924ff&gt;Cấp độ x600&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -7651,7 +7651,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Cooldown chiêu &lt;color=#b72924ff&gt;Resonator switch Cooldown&lt;/color&gt; tăng lên &lt;color=#b72924ff&gt;3s&lt;/color&gt; (Skill Khởi Động không bị ảnh hưởng).</t>
+          <t>Thời gian hồi chiêu &lt;color=#b72924ff&gt;chuyển đổi Resonator&lt;/color&gt; tăng lên &lt;color=#b72924ff&gt;3 giây&lt;/color&gt; (Kỹ năng Khởi Động không bị ảnh hưởng).</t>
         </is>
       </c>
     </row>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Cooldown chiêu &lt;color=#b72924ff&gt;Resonator switch Cooldown&lt;/color&gt; tăng lên &lt;color=#b72924ff&gt;5s&lt;/color&gt; (Skill Khởi Động không bị ảnh hưởng).</t>
+          <t>Thời gian hồi chiêu &lt;color=#b72924ff&gt;chuyển đổi Resonator&lt;/color&gt; tăng lên &lt;color=#b72924ff&gt;5 giây&lt;/color&gt; (Kỹ năng Khởi Động không bị ảnh hưởng).</t>
         </is>
       </c>
     </row>
@@ -7782,8 +7782,8 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Mỗi khi Resonators thực hiện &lt;color=#b72924ff&gt;Dash&lt;/color&gt;, kẻ địch nhận 1 tầng hiệu ứng sau: &lt;color=#b72924ff&gt;ATK is increased by 10%&lt;/color&gt;, tối đa &lt;color=#b72924ff&gt;10&lt;/color&gt; tầng.
-Mỗi lần &lt;color=#5cc96aff&gt;successful Dodge&lt;/color&gt; sẽ loại bỏ &lt;color=#5cc96aff&gt;3&lt;/color&gt; tầng.</t>
+          <t>Mỗi khi Resonator thực hiện &lt;color=#b72924ff&gt;Đột Kích&lt;/color&gt;, kẻ địch nhận 1 tầng hiệu ứng sau: &lt;color=#b72924ff&gt;ATK tăng 10%&lt;/color&gt;, tối đa &lt;color=#b72924ff&gt;10&lt;/color&gt; tầng.
+Mỗi lần &lt;color=#5cc96aff&gt;Né tránh thành công&lt;/color&gt; sẽ loại bỏ &lt;color=#5cc96aff&gt;3&lt;/color&gt; tầng.</t>
         </is>
       </c>
     </row>
@@ -7848,7 +7848,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Một số kẻ địch sẽ &lt;color=#b72924ff&gt;pull&lt;/color&gt; Resonators về phía chúng sau mỗi &lt;color=#b72924ff&gt;20s&lt;/color&gt;.</t>
+          <t>Một số kẻ địch sẽ &lt;color=#b72924ff&gt;kéo&lt;/color&gt; Resonator về phía chúng sau mỗi &lt;color=#b72924ff&gt;20 giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -7913,7 +7913,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Một số kẻ địch sẽ &lt;color=#b72924ff&gt;pull&lt;/color&gt; Resonators về phía chúng sau mỗi &lt;color=#b72924ff&gt;12s&lt;/color&gt;.</t>
+          <t>Một số kẻ địch sẽ &lt;color=#b72924ff&gt;kéo&lt;/color&gt; Resonator về phía chúng sau mỗi &lt;color=#b72924ff&gt;12 giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Khi ở trong &lt;color=#b72924ff&gt;a certain range&lt;/color&gt; quanh kẻ địch, Resonators sẽ chịu sát thương bằng &lt;color=#b72924ff&gt;1.2% of their max HP&lt;/color&gt; mỗi &lt;color=#b72924ff&gt;0.5s&lt;/color&gt;.</t>
+          <t>Khi ở trong &lt;color=#b72924ff&gt;phạm vi nhất định&lt;/color&gt; quanh kẻ địch, Resonator sẽ chịu sát thương bằng &lt;color=#b72924ff&gt;1.2% HP tối đa&lt;/color&gt; mỗi &lt;color=#b72924ff&gt;0.5 giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Khi ở trong &lt;color=#b72924ff&gt;a certain range&lt;/color&gt; quanh kẻ địch, Resonators sẽ chịu sát thương bằng &lt;color=#b72924ff&gt;2.2% of their max HP&lt;/color&gt; mỗi &lt;color=#b72924ff&gt;0.5s&lt;/color&gt;.</t>
+          <t>Khi ở trong &lt;color=#b72924ff&gt;phạm vi nhất định&lt;/color&gt; quanh kẻ địch, Resonator sẽ chịu sát thương bằng &lt;color=#b72924ff&gt;2.2% HP tối đa&lt;/color&gt; mỗi &lt;color=#b72924ff&gt;0.5 giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Khi ở trong &lt;color=#b72924ff&gt;a certain range&lt;/color&gt; quanh kẻ địch, Resonators sẽ chịu sát thương bằng &lt;color=#b72924ff&gt;3.2% of their max HP&lt;/color&gt; mỗi &lt;color=#b72924ff&gt;0.5s&lt;/color&gt;.</t>
+          <t>Khi ở trong &lt;color=#b72924ff&gt;phạm vi nhất định&lt;/color&gt; quanh kẻ địch, Resonator sẽ chịu sát thương bằng &lt;color=#b72924ff&gt;3.2% HP tối đa&lt;/color&gt; mỗi &lt;color=#b72924ff&gt;0.5 giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -8173,7 +8173,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Kẻ địch chịu &lt;color=#b72924ff&gt;50% less damage&lt;/color&gt; khi &lt;color=#b72924ff&gt;0 Vibration Strength&lt;/color&gt;. &lt;color=#5cc96aff&gt;Coordinated Attacks&lt;/color&gt; khi trúng mục tiêu sẽ tạo sóng xung kích, giảm &lt;color=#5cc96aff&gt;7,5%&lt;/color&gt; Vibration Strength của mục tiêu.</t>
+          <t>Kẻ địch chịu &lt;color=#b72924ff&gt;ít hơn 50% sát thương&lt;/color&gt; khi &lt;color=#b72924ff&gt;Sức Rung còn trên 0&lt;/color&gt;. &lt;color=#5cc96aff&gt;Đòn Phối Hợp&lt;/color&gt; khi trúng mục tiêu sẽ tạo sóng xung kích, giảm &lt;color=#5cc96aff&gt;7,5%&lt;/color&gt; Sức Rung của mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -8238,7 +8238,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Kẻ địch chịu &lt;color=#b72924ff&gt;70% less damage&lt;/color&gt; khi &lt;color=#b72924ff&gt;0 Vibration Strength&lt;/color&gt;. &lt;color=#5cc96aff&gt;Coordinated Attacks&lt;/color&gt; khi trúng mục tiêu sẽ tạo sóng xung kích, giảm &lt;color=#5cc96aff&gt;7,5%&lt;/color&gt; Vibration Strength của mục tiêu.</t>
+          <t>Kẻ địch chịu &lt;color=#b72924ff&gt;ít hơn 70% sát thương&lt;/color&gt; khi &lt;color=#b72924ff&gt;Sức Rung còn trên 0&lt;/color&gt;. &lt;color=#5cc96aff&gt;Đòn Phối Hợp&lt;/color&gt; khi trúng mục tiêu sẽ tạo sóng xung kích, giảm &lt;color=#5cc96aff&gt;7,5%&lt;/color&gt; Sức Rung của mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Kẻ địch chịu &lt;color=#b72924ff&gt;90% less damage&lt;/color&gt; khi &lt;color=#b72924ff&gt;0 Vibration Strength&lt;/color&gt;. &lt;color=#5cc96aff&gt;Coordinated Attacks&lt;/color&gt; khi trúng mục tiêu sẽ tạo sóng xung kích, giảm &lt;color=#5cc96aff&gt;7,5%&lt;/color&gt; Vibration Strength của mục tiêu.</t>
+          <t>Kẻ địch chịu &lt;color=#b72924ff&gt;ít hơn 90% sát thương&lt;/color&gt; khi &lt;color=#b72924ff&gt;Sức Rung còn trên 0&lt;/color&gt;. &lt;color=#5cc96aff&gt;Đòn Phối Hợp&lt;/color&gt; khi trúng mục tiêu sẽ tạo sóng xung kích, giảm &lt;color=#5cc96aff&gt;7,5%&lt;/color&gt; Sức Rung của mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Khi &lt;color=#b72924ff&gt;When about to recover from being Immobilized&lt;/color&gt;, kẻ địch sẽ gây sát thương bằng &lt;color=#b72924ff&gt;300% Tấn Công&lt;/color&gt; lên Resonators xung quanh.</t>
+          <t>Khi &lt;color=#b72924ff&gt;sắp hồi phục khỏi trạng thái Bất Động&lt;/color&gt;, kẻ địch sẽ gây sát thương bằng &lt;color=#b72924ff&gt;300% ATK&lt;/color&gt; lên các Resonator xung quanh.</t>
         </is>
       </c>
     </row>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Khi &lt;color=#b72924ff&gt;Upon hitting an enemy&lt;/color&gt;, &lt;color=#b72924ff&gt;a lightning strike is summoned&lt;/color&gt; vị trí trúng đòn, gây sát thương bằng &lt;color=#b72924ff&gt;10% of the Resonator's max HP&lt;/color&gt; của Resonators. Hiệu ứng này có thể kích hoạt mỗi &lt;color=#b72924ff&gt;5s&lt;/color&gt; một lần.</t>
+          <t>Khi &lt;color=#b72924ff&gt;đánh trúng kẻ địch&lt;/color&gt;, &lt;color=#b72924ff&gt;một tia sét sẽ giáng xuống&lt;/color&gt; vị trí trúng đòn, gây sát thương bằng &lt;color=#b72924ff&gt;10% HP tối đa&lt;/color&gt; của Resonator. Hiệu ứng này có thể kích hoạt mỗi &lt;color=#b72924ff&gt;5 giây&lt;/color&gt; một lần.</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Khi &lt;color=#b72924ff&gt;Upon hitting an enemy&lt;/color&gt;, &lt;color=#b72924ff&gt;a lightning strike is summoned&lt;/color&gt; vị trí trúng đòn, gây sát thương bằng &lt;color=#b72924ff&gt;20% of the Resonator's max HP&lt;/color&gt; của Resonators. Hiệu ứng này có thể kích hoạt mỗi &lt;color=#b72924ff&gt;5s&lt;/color&gt; một lần.</t>
+          <t>Khi &lt;color=#b72924ff&gt;đánh trúng kẻ địch&lt;/color&gt;, &lt;color=#b72924ff&gt;một tia sét sẽ giáng xuống&lt;/color&gt; vị trí trúng đòn, gây sát thương bằng &lt;color=#b72924ff&gt;20% HP tối đa&lt;/color&gt; của Resonator. Hiệu ứng này có thể kích hoạt mỗi &lt;color=#b72924ff&gt;5 giây&lt;/color&gt; một lần.</t>
         </is>
       </c>
     </row>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Khi &lt;color=#b72924ff&gt;Vibration Strength is above 0&lt;/color&gt;, kẻ địch sẽ hồi phục &lt;color=#b72924ff&gt;3% of their max HP&lt;/color&gt; mỗi khi gây sát thương. Hiệu ứng này có thể kích hoạt mỗi &lt;color=#b72924ff&gt;10s&lt;/color&gt; một lần.</t>
+          <t>Khi &lt;color=#b72924ff&gt;Sức Rung lớn hơn 0&lt;/color&gt;, kẻ địch sẽ hồi phục &lt;color=#b72924ff&gt;3% HP tối đa&lt;/color&gt; mỗi khi gây sát thương. Hiệu ứng này có thể kích hoạt mỗi &lt;color=#b72924ff&gt;10 giây&lt;/color&gt; một lần.</t>
         </is>
       </c>
     </row>
@@ -8628,7 +8628,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Khi &lt;color=#b72924ff&gt;Vibration Strength is above 0&lt;/color&gt;, kẻ địch sẽ hồi phục &lt;color=#b72924ff&gt;6% of their max HP&lt;/color&gt; mỗi khi gây sát thương. Hiệu ứng này có thể kích hoạt mỗi &lt;color=#b72924ff&gt;10s&lt;/color&gt; một lần.</t>
+          <t>Khi &lt;color=#b72924ff&gt;Sức Rung lớn hơn 0&lt;/color&gt;, kẻ địch sẽ hồi phục &lt;color=#b72924ff&gt;6% HP tối đa&lt;/color&gt; mỗi khi gây sát thương. Hiệu ứng này có thể kích hoạt mỗi &lt;color=#b72924ff&gt;10 giây&lt;/color&gt; một lần.</t>
         </is>
       </c>
     </row>
@@ -8694,8 +8694,8 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Mỗi khi Resonators thực hiện &lt;color=#b72924ff&gt;Dash&lt;/color&gt;, kẻ địch nhận 1 tầng hiệu ứng sau: &lt;color=#b72924ff&gt;ATK is increased by 10%&lt;/color&gt;, tối đa &lt;color=#b72924ff&gt;10&lt;/color&gt; tầng.
-Mỗi lần &lt;color=#5cc96aff&gt;successful Counterattack&lt;/color&gt; sẽ loại bỏ &lt;color=#5cc96aff&gt;3&lt;/color&gt; tầng.</t>
+          <t>Mỗi khi Resonator thực hiện &lt;color=#b72924ff&gt;Đột Kích&lt;/color&gt;, kẻ địch nhận 1 tầng hiệu ứng sau: &lt;color=#b72924ff&gt;ATK tăng 10%&lt;/color&gt;, tối đa &lt;color=#b72924ff&gt;10&lt;/color&gt; tầng.
+Mỗi lần &lt;color=#5cc96aff&gt;Phản Đòn thành công&lt;/color&gt; sẽ loại bỏ &lt;color=#5cc96aff&gt;3&lt;/color&gt; tầng.</t>
         </is>
       </c>
     </row>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Kẻ địch &lt;color=#b72924ff&gt;DEF is increased by 150%&lt;/color&gt;. &lt;color=#5cc96aff&gt;While in trên không&lt;/color&gt;, gây thêm sát thương bằng &lt;color=#5cc96aff&gt;1%&lt;/color&gt; HP tối đa của mục tiêu. Hiệu ứng này có thể kích hoạt mỗi &lt;color=#5cc96aff&gt;1s&lt;/color&gt;.</t>
+          <t>Kẻ địch &lt;color=#b72924ff&gt;Phòng Ngự tăng 150%&lt;/color&gt;. &lt;color=#5cc96aff&gt;Khi Resonator ở trên không&lt;/color&gt;, gây thêm sát thương bằng &lt;color=#5cc96aff&gt;1%&lt;/color&gt; HP tối đa của mục tiêu. Hiệu ứng này có thể kích hoạt mỗi &lt;color=#5cc96aff&gt;1 giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -8825,7 +8825,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Kẻ địch &lt;color=#b72924ff&gt;DEF is increased by 300%&lt;/color&gt;. &lt;color=#5cc96aff&gt;While in trên không&lt;/color&gt;, gây thêm sát thương bằng &lt;color=#5cc96aff&gt;1%&lt;/color&gt; HP tối đa của mục tiêu. Hiệu ứng này có thể kích hoạt mỗi &lt;color=#5cc96aff&gt;1s&lt;/color&gt;.</t>
+          <t>Kẻ địch &lt;color=#b72924ff&gt;Phòng Ngự tăng 300%&lt;/color&gt;. &lt;color=#5cc96aff&gt;Khi Resonator ở trên không&lt;/color&gt;, gây thêm sát thương bằng &lt;color=#5cc96aff&gt;1%&lt;/color&gt; HP tối đa của mục tiêu. Hiệu ứng này có thể kích hoạt mỗi &lt;color=#5cc96aff&gt;1 giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -8890,7 +8890,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Các Resonators đang hoạt động sẽ nhận &lt;color=#b72924ff&gt;1&lt;/color&gt; tầng &lt;color=#b72924ff&gt;Glacio Chafe&lt;/color&gt; mỗi &lt;color=#b72924ff&gt;2s&lt;/color&gt; khi &lt;color=#b72924ff&gt;on the ground&lt;/color&gt; và &lt;color=#b72924ff&gt;DEF is reduced to 0&lt;/color&gt; khi bị Đông Cứng. Tất cả tầng &lt;color=#5cc96aff&gt;Glacio Chafe&lt;/color&gt; sẽ bị xóa khi ở &lt;color=#5cc96aff&gt;trên không&lt;/color&gt;.</t>
+          <t>Các Resonator đang hoạt động sẽ nhận &lt;color=#b72924ff&gt;1&lt;/color&gt; tầng &lt;color=#b72924ff&gt;Glacio Chafe&lt;/color&gt; mỗi &lt;color=#b72924ff&gt;2 giây&lt;/color&gt; khi &lt;color=#b72924ff&gt;đứng trên mặt đất&lt;/color&gt; và &lt;color=#b72924ff&gt;DEF giảm về 0&lt;/color&gt; khi bị Đông Cứng. Tất cả tầng &lt;color=#5cc96aff&gt;Glacio Chafe&lt;/color&gt; sẽ bị xóa khi ở &lt;color=#5cc96aff&gt;trên không&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8955,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Các Resonators đang hoạt động sẽ nhận &lt;color=#b72924ff&gt;1&lt;/color&gt; tầng &lt;color=#b72924ff&gt;Glacio Chafe&lt;/color&gt; mỗi &lt;color=#b72924ff&gt;1s&lt;/color&gt; khi &lt;color=#b72924ff&gt;on the ground&lt;/color&gt; và &lt;color=#b72924ff&gt;DEF is reduced to 0&lt;/color&gt; khi bị Đông Cứng. Tất cả tầng &lt;color=#5cc96aff&gt;Glacio Chafe&lt;/color&gt; sẽ bị xóa khi ở &lt;color=#5cc96aff&gt;trên không&lt;/color&gt;.</t>
+          <t>Các Resonator đang hoạt động sẽ nhận &lt;color=#b72924ff&gt;1&lt;/color&gt; tầng &lt;color=#b72924ff&gt;Glacio Chafe&lt;/color&gt; mỗi &lt;color=#b72924ff&gt;1 giây&lt;/color&gt; khi &lt;color=#b72924ff&gt;đứng trên mặt đất&lt;/color&gt; và &lt;color=#b72924ff&gt;DEF giảm về 0&lt;/color&gt; khi bị Đông Cứng. Tất cả tầng &lt;color=#5cc96aff&gt;Glacio Chafe&lt;/color&gt; sẽ bị xóa khi ở &lt;color=#5cc96aff&gt;trên không&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9020,7 +9020,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Các Resonators đang kích hoạt nhận &lt;color=#b72924ff&gt;1&lt;/color&gt; lớp &lt;color=#b72924ff&gt;Glacio Chafe&lt;/color&gt; sau mỗi &lt;color=#b72924ff&gt;0.6s&lt;/color&gt; &lt;color=#b72924ff&gt;on the ground&lt;/color&gt; và &lt;color=#b72924ff&gt;DEF is reduced to 0&lt;/color&gt; khi bị Đông cứng. Tất cả các lớp &lt;color=#5cc96aff&gt;Glacio Chafe&lt;/color&gt; sẽ bị loại bỏ khi ở &lt;color=#5cc96aff&gt;trên không&lt;/color&gt;</t>
+          <t>Các Resonator đang kích hoạt nhận &lt;color=#b72924ff&gt;1&lt;/color&gt; lớp &lt;color=#b72924ff&gt;Glacio Chafe&lt;/color&gt; sau mỗi &lt;color=#b72924ff&gt;0.6 giây&lt;/color&gt; &lt;color=#b72924ff&gt;trên mặt đất&lt;/color&gt; và &lt;color=#b72924ff&gt;Phòng Ngự giảm về 0&lt;/color&gt; khi bị Đông cứng. Tất cả các lớp &lt;color=#5cc96aff&gt;Glacio Chafe&lt;/color&gt; sẽ bị loại bỏ khi ở &lt;color=#5cc96aff&gt;trên không.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -9085,7 +9085,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Kẻ địch nhận hiệu ứng sau: &lt;color=#b72924ff&gt;Tất cả nearby enemies are empowered&lt;/color&gt;. &lt;color=#b72924ff&gt;ATK is increased by 10%&lt;/color&gt;. Hiệu ứng có thể chồng chất.</t>
+          <t>Kẻ địch nhận hiệu ứng sau: &lt;color=#b72924ff&gt;Tất cả kẻ địch gần đó được tăng cường&lt;/color&gt;. &lt;color=#b72924ff&gt;ATK của chúng tăng 10%&lt;/color&gt;. Hiệu ứng có thể chồng chất.</t>
         </is>
       </c>
     </row>
@@ -9150,7 +9150,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Kẻ địch nhận hiệu ứng sau: &lt;color=#b72924ff&gt;Tất cả nearby enemies are empowered&lt;/color&gt;. &lt;color=#b72924ff&gt;ATK is increased by 20%&lt;/color&gt;. Hiệu ứng có thể chồng chất.</t>
+          <t>Kẻ địch nhận hiệu ứng sau: &lt;color=#b72924ff&gt;Tất cả kẻ địch gần đó được tăng cường&lt;/color&gt;. &lt;color=#b72924ff&gt;ATK của chúng tăng 20%&lt;/color&gt;. Hiệu ứng có thể chồng chất.</t>
         </is>
       </c>
     </row>
@@ -9215,7 +9215,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Kẻ địch nhận hiệu ứng sau: &lt;color=#b72924ff&gt;Tất cả nearby enemies are empowered&lt;/color&gt;. &lt;color=#b72924ff&gt;ATK is increased by 30%&lt;/color&gt;. Hiệu ứng có thể chồng chất.</t>
+          <t>Kẻ địch nhận hiệu ứng sau: &lt;color=#b72924ff&gt;Tất cả kẻ địch gần đó được tăng cường&lt;/color&gt;. &lt;color=#b72924ff&gt;ATK của chúng tăng 30%&lt;/color&gt;. Hiệu ứng có thể chồng chất.</t>
         </is>
       </c>
     </row>
@@ -9280,7 +9280,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Kẻ địch trở nên &lt;color=#b72924ff&gt;more aggressive&lt;/color&gt;.</t>
+          <t>Kẻ địch trở nên &lt;color=#b72924ff&gt;hung hãn hơn&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9345,7 +9345,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Mỗi đợt kẻ địch xuất hiện sẽ tạo ra một lượng vừa phải &lt;color=#b72924ff&gt;Ice Chrysalise&lt;/color&gt;, gây hiệu ứng &lt;color=#b72924ff&gt;Glacio Chafe&lt;/color&gt; lên Resonators gần đó.</t>
+          <t>Mỗi đợt kẻ địch xuất hiện sẽ tạo ra một lượng vừa phải &lt;color=#b72924ff&gt;Ice Chrysalise&lt;/color&gt;, gây hiệu ứng &lt;color=#b72924ff&gt;Glacio Chafe&lt;/color&gt; lên các Resonator gần đó.</t>
         </is>
       </c>
     </row>
@@ -9410,7 +9410,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Mỗi đợt kẻ địch xuất hiện sẽ tạo ra một lượng lớn &lt;color=#b72924ff&gt;Ice Chrysalise&lt;/color&gt;, gây hiệu ứng &lt;color=#b72924ff&gt;Glacio Chafe&lt;/color&gt; lên Resonators gần đó.</t>
+          <t>Mỗi đợt kẻ địch xuất hiện sẽ tạo ra một lượng lớn &lt;color=#b72924ff&gt;Ice Chrysalise&lt;/color&gt;, gây hiệu ứng &lt;color=#b72924ff&gt;Glacio Chafe&lt;/color&gt; lên các Resonator gần đó.</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Khi &lt;color=#b72924ff&gt;interruption&lt;/color&gt;, kẻ địch &lt;color=#b72924ff&gt;above 70% HP&lt;/color&gt;.</t>
+          <t>Khi &lt;color=#b72924ff&gt;HP trên 70%&lt;/color&gt;, kẻ địch &lt;color=#b72924ff&gt;miễn nhiễm với gián đoạn&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9540,7 +9540,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Khi &lt;color=#b72924ff&gt;interruption&lt;/color&gt;, kẻ địch &lt;color=#b72924ff&gt;above 50% HP&lt;/color&gt;.</t>
+          <t>Khi &lt;color=#b72924ff&gt;HP trên 50%&lt;/color&gt;, kẻ địch &lt;color=#b72924ff&gt;miễn nhiễm với gián đoạn&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9605,7 +9605,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Một số kẻ địch sẽ &lt;color=#b72924ff&gt;summon reinforcements&lt;/color&gt; khi HP của chúng giảm xuống dưới &lt;color=#b72924ff&gt;50%&lt;/color&gt;.</t>
+          <t>Một số kẻ địch sẽ &lt;color=#b72924ff&gt;triệu hồi tiếp viện&lt;/color&gt; khi HP của chúng giảm xuống dưới &lt;color=#b72924ff&gt;50%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9670,7 +9670,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Kẻ địch &lt;color=#b72924ff&gt;ATK is increased by 15%&lt;/color&gt;.</t>
+          <t>Kẻ địch &lt;color=#b72924ff&gt;ATK tăng 15%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9735,7 +9735,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Kẻ địch &lt;color=#b72924ff&gt;ATK is increased by 30%&lt;/color&gt;.</t>
+          <t>Kẻ địch &lt;color=#b72924ff&gt;ATK tăng 30%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9800,7 +9800,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Kẻ địch &lt;color=#b72924ff&gt;max HP is increased by 30%&lt;/color&gt;.</t>
+          <t>Kẻ địch &lt;color=#b72924ff&gt;tăng 30% HP tối đa&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9865,7 +9865,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Kẻ địch &lt;color=#b72924ff&gt;max HP is increased by 50%&lt;/color&gt;.</t>
+          <t>Kẻ địch &lt;color=#b72924ff&gt;tăng 50% HP tối đa&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>&lt;color=#b72924ff&gt;max STA is reduced by 20%&lt;/color&gt;.</t>
+          <t>&lt;color=#b72924ff&gt;STA tối đa của Resonator giảm 20%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9995,7 +9995,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>&lt;color=#b72924ff&gt;max STA is reduced by 60%&lt;/color&gt;.</t>
+          <t>&lt;color=#b72924ff&gt;STA tối đa của Resonator giảm 60%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>&lt;color=#b72924ff&gt;Mức Stress chưa đạt yêu cầu&lt;/color&gt;</t>
+          <t>&lt;color=#b72924ff&gt;Mức Độ Căng Thẳng chưa đạt yêu cầu&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -10125,7 +10125,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Khi Resonators gây Aero DMG lên kẻ địch đang bị Aero Erosion, Crit. DMG của họ sẽ tăng thêm 80%.</t>
+          <t>Khi Resonator gây Sát Thương Aero lên kẻ địch đang bị Aero Erosion, Crit. DMG của họ sẽ tăng thêm 80%.</t>
         </is>
       </c>
     </row>
@@ -10190,7 +10190,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Hiệu Quả Healing của Resonators tăng 100%. Khi được hồi phục, Resonators đang hoạt động nhận ít hơn 20% sát thương trong 8 giây.</t>
+          <t>Hiệu Quả Hồi Phục của Resonator tăng 100%. Khi được hồi phục, Resonator đang hoạt động nhận ít hơn 20% sát thương trong 8 giây.</t>
         </is>
       </c>
     </row>
@@ -10255,7 +10255,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Khi Resonators gây Spectro DMG lên kẻ địch đang bị Spectro Frazzle, Spectro RES của kẻ địch sẽ giảm 10% trong 10 giây, có thể chồng chất tối đa 5 lần.</t>
+          <t>Khi Resonator gây Sát Thương Spectro lên kẻ địch đang bị Spectro Frazzle, Kháng Spectro của kẻ địch sẽ giảm 10% trong 10 giây, có thể chồng chất tối đa 5 lần.</t>
         </is>
       </c>
     </row>
@@ -10320,7 +10320,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Resonators chịu ít hơn 50% sát thương và tăng khả năng kháng gián đoạn khi có khiên. Kích hoạt Kỹ Năng Giới Thiệu sẽ tạo khiên tương đương 15% HP tối đa của Resonators đang hoạt động, kéo dài 10 giây.</t>
+          <t>Resonator chịu ít hơn 50% DMG và tăng khả năng kháng gián đoạn khi có khiên. Kích hoạt Kỹ Năng Giới Thiệu sẽ tạo khiên tương đương 15% HP tối đa của Resonator đang hoạt động, kéo dài 10 giây.</t>
         </is>
       </c>
     </row>
@@ -10385,7 +10385,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Khi ở trên không, Tấn Công của Resonators tăng 100%. Hiệu ứng này sẽ mất sau 2 giây hạ cánh.</t>
+          <t>Khi ở trên không, ATK của Resonator tăng 100%. Hiệu ứng này sẽ mất sau 2 giây hạ cánh.</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Liberation phục hồi 25% HP tối đa cho tất cả Resonators trong đội. Hiệu ứng này có thể kích hoạt mỗi 12 giây một lần cho mỗi Resonators.</t>
+          <t>Kích hoạt Resonance Liberation phục hồi 25% HP tối đa cho tất cả Resonator trong đội. Hiệu ứng này có thể kích hoạt mỗi 12 giây một lần cho mỗi Resonator.</t>
         </is>
       </c>
     </row>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Resonators chịu ít hơn 60% sát thương khi HP trên 50%.</t>
+          <t>Resonator chịu ít hơn 60% DMG khi HP trên 50%.</t>
         </is>
       </c>
     </row>
@@ -10645,7 +10645,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Tiêu hao &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/ActivityBabelTower/T_BabelIconStar.T_BabelIconStar/&gt;{0} để hồi sinh Resonators và nhận hiệu ứng tăng cường.</t>
+          <t>Tiêu hao &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/ActivityBabelTower/T_BabelIconStar.T_BabelIconStar/&gt;{0} để hồi sinh Resonator và nhận hiệu ứng tăng cường.</t>
         </is>
       </c>
     </row>
@@ -10710,7 +10710,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Hiệu Quả Healing của Resonators tăng 100%. Khi được hồi phục, Resonators đang hoạt động nhận ít hơn 20% sát thương trong 8 giây.</t>
+          <t>Hiệu Quả Hồi Phục của Resonator tăng 100%. Khi được hồi phục, Resonator đang hoạt động nhận ít hơn 20% sát thương trong 8 giây.</t>
         </is>
       </c>
     </row>
@@ -10840,7 +10840,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Mỗi 15 đòn Basic Attack của Resonators chủ động gây sát thương, Attack của tất cả Resonators tăng 20% trong 5 giây, có thể chồng chất tối đa 4 lần.</t>
+          <t>Mỗi 15 đòn Basic Attack của Resonator chủ động gây DMG, ATK của tất cả Resonator tăng 20% trong 5 giây, có thể chồng chất tối đa 4 lần.</t>
         </is>
       </c>
     </row>
@@ -10970,7 +10970,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Gây sát thương lên kẻ địch bị Aero Erosion và Spectro Frazzle sẽ tăng Tấn Công của Resonator lên 15% trong 5 giây, tối đa 5 tầng.</t>
+          <t>Gây sát thương lên kẻ địch bị Aero Erosion và Spectro Frazzle sẽ tăng ATK của Resonator lên 15% trong 5 giây, tối đa 5 tầng.</t>
         </is>
       </c>
     </row>
@@ -11035,7 +11035,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Resonators chịu ít hơn 35% sát thương và tăng khả năng kháng gián đoạn khi có khiên. Kích hoạt Kỹ Năng Giới Thiệu sẽ tạo khiên tương đương 10% HP tối đa của Resonators đang hoạt động, kéo dài 10 giây.</t>
+          <t>Resonator chịu ít hơn 35% sát thương và tăng khả năng kháng gián đoạn khi có khiên. Kích hoạt Kỹ Năng Giới Thiệu sẽ tạo khiên tương đương 10% HP tối đa của Resonator đang hoạt động, kéo dài 10 giây.</t>
         </is>
       </c>
     </row>
@@ -11100,7 +11100,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Resonators chịu ít hơn 50% sát thương khi HP trên 50%.</t>
+          <t>Resonator chịu ít hơn 50% sát thương khi HP trên 50%.</t>
         </is>
       </c>
     </row>
@@ -11230,7 +11230,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Hồi sinh tất cả Resonators bị đánh gục, phục hồi 100% HP, sau đó tăng 20% Tấn Công và Resonance Energy tối đa cho họ trong 30 giây. Hiệu ứng có thể chồng chất.</t>
+          <t>Hồi sinh tất cả Resonator bị đánh gục, phục hồi 100% HP, sau đó tăng 20% ATK và Resonance Energy tối đa cho họ trong 30 giây. Hiệu ứng có thể chồng chất.</t>
         </is>
       </c>
     </row>
@@ -11301,7 +11301,7 @@
           <t>Chiếc dù của Cantarella.
 Phần mái tròn của nó giống như một con sứa mềm mại, mũm mĩm với những xúc tu dài duyên dáng, trôi lơ lửng trong không khí. Nan dù được chế tác từ san hô biển sâu, uốn lượn tinh xảo thành những đường cong hoàn hảo, lấp lánh ánh sáng dịu dàng, vừa đẹp đẽ vừa kiên cường. Ở cán dù, một viên ngọc sapphire được gắn vào, biểu tượng cho quyền uy bất di bất dịch của người đứng đầu gia tộc.
 Bạo lực chưa bao giờ là lựa chọn đầu tiên của Cantarella, nhưng khi buộc phải tự vệ, cô chỉ cần xoay chiếc dù, và trong nháy mắt, mái dù tỏa ra ánh sáng rực rỡ. Từ đó, một đàn sứa huyền ảo hiện ra, trôi dạt vào một biển ảo ảnh đầy mê hoặc.
-Kéo kẻ thù vào vùng biển mộng mị nhưng đầy hiểm nguy ấy chính là tuyệt kỹ của Cantarella. Like chủ nhân của nó, chiếc dù có vẻ mềm mại, uyển chuyển, nhưng khi cần, nó luôn bất khả xâm phạm.</t>
+Kéo kẻ thù vào vùng biển mộng mị nhưng đầy hiểm nguy ấy chính là tuyệt kỹ của Cantarella. Giống như chủ nhân của nó, chiếc dù có vẻ mềm mại, uyển chuyển, nhưng khi cần, nó luôn bất khả xâm phạm.</t>
         </is>
       </c>
     </row>
@@ -11366,7 +11366,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Tiêu diệt &lt;color=#ffb04a&gt;target&lt;/color&gt; sẽ kích hoạt vụ nổ, gây 600% Electro DMG lên các mục tiêu xung quanh. Hồi chiêu: 3 giây.</t>
+          <t>Tiêu diệt &lt;color=#ffb04a&gt;mục tiêu&lt;/color&gt; sẽ kích hoạt vụ nổ, gây 600% DMG Electro lên các mục tiêu xung quanh. Hồi chiêu: 3 giây.</t>
         </is>
       </c>
     </row>
@@ -11431,7 +11431,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Mỗi lần &lt;color=#ffb04a&gt;defeating&lt;/color&gt; mục tiêu sẽ hồi 5% Concerto Energy và 10% Resonance Energy.</t>
+          <t>Mỗi lần &lt;color=#ffb04a&gt;hạ gục&lt;/color&gt; mục tiêu sẽ hồi 5% Concerto Energy và 10% Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -11496,7 +11496,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Đạn kỹ năng</t>
+          <t>Đạn Kỹ Năng</t>
         </is>
       </c>
     </row>
@@ -11561,7 +11561,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Tầm kỹ năng</t>
+          <t>Phạm Vi Kỹ Năng</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Thời gian kỹ năng</t>
+          <t>Thời gian Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -11691,7 +11691,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Đạn kỹ năng</t>
+          <t>Đạn Kỹ Năng</t>
         </is>
       </c>
     </row>
@@ -11756,7 +11756,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Tầm kỹ năng</t>
+          <t>Phạm Vi Kỹ Năng</t>
         </is>
       </c>
     </row>
@@ -11821,7 +11821,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Thời gian kỹ năng</t>
+          <t>Thời gian Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Trí tưởng tượng không có giới hạn. Nếu không kiểm soát, những sự cố như thế này sẽ ngày càng tăng. Đối với Resonators, xử lý chúng không phải là vấn đề lớn, nhưng với người dân thường, điều này đủ để gây hoảng loạn khắp thành phố. 
+          <t>Trí tưởng tượng không có giới hạn. Nếu không kiểm soát, những sự cố như thế này sẽ ngày càng tăng. Đối với Resonator, xử lý chúng không phải là vấn đề lớn, nhưng với người dân thường, điều này đủ để gây hoảng loạn khắp thành phố. 
 Tìm ra kẻ đứng sau mọi chuyện mới là ưu tiên hàng đầu của chúng ta...</t>
         </is>
       </c>
@@ -12090,10 +12090,10 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Kẻ địch Cấp Elite gây sát thương mỗi giây bằng 2% HP tối đa của mục tiêu lên các mục tiêu lân cận. Hiệu ứng này không thể chồng chất.
-Cooldown sinh: 10 giây (Chơi đơn &amp; Đồng đội)
+          <t>Kẻ địch Cấp Tinh Anh gây DMG mỗi giây bằng 2% HP tối đa của mục tiêu lên các mục tiêu lân cận. Hiệu ứng này không thể chồng chất.
+Thời gian hồi sinh: 10 giây (Chơi đơn &amp; Đồng đội)
 Lượt hồi sinh chung: 9
-&lt;color=#aa9b6a&gt;Trial Resonators will be available in Solo mode.&lt;/color&gt;</t>
+&lt;color=#aa9b6a&gt;Resonator thử nghiệm sẽ xuất hiện trong chế độ Chơi đơn.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -12163,10 +12163,10 @@
       <c r="M176" t="inlineStr">
         <is>
           <t>- Khi gây sát thương lên mục tiêu, kẻ địch sẽ áp dụng 1 tầng Frazzle Quang Phổ, kích hoạt mỗi 3 giây.
-- Nếu không bị tấn công trong 5 giây, kẻ địch hạng Common sẽ hồi phục 5% HP tối đa sau mỗi 2 giây.
-Cooldown sinh: 10 giây (Chơi đơn &amp; Đồng đội)
+- Nếu không bị tấn công trong 5 giây, kẻ địch hạng Thường sẽ hồi phục 5% HP tối đa sau mỗi 2 giây.
+Thời gian hồi sinh: 10 giây (Chơi đơn &amp; Đồng đội)
 Lượt hồi sinh chung: 6
-&lt;color=#aa9b6a&gt;Trial Resonators will be available in Solo mode.&lt;/color&gt;</t>
+&lt;color=#aa9b6a&gt;Resonator thử nghiệm sẽ khả dụng trong chế độ Chơi đơn.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -12237,9 +12237,9 @@
         <is>
           <t>- Khi gây sát thương lên mục tiêu, kẻ địch sẽ áp dụng 1 tầng Chafe Băng Giá, kích hoạt mỗi 3 giây.
 - Kẻ địch hạng Elite có hiệu ứng sau: Phòng Ngự của các đơn vị đồng minh gần đó tăng 60%.
-Cooldown sinh: 10 giây (Chơi đơn &amp; Đồng đội)
+Thời gian hồi sinh: 10 giây (Chơi đơn &amp; Đồng đội)
 Lượt hồi sinh chung: 6
-&lt;color=#aa9b6a&gt;Trial Resonators will be available in Solo mode.&lt;/color&gt;</t>
+&lt;color=#aa9b6a&gt;Resonator thử nghiệm sẽ khả dụng trong chế độ Chơi đơn.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -12308,7 +12308,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Kẻ địch gây 1 lớp Erosion Gió khi tấn công mục tiêu, kích hoạt mỗi 3 giây.</t>
+          <t>Kẻ địch gây 1 lớp Aero Erosion khi tấn công mục tiêu, kích hoạt mỗi 3 giây.</t>
         </is>
       </c>
     </row>
@@ -12515,8 +12515,8 @@
       <c r="M181" t="inlineStr">
         <is>
           <t>- Khi gây sát thương lên mục tiêu, kẻ địch sẽ áp dụng 1 tầng Frazzle Quang Phổ, kích hoạt mỗi 3 giây.
-- Nếu không bị trúng đòn trong 5 giây, kẻ địch hạng Common sẽ hồi phục 5% HP tối đa sau mỗi 2 giây.
-Cooldown sinh: 10 giây (Chơi đơn &amp; Đồng đội)
+- Nếu không bị trúng đòn trong 5 giây, kẻ địch hạng Thường sẽ hồi phục 5% HP tối đa sau mỗi 2 giây.
+Thời gian hồi sinh: 10 giây (Chơi đơn &amp; Đồng đội)
 Lượt hồi sinh chung: 4</t>
         </is>
       </c>
@@ -12587,7 +12587,7 @@
         <is>
           <t>- Khi gây sát thương lên mục tiêu, kẻ địch sẽ áp dụng 1 tầng Chafe Băng Giá, kích hoạt mỗi 3 giây.
 - Kẻ địch hạng Elite có hiệu ứng sau: Phòng Ngự của các đơn vị đồng minh gần đó tăng 60%.
-Cooldown sinh: 10 giây (Chơi đơn &amp; Đồng đội)
+Thời gian hồi sinh: 10 giây (Chơi đơn &amp; Đồng đội)
 Lượt hồi sinh chung: 4</t>
         </is>
       </c>
@@ -12656,7 +12656,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Kẻ địch gây 1 lớp Erosion Gió khi tấn công mục tiêu, kích hoạt mỗi 3 giây.</t>
+          <t>Kẻ địch gây 1 lớp Aero Erosion khi tấn công mục tiêu, kích hoạt mỗi 3 giây.</t>
         </is>
       </c>
     </row>
@@ -12859,8 +12859,8 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Kẻ địch Cấp Elite gây sát thương mỗi giây bằng 2% HP tối đa của mục tiêu lên các mục tiêu lân cận. Hiệu ứng này không thể chồng chất.
-Cooldown sinh: 10 giây (Chơi đơn &amp; Đồng đội)
+          <t>Kẻ địch Cấp Tinh Anh gây DMG mỗi giây bằng 2% HP tối đa của mục tiêu lên các mục tiêu lân cận. Hiệu ứng này không thể chồng chất.
+Thời gian hồi sinh: 10 giây (Chơi đơn &amp; Đồng đội)
 Lượt hồi sinh chung: 9</t>
         </is>
       </c>
@@ -12930,8 +12930,8 @@
       <c r="M187" t="inlineStr">
         <is>
           <t>- Khi gây sát thương lên mục tiêu, kẻ địch sẽ áp dụng 1 tầng Frazzle Quang Phổ, kích hoạt mỗi 3 giây.
-- Nếu không bị trúng đòn trong 5 giây, kẻ địch hạng Common sẽ hồi phục 5% HP tối đa sau mỗi 2 giây.
-Cooldown sinh: 10 giây (Chơi đơn &amp; Đồng đội)
+- Nếu không bị trúng đòn trong 5 giây, kẻ địch hạng Thường sẽ hồi phục 5% HP tối đa sau mỗi 2 giây.
+Thời gian hồi sinh: 10 giây (Chơi đơn &amp; Đồng đội)
 Lượt hồi sinh chung: 6</t>
         </is>
       </c>
@@ -13002,7 +13002,7 @@
         <is>
           <t>- Khi gây sát thương lên mục tiêu, kẻ địch sẽ áp dụng 1 tầng Chafe Băng Giá, kích hoạt mỗi 3 giây.
 - Kẻ địch hạng Elite có hiệu ứng sau: Phòng Ngự của các đơn vị đồng minh gần đó tăng 60%.
-Cooldown sinh: 10 giây (Chơi đơn &amp; Đồng đội)
+Thời gian hồi sinh: 10 giây (Chơi đơn &amp; Đồng đội)
 Lượt hồi sinh chung: 6</t>
         </is>
       </c>
@@ -13071,7 +13071,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Kẻ địch gây 1 lớp Erosion Gió khi tấn công mục tiêu, kích hoạt mỗi 3 giây.</t>
+          <t>Kẻ địch gây 1 lớp Aero Erosion khi tấn công mục tiêu, kích hoạt mỗi 3 giây.</t>
         </is>
       </c>
     </row>
@@ -13292,7 +13292,7 @@
 Một buổi chiều bình thường, Ciaccona đẩy cửa phòng làm việc của cha. Vật được cất trên tủ là thứ đầu tiên cô chú ý sau khi ngước lên. Cô nhẹ nhàng lấy nó xuống—đó là một cây vĩ cầm, lần đầu tiên cô chạm vào một nhạc cụ. Nhớ lại cách cha từng chơi nó, cô quyết định thử một lần.
 "Két..."
 Âm thanh chói tai không thể nhầm lẫn. Nhưng cô cảm thấy một cảm giác kỳ lạ, như thể mình đang chìm sâu xuống đáy biển. Mọi âm thanh khác dần biến mất, chỉ còn tiếng vĩ cầm. Ánh sáng và bóng tối của hoàng hôn mờ dần. Thế giới trước mắt cô như kéo rèm lại, và khi mở ra, một thế giới mới hiện ra. Không khí tràn ngập những nốt nhạc nhảy múa, và ở phía xa, một nhóm người đang chơi nhạc.
-"X-Hello?"
+"X-Xin chào?"
 Không ai đáp lại cô bé. Cô tiến lại gần, dù khuôn mặt họ mờ nhạt, nhưng giai điệu nghe thật quen thuộc.
 "Đây là bản nhạc cha thường chơi. Do gia đình mình sáng tác." Cô bé Ciaccona nhớ lại nguồn gốc của bản nhạc.
 Nhóm người đó như không hề biết đến sự hiện diện của cô, họ tiếp tục chơi, bao quanh cô bằng những giai điệu vang vọng tiếng khóc của trẻ sơ sinh, niềm vui và bi kịch của cuộc đời...
@@ -13495,7 +13495,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>"Đám địch ào tới bỗng gặp phải một vệt sáng xanh. Qingloong cuốn theo gió ập đến, và khi cơn bão qua đi, lá cờ Midnight Rangers vẫn hiên ngang trên cao điểm..."</t>
+          <t>"Đám địch ào tới bỗng gặp phải một vệt sáng xanh. Thanh Long cuốn theo gió ập đến, và khi cơn bão qua đi, lá cờ Midnight Rangers vẫn hiên ngang trên cao điểm..."</t>
         </is>
       </c>
     </row>
@@ -13560,7 +13560,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Kích hoạt hoàn toàn Chuỗi Resonance Spectro của Rover</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain Spectro của Rover</t>
         </is>
       </c>
     </row>
@@ -13625,7 +13625,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Kích hoạt toàn bộ Chuỗi Resonance của Yangyang</t>
+          <t>Kích hoạt toàn bộ Resonance Chain của Yangyang</t>
         </is>
       </c>
     </row>
@@ -13690,7 +13690,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Kích hoạt đầy đủ Resonance Chain của Chixia</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Chixia</t>
         </is>
       </c>
     </row>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Kích hoạt đầy đủ Resonance Chain của Baizhi</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Baizhi</t>
         </is>
       </c>
     </row>
@@ -13820,7 +13820,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Kích hoạt đầy đủ Resonance Chain của Danjin</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Danjin</t>
         </is>
       </c>
     </row>
@@ -13885,7 +13885,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Kích hoạt đầy đủ Resonance Chain của Sanhua</t>
+          <t>Kích hoạt toàn bộ Resonance Chain của Sanhua</t>
         </is>
       </c>
     </row>
@@ -13950,7 +13950,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Kích hoạt đầy đủ Resonance Chain của Taoqi</t>
+          <t>Kích hoạt toàn bộ Resonance Chain của Taoqi</t>
         </is>
       </c>
     </row>
@@ -14015,7 +14015,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Kích hoạt hoàn toàn Chuỗi Resonance của Mortefi</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Mortefi</t>
         </is>
       </c>
     </row>
@@ -14080,7 +14080,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Kích hoạt đầy đủ Resonance Chain của Yuanwu</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Yuanwu</t>
         </is>
       </c>
     </row>
@@ -14145,7 +14145,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Kích hoạt đầy đủ Resonance Chain của Aalto</t>
+          <t>Kích Hoạt Hoàn Toàn Resonance Chain Aalto</t>
         </is>
       </c>
     </row>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Kích hoạt đầy đủ Resonance Chain của Verina</t>
+          <t>Kích hoạt toàn bộ Resonance Chain của Verina</t>
         </is>
       </c>
     </row>
@@ -14275,7 +14275,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Kích hoạt đầy đủ Resonance Chain của Encore</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Encore</t>
         </is>
       </c>
     </row>
@@ -14340,7 +14340,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Kích hoạt hoàn toàn Chuỗi Resonance của Calcharo</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Calcharo</t>
         </is>
       </c>
     </row>
@@ -14405,7 +14405,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Kích hoạt toàn bộ Chuỗi Resonance của Lingyang</t>
+          <t>Kích hoạt toàn bộ Resonance Chain của Lingyang</t>
         </is>
       </c>
     </row>
@@ -14470,7 +14470,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Kích hoạt toàn bộ Chuỗi Resonance của Jianxin</t>
+          <t>Kích hoạt toàn bộ Resonance Chain của Jianxin</t>
         </is>
       </c>
     </row>
@@ -14535,7 +14535,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Kích hoạt đầy đủ Resonance Chain của Jiyan</t>
+          <t>Kích hoạt toàn bộ Resonance Chain của Jiyan</t>
         </is>
       </c>
     </row>
@@ -14600,7 +14600,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Kích hoạt đầy đủ Resonance Chain của Yinlin</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Yinlin</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Kích hoạt đầy đủ Resonance Chain của Jinhsi</t>
+          <t>Kích hoạt toàn bộ Resonance Chain của Jinhsi</t>
         </is>
       </c>
     </row>
@@ -14730,7 +14730,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Kích hoạt hoàn toàn Chuỗi Resonance của Changli</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Changli</t>
         </is>
       </c>
     </row>
@@ -14795,7 +14795,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Kích hoạt toàn bộ Chuỗi Resonance của Xiangli Yao</t>
+          <t>Kích hoạt toàn bộ Resonance Chain của Xiangli Yao</t>
         </is>
       </c>
     </row>
@@ -14860,7 +14860,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Kích hoạt đầy đủ Resonance Chain của Zhezhi</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Zhezhi</t>
         </is>
       </c>
     </row>
@@ -14925,7 +14925,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Kích hoạt toàn bộ Chuỗi Resonance của Shorekeeper</t>
+          <t>Kích hoạt toàn bộ Resonance Chain của Shorekeeper</t>
         </is>
       </c>
     </row>
@@ -14990,7 +14990,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Kích hoạt đầy đủ Resonance Chain của Youhu</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Youhu</t>
         </is>
       </c>
     </row>
@@ -15055,7 +15055,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Kích hoạt hoàn toàn Chuỗi Resonance của Camellya</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Camellya</t>
         </is>
       </c>
     </row>
@@ -15120,7 +15120,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Kích hoạt đầy đủ Resonance Chain của Lumi</t>
+          <t>Kích hoạt toàn bộ Resonance Chain của Lumi</t>
         </is>
       </c>
     </row>
@@ -15185,7 +15185,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Kích hoạt hoàn toàn Chuỗi Resonance của Carlotta</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Carlotta</t>
         </is>
       </c>
     </row>
@@ -15250,7 +15250,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Kích hoạt đầy đủ Resonance Chain của Roccia</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Roccia</t>
         </is>
       </c>
     </row>
@@ -15315,7 +15315,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Kích hoạt đầy đủ Resonance Chain của Brant</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Brant</t>
         </is>
       </c>
     </row>
@@ -15380,7 +15380,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Kích hoạt đầy đủ Resonance Chain của Phoebe</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Phoebe</t>
         </is>
       </c>
     </row>
@@ -15445,7 +15445,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Kích hoạt hoàn toàn Chuỗi Resonance của Cantarella</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Cantarella</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Kích hoạt hoàn toàn Chuỗi Resonance của Ciaccona</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Ciaccona</t>
         </is>
       </c>
     </row>
@@ -15575,7 +15575,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Kích hoạt đầy đủ Resonance Chain của Zani</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Zani</t>
         </is>
       </c>
     </row>
@@ -15640,7 +15640,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Cooldown Skill</t>
+          <t>Thời gian hồi Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -15705,7 +15705,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Cooldown Skill</t>
+          <t>Thời gian hồi Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -15965,7 +15965,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Kỹ Năng Special</t>
+          <t>Kỹ Năng Đặc Biệt</t>
         </is>
       </c>
     </row>
@@ -16031,8 +16031,8 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Trong giai đoạn này, bạn có thể Triển khai, Điều Chỉnh hoặc Biến Đổi một Echo. Bạn cũng có thể kéo Echo vào Khu Vực Tái Tạo để phục hồi Năng Lượng.
-- {Cus:Ipt,Touch=tap PC=click Gamepad=press} "Fight!" để kết thúc giai đoạn này.</t>
+          <t>Trong giai đoạn này, bạn có thể Triển Khai, Điều Chỉnh hoặc Biến Đổi một Echo. Bạn cũng có thể kéo Echo vào Khu Vực Tái Tạo để phục hồi Năng Lượng.
+- {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} "Chiến đấu!" để kết thúc giai đoạn này.</t>
         </is>
       </c>
     </row>
@@ -16097,7 +16097,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Kích hoạt &lt;color=#ffb04a&gt;Resonance Liberation&lt;/color&gt; sẽ tăng Spectro DMG của họ lên 10% trong 15 giây.</t>
+          <t>Kích hoạt &lt;color=#ffb04a&gt;Resonance Liberation&lt;/color&gt; sẽ tăng Sát Thương Spectro của họ lên 10% trong 15 giây.</t>
         </is>
       </c>
     </row>
@@ -16162,7 +16162,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Đánh trúng mục tiêu bằng &lt;color=#ffb04a&gt;Resonance Skill&lt;/color&gt; sẽ tăng &lt;color=#ffb04a&gt;Resonance Skill&lt;/color&gt; của chúng lên 20% trong 10 giây.</t>
+          <t>Đánh trúng mục tiêu bằng &lt;color=#ffb04a&gt;Resonance Skill&lt;/color&gt; sẽ tăng &lt;color=#ffb04a&gt;Sát Thương Resonance Skill&lt;/color&gt; của chúng lên 20% trong 10 giây.</t>
         </is>
       </c>
     </row>
@@ -16357,7 +16357,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Kỹ Năng Special</t>
+          <t>Kỹ Năng Đặc Biệt</t>
         </is>
       </c>
     </row>
@@ -16422,7 +16422,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Thông tin kỹ năng</t>
+          <t>Thông tin Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -16487,7 +16487,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Tiêu hao tổng cộng 10 Thủy Triều Lấp Lánh.</t>
+          <t>Tiêu hao tổng cộng 10 Lustrous Tide.</t>
         </is>
       </c>
     </row>
@@ -16552,7 +16552,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Invisibility&lt;/color&gt; - Trong {0} giây đầu Battle Stage và cho đến khi gây sát thương, Echo này không thể bị tấn công. Sau khi Tàng Hình kết thúc, sát thương gây ra bởi Echo này tăng thêm {2} trong {1} giây.</t>
+          <t>&lt;color=#e4c69b&gt;Tàng Hình&lt;/color&gt; - Trong {0} giây đầu Giai Đoạn Chiến Đấu và cho đến khi gây sát thương, Tổ Tacet này không thể bị tấn công. Sau khi Tàng Hình kết thúc, sát thương gây ra bởi Tổ Tacet này tăng thêm {2} trong {1} giây.</t>
         </is>
       </c>
     </row>
@@ -16617,7 +16617,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Toughness&lt;/color&gt; - Khi Resonator bị tấn công trong Battle Stage, sát thương nhận vào giảm {0} trong {1} giây. Cooldown chiêu sẽ được đặt lại thay vì chồng chất nếu kích hoạt lại.</t>
+          <t>&lt;color=#e4c69b&gt;Kiên Cường&lt;/color&gt; - Khi Cộng Hưởng Giả bị tấn công trong Giai Đoạn Chiến Đấu, DMG nhận vào giảm {0} trong {1} giây. Thời gian hồi chiêu sẽ được đặt lại thay vì chồng chất nếu kích hoạt lại.</t>
         </is>
       </c>
     </row>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Mimic&lt;/color&gt; - Khi Echo này kích hoạt Kỹ Năng Special tiếp theo thông qua Điều Tần, Bắt Chước sẽ biến thành kỹ năng đó.</t>
+          <t>&lt;color=#e4c69b&gt;Bắt Chước&lt;/color&gt; - Khi Tổ Tacet này kích hoạt Kỹ Năng Đặc Biệt tiếp theo thông qua Điều Tần, Bắt Chước sẽ biến thành kỹ năng đó.</t>
         </is>
       </c>
     </row>
@@ -16747,7 +16747,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Explosion&lt;/color&gt; - Khi Tacet Discord này bị hạ gục trong Battle Stage, nó sẽ phát nổ và gây sát thương lên các Tacet Discord địch xung quanh.</t>
+          <t>&lt;color=#e4c69b&gt;Explosion&lt;/color&gt; - Khi Tacet Discord này bị hạ gục trong Giai Đoạn Chiến Đấu, nó sẽ phát nổ và gây sát thương lên các Tacet Discord địch xung quanh.</t>
         </is>
       </c>
     </row>
@@ -16812,7 +16812,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Restraint&lt;/color&gt; - Khi Giai Đoạn Triển Khai kết thúc, Resonator địch ở cùng vị trí với Resonator này (Hàng Trước hoặc Hàng Sau) sẽ mất {0} Strength trong lượt này.</t>
+          <t>&lt;color=#e4c69b&gt;Kiềm Chế&lt;/color&gt; - Khi Giai Đoạn Triển Khai kết thúc, Cộng Hưởng Giả địch ở cùng vị trí với Cộng Hưởng Giả này (Hàng Trước hoặc Hàng Sau) sẽ mất {0} Sức Mạnh trong lượt này.</t>
         </is>
       </c>
     </row>
@@ -16877,7 +16877,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Last Stand&lt;/color&gt; - Nếu HP của ngươi còn {0} hoặc thấp hơn khi Giai Đoạn Triển Khai kết thúc, Echo này sẽ gây thêm {1} Sát Thương lên Echo địch trong Battle Stage kế tiếp.</t>
+          <t>&lt;color=#e4c69b&gt;Bất Khuất&lt;/color&gt; - Nếu HP của ngươi còn {0} hoặc thấp hơn khi Giai Đoạn Triển Khai kết thúc, Tổ Tacet này sẽ gây thêm {1} Sát Thương lên Tổ Tacet địch trong Giai Đoạn Chiến Đấu kế tiếp.</t>
         </is>
       </c>
     </row>
@@ -16942,7 +16942,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Berserk&lt;/color&gt; - Nếu HP của Tacet Discord này giảm xuống còn {0} hoặc thấp hơn trong Battle Stage, nó sẽ gây thêm {1} Sát Thương lên các Tacet Discord địch trong giai đoạn này.</t>
+          <t>&lt;color=#e4c69b&gt;Berserk&lt;/color&gt; - Nếu HP của Tacet Discord này giảm xuống còn {0} hoặc thấp hơn trong Giai Đoạn Chiến Đấu, nó sẽ gây thêm {1} Sát Thương lên các Tacet Discord địch trong giai đoạn này.</t>
         </is>
       </c>
     </row>
@@ -17007,7 +17007,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Forestall&lt;/color&gt; - Khi Battle Stage bắt đầu, Echo này gây thêm {0} Sát Thương lên Echo địch trong {1} giây.</t>
+          <t>&lt;color=#e4c69b&gt;Chặn Đầu&lt;/color&gt; - Khi Giai Đoạn Chiến Đấu bắt đầu, Tổ Tacet này gây thêm {0} Sát Thương lên Tổ Tacet địch trong {1} giây.</t>
         </is>
       </c>
     </row>
@@ -17072,7 +17072,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Taunt&lt;/color&gt; - Khi ở Hàng Trước, Resonator địch sẽ tấn công Resonator này trước trong Battle Stage.</t>
+          <t>&lt;color=#e4c69b&gt;Khiêu Khích&lt;/color&gt; - Khi ở Hàng Trước, Cộng Hưởng Giả địch sẽ tấn công Cộng Hưởng Giả này trước trong Giai Đoạn Chiến Đấu.</t>
         </is>
       </c>
     </row>
@@ -17202,7 +17202,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Flank Force&lt;/color&gt; - Khi Echo này ở Khu Triển Khai (cả Hàng Tiền hoặc Hàng Hậu) cùng hai another Echo, tất cả sẽ nhận {0} Sát Thương khi Giai Đoạn Triển Khai kết thúc, hiệu lực đến hết lượt đấu.</t>
+          <t>&lt;color=#e4c69b&gt;Lực Lượng Cánh&lt;/color&gt; - Khi Tổ Tacet này ở Khu Triển Khai (cả Hàng Tiền hoặc Hàng Hậu) cùng hai Tổ Tacet khác, tất cả sẽ nhận {0} Sát Thương khi Giai Đoạn Triển Khai kết thúc, hiệu lực đến hết lượt đấu.</t>
         </is>
       </c>
     </row>
@@ -17267,7 +17267,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Superpower&lt;/color&gt; - Với mỗi Kỹ Năng Special mà Resonator này sở hữu, nó gây thêm {0} Sát Thương lên Resonator địch trong Battle Stage, cộng dồn tối đa {1} lần.</t>
+          <t>&lt;color=#e4c69b&gt;Siêu Năng Lực&lt;/color&gt; - Với mỗi Kỹ Năng Đặc Biệt mà Cộng Hưởng Giả này sở hữu, nó gây thêm {0} Sát Thương lên Cộng Hưởng Giả địch trong Giai Đoạn Chiến Đấu, cộng dồn tối đa {1} lần.</t>
         </is>
       </c>
     </row>
@@ -17462,7 +17462,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Kích hoạt hoàn toàn Chuỗi Resonance Havoc của Rover</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain Havoc của Rover</t>
         </is>
       </c>
     </row>
@@ -17527,7 +17527,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Kích hoạt hoàn toàn Chuỗi Resonance Aero của Rover</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain Aero của Rover</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
           <t>Về Sự Kiện
 Đây là một Sonoro Sphere thu nhỏ do Forte của Ciaccona - Vương Quốc Giai Điệu tạo ra. Trong không gian này, những câu chuyện quá khứ tái hiện qua từng mảnh ghép, và cần sự suy luận cùng manh mối để có được bức tranh toàn cảnh.
 Điều Kiện Tham Gia
-Đạt Cấp Liên Minh 14. Hoàn thành Chương II Lời Mở Đầu Nhiệm Vụ Chính để mở khóa sớm. Nên hoàn thành Chương II Act IV Nhiệm Vụ Chính để có trải nghiệm tốt hơn.</t>
+Đạt Cấp Liên Minh 14. Hoàn thành Chương II Lời Mở Đầu Nhiệm Vụ Chính để mở khóa sớm. Nên hoàn thành Chương II Hồi IV Nhiệm Vụ Chính để có trải nghiệm tốt hơn.</t>
         </is>
       </c>
     </row>
@@ -17794,8 +17794,8 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Dù là thiên tài như Gallus Nightmare, vẫn có những vấn đề mà ngay cả thiên tài cũng không thể giải quyết.
-Chiến thuật của Gallus: Increase HP cơ bản lên 45. Gallus rút thêm 2 lá bài trong giai đoạn triển khai mỗi lượt.</t>
+          <t>Dù là thiên tài như Gallus Ác Mộng, vẫn có những vấn đề mà ngay cả thiên tài cũng không thể giải quyết.
+Chiến thuật của Gallus: Tăng HP cơ bản lên 45. Gallus rút thêm 2 lá bài trong giai đoạn triển khai mỗi lượt.</t>
         </is>
       </c>
     </row>
@@ -17861,8 +17861,8 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Furius the Firebrand, Kẻ Chinh Phục Danh Vọng và người tạo ra trò chơi này, là thử thách cuối cùng mà các Duelist phải vượt qua trước khi chạm tới đỉnh vinh quang.
-Chiến thuật của Furius: Increase HP cơ bản lên 50. Bắt đầu lượt đầu tiên với 8 lá bài tự chọn và nhận thêm 6 Năng Lượng.</t>
+          <t>Furius Ngọn Lửa Bất Khuất, Kẻ Chinh Phục Danh Vọng và người tạo ra trò chơi này, là thử thách cuối cùng mà các Duelist phải vượt qua trước khi chạm tới đỉnh vinh quang.
+Chiến thuật của Furius: Tăng HP cơ bản lên 50. Bắt đầu lượt đầu tiên với 8 lá bài tự chọn và nhận thêm 6 Năng Lượng.</t>
         </is>
       </c>
     </row>
@@ -17928,8 +17928,8 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Thách đấu những Duel Thủ Ưu Tú và chứng tỏ sức mạnh vô song của ngươi!
-Chiến thuật Duel Thủ Ưu Tú: Increase HP cơ bản lên 45. Khi bắt đầu Giai đoạn Triển khai, Duel Thủ Ưu Tú rút thêm một lá bài. Trong trận đấu này, Echoes của Duel Thủ Ưu Tú được tăng STR và CON thêm 2.</t>
+          <t>Thách đấu những Đấu Thủ Ưu Tú và chứng tỏ sức mạnh vô song của ngươi!
+Chiến thuật Đấu Thủ Ưu Tú: Tăng HP cơ bản lên 45. Khi bắt đầu Giai đoạn Triển khai, Đấu Thủ Ưu Tú rút thêm một lá bài. Trong trận đấu này, Echo của Đấu Thủ Ưu Tú được tăng STR và CON thêm 2.</t>
         </is>
       </c>
     </row>
@@ -17994,7 +17994,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Round 8.</t>
+          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Vòng 8.</t>
         </is>
       </c>
     </row>
@@ -18059,7 +18059,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Round 8.</t>
+          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Vòng 8.</t>
         </is>
       </c>
     </row>
@@ -18124,7 +18124,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Round 8.</t>
+          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Vòng 8.</t>
         </is>
       </c>
     </row>
@@ -18189,7 +18189,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Round 8.</t>
+          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Vòng 8.</t>
         </is>
       </c>
     </row>
@@ -18254,7 +18254,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Round 8.</t>
+          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Vòng 8.</t>
         </is>
       </c>
     </row>
@@ -18319,7 +18319,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Round 8.</t>
+          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Vòng 8.</t>
         </is>
       </c>
     </row>
@@ -18384,7 +18384,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Round 8.</t>
+          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Vòng 8.</t>
         </is>
       </c>
     </row>
@@ -18449,7 +18449,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Round 8.</t>
+          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Vòng 8.</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Round 8.</t>
+          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Vòng 8.</t>
         </is>
       </c>
     </row>
@@ -18579,7 +18579,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Round 8.</t>
+          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Vòng 8.</t>
         </is>
       </c>
     </row>
@@ -18644,7 +18644,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Round 8.</t>
+          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Vòng 8.</t>
         </is>
       </c>
     </row>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Round 8.</t>
+          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Vòng 8.</t>
         </is>
       </c>
     </row>
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Round 8.</t>
+          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Vòng 8.</t>
         </is>
       </c>
     </row>
@@ -18839,7 +18839,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Round 8.</t>
+          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Vòng 8.</t>
         </is>
       </c>
     </row>
@@ -18904,7 +18904,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Round 8.</t>
+          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Vòng 8.</t>
         </is>
       </c>
     </row>
@@ -18970,8 +18970,8 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Hạ HP đối thủ về 0, hoặc có nhiều HP hơn họ khi kết thúc Round 8.
-Chiến thuật Gallus: Increase HP Cơ Bản lên 45. Gallus rút thêm 2 lá bài trong giai đoạn triển khai mỗi vòng.</t>
+          <t>Hạ HP đối thủ về 0, hoặc có nhiều HP hơn họ khi kết thúc Vòng 8.
+Chiến thuật Gallus: Tăng HP Cơ Bản lên 45. Gallus rút thêm 2 lá bài trong giai đoạn triển khai mỗi vòng.</t>
         </is>
       </c>
     </row>
@@ -19036,7 +19036,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Round 8.</t>
+          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Vòng 8.</t>
         </is>
       </c>
     </row>
@@ -19101,7 +19101,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Round 8.</t>
+          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Vòng 8.</t>
         </is>
       </c>
     </row>
@@ -19166,7 +19166,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Round 8.</t>
+          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Vòng 8.</t>
         </is>
       </c>
     </row>
@@ -19232,8 +19232,8 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Round 8.
-Chiến thuật của Furius: Increase HP cơ bản lên 50. Bắt đầu vòng đầu tiên, rút 8 lá bài tùy chọn và nhận thêm 6 Năng Lượng.</t>
+          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Vòng 8.
+Chiến thuật của Furius: Tăng HP cơ bản lên 50. Bắt đầu vòng đầu tiên, rút 8 lá bài tùy chọn và nhận thêm 6 Năng Lượng.</t>
         </is>
       </c>
     </row>
@@ -19299,8 +19299,8 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Round 8.
-Chiến thuật của Brant: Increase HP cơ bản lên 55. Brant chịu ít hơn 6 sát thương mỗi vòng trong Battle Stage.</t>
+          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Vòng 8.
+Chiến thuật của Brant: Tăng HP cơ bản lên 55. Brant chịu ít hơn 6 sát thương mỗi vòng trong Giai Đoạn Chiến Đấu.</t>
         </is>
       </c>
     </row>
@@ -19366,8 +19366,8 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Round 8.
-Chiến thuật của Ciaccona: Increase HP cơ bản lên 55. Echoes của Ciaccona tăng 2 STR và 2 CON trong 5 vòng đầu.</t>
+          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Vòng 8.
+Chiến thuật của Ciaccona: Tăng HP cơ bản lên 55. Echo của Ciaccona tăng 2 STR và 2 CON trong 5 vòng đầu.</t>
         </is>
       </c>
     </row>
@@ -19433,8 +19433,8 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Hạ HP đối thủ về 0, hoặc có nhiều HP hơn họ khi kết thúc Round 8.
-Chiến thuật Lupa: Increase HP Cơ Bản lên 55. Lupa rút thêm 3 lá bài trong giai đoạn triển khai mỗi vòng.</t>
+          <t>Hạ HP đối thủ về 0, hoặc có nhiều HP hơn họ khi kết thúc Vòng 8.
+Chiến thuật Lupa: Tăng HP Cơ Bản lên 55. Lupa rút thêm 3 lá bài trong giai đoạn triển khai mỗi vòng.</t>
         </is>
       </c>
     </row>
@@ -19500,8 +19500,8 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Round 8.
-Chiến thuật của Calcharo: Increase HP cơ bản lên 55. Core Echo của Calcharo tăng 4 STR và 8 CON.</t>
+          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Vòng 8.
+Chiến thuật của Calcharo: Tăng HP cơ bản lên 55. Core Echo của Calcharo tăng 4 STR và 8 CON.</t>
         </is>
       </c>
     </row>
@@ -19566,7 +19566,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Round 8.</t>
+          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Vòng 8.</t>
         </is>
       </c>
     </row>
@@ -19632,8 +19632,8 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Round 8.
-Chiến thuật của Duelist Cao Cấp: Increase HP cơ bản lên 45. Khi bắt đầu Giai Đoạn Triển Khai, Duelist Cao Cấp rút thêm một lá bài. Echoes của Duelist Cao Cấp tăng 2 STR và 2 CON trong trận đấu này.</t>
+          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Vòng 8.
+Chiến thuật của Duelist Cao Cấp: Tăng HP cơ bản lên 45. Khi bắt đầu Giai Đoạn Triển Khai, Duelist Cao Cấp rút thêm một lá bài. Echo của Duelist Cao Cấp tăng 2 STR và 2 CON trong trận đấu này.</t>
         </is>
       </c>
     </row>
@@ -19698,7 +19698,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Round 8.</t>
+          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Vòng 8.</t>
         </is>
       </c>
     </row>
@@ -19763,7 +19763,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Round 8.</t>
+          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Vòng 8.</t>
         </is>
       </c>
     </row>
@@ -19828,7 +19828,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Round 8.</t>
+          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Vòng 8.</t>
         </is>
       </c>
     </row>
@@ -19893,7 +19893,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Round 8.</t>
+          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Vòng 8.</t>
         </is>
       </c>
     </row>
@@ -19958,7 +19958,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Round 8.</t>
+          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Vòng 8.</t>
         </is>
       </c>
     </row>
@@ -20023,7 +20023,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Round 8.</t>
+          <t>Giảm HP của đối thủ xuống 0, hoặc có nhiều HP hơn họ khi kết thúc Vòng 8.</t>
         </is>
       </c>
     </row>
@@ -20088,7 +20088,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Lượt này, với tư cách Đấu Thủ, ngươi sẽ nhận ít hơn 1 sát thương.</t>
+          <t>Lượt này, với tư cách Đấu Thủ, ngươi sẽ nhận ít hơn 1 DMG.</t>
         </is>
       </c>
     </row>
@@ -20153,7 +20153,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Chiến Thuật Chủ Động ({0}): Trong lượt này, tăng sát thương của Echoes lên {1}.</t>
+          <t>Chiến Thuật Chủ Động ({0}): Trong lượt này, tăng DMG của Echo lên {1}.</t>
         </is>
       </c>
     </row>
@@ -20218,7 +20218,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Passive Tactic: Trong Battle Stage, tăng Crit. Rate cho Echoes có Cost {0} của bạn thêm {1}.</t>
+          <t>Thụ Động Chiến Thuật: Trong Giai Đoạn Chiến Đấu, tăng Crit. Rate cho Echo có Cost {0} của bạn thêm {1}.</t>
         </is>
       </c>
     </row>
@@ -20283,7 +20283,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Chiến Thuật Chủ Động ({0}): Chọn một Echoes của bạn để giảm {1} sát thương nhận vào trong {2} giây ở Battle Stage lượt này.</t>
+          <t>Chiến Thuật Chủ Động ({0}): Chọn một Echo của bạn để giảm {1} DMG nhận vào trong {2} giây ở Giai Đoạn Chiến Đấu lượt này.</t>
         </is>
       </c>
     </row>
@@ -20348,7 +20348,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Passive Tactic: Trong ba hiệp đầu, khi là người thách đấu trong Battle Stage, bạn chịu ít hơn {0} Sát Thương.</t>
+          <t>Thụ Động Chiến Thuật: Trong ba hiệp đầu, khi là người thách đấu trong Giai Đoạn Chiến Đấu, bạn chịu ít hơn {0} Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -20413,7 +20413,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Chiến Thuật Chủ Động ({0}): Chọn một Echoes của đối thủ và giảm sức mạnh của nó đi {1} cho đến khi lượt kết thúc.</t>
+          <t>Chiến Thuật Chủ Động ({0}): Chọn một Echo của đối thủ và giảm sức mạnh của nó đi {1} cho đến khi lượt kết thúc.</t>
         </is>
       </c>
     </row>
@@ -20478,7 +20478,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Passive Tactic: Trong Battle Stage, tăng Crit. Rate cho Echo Cốt Core của bạn thêm {0}.</t>
+          <t>Thụ Động Chiến Thuật: Trong Giai Đoạn Chiến Đấu, tăng Crit. Rate cho Echo Cốt Lõi của bạn thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -20611,8 +20611,8 @@
       <c r="M304" t="inlineStr">
         <is>
           <t>Khi Tacet Discord này được Triển Khai, tăng Sát Thương thêm {7}.
-Tacet Discord này không gây sát thương trong {0} giây đầu của Battle Stage.
-Vào giây thứ {1} của Battle Stage, phá hủy tất cả Tacet Discord của ngươi ngoại trừ Tacet Discord này và hồi phục {2} HP tối đa của nó. Sau đó, tăng Sát Thương gây ra lên Tacet Discord địch của Tacet Discord này thêm {3}, Crit. Rate thêm {4}, và giảm Sát Thương nhận vào {5}. Hiệu ứng kéo dài trong {6} giây.</t>
+Tacet Discord này không gây DMG trong {0} giây đầu của Giai Đoạn Chiến Đấu.
+Vào giây thứ {1} của Giai Đoạn Chiến Đấu, phá hủy tất cả Tacet Discord của ngươi ngoại trừ Tacet Discord này và hồi phục {2} HP tối đa của nó. Sau đó, tăng Sát Thương gây ra lên Tacet Discord địch của Tacet Discord này thêm {3}, Crit. Rate thêm {4}, và giảm Sát Thương nhận vào {5}. Hiệu ứng kéo dài trong {6} giây.</t>
         </is>
       </c>
     </row>
@@ -20807,7 +20807,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Khi Battle Stage bắt đầu, nếu Echo này được Triển Khai trong lượt này và vẫn còn trong Vùng Triển Khai, bạn sẽ gây thêm {0} sát thương lên đối thủ khi Battle Stage kết thúc.</t>
+          <t>Khi Giai Đoạn Chiến Đấu bắt đầu, nếu Echo này được Triển Khai trong lượt này và vẫn còn trong Vùng Triển Khai, bạn sẽ gây thêm {0} DMG lên đối thủ khi Giai Đoạn Chiến Đấu kết thúc.</t>
         </is>
       </c>
     </row>
@@ -21067,7 +21067,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>- Khi Modulate Echo này, nếu Taunt và Toughness đã được Kích Hoạt, có {0}% cơ hội hồi {1} HP tối đa của nó khi bị tấn công trong Battle Stage. Hiệu ứng này có thể kích hoạt mỗi giây một lần.</t>
+          <t>- Khi Modulate Echo này, nếu Taunt và Toughness đã được Kích Hoạt, có {0}% cơ hội hồi {1} HP tối đa của nó khi bị tấn công trong Giai Đoạn Chiến Đấu. Hiệu ứng này có thể kích hoạt mỗi giây một lần.</t>
         </is>
       </c>
     </row>
@@ -21197,7 +21197,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Trong Battle Stage, các Echoes của bạn phục hồi {0} HP tối đa mỗi giây.</t>
+          <t>Trong Giai Đoạn Chiến Đấu, các Echo của bạn phục hồi {0} HP tối đa mỗi giây.</t>
         </is>
       </c>
     </row>
@@ -21262,7 +21262,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Biến Hóa ({0}): Increase Sức Mạnh của các Resonator lên {1} đến hết lượt.</t>
+          <t>Biến Hóa ({0}): Tăng Sức Mạnh của các Cộng Hưởng Giả lên {1} đến hết lượt.</t>
         </is>
       </c>
     </row>
@@ -21393,7 +21393,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Trong Battle Stage, mỗi {0} giây Echo này tồn tại, bạn sẽ gây thêm {1} Sát Thương lên đối thủ khi Battle Stage kết thúc.
+          <t>Trong Giai Đoạn Chiến Đấu, mỗi {0} giây Echo này tồn tại, bạn sẽ gây thêm {1} Sát Thương lên đối thủ khi Giai Đoạn Chiến Đấu kết thúc.
 - Khi Bạn Điều Chỉnh Echo này, nếu trạng thái Tàng Hình đã được Kích Hoạt, hãy tăng CON của nó lên {2}.</t>
         </is>
       </c>
@@ -21459,7 +21459,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>- Khi sử dụng Biến Đổi, chỉ số STR và CON của Echo này sẽ tăng {0} cho đến hết vòng.</t>
+          <t>- Khi sử dụng Transform, chỉ số STR và CON của Echo này sẽ tăng {0} cho đến hết vòng.</t>
         </is>
       </c>
     </row>
@@ -21524,7 +21524,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Biến Hóa ({0}): Chọn một Resonator của đối thủ và giảm Sức Mạnh của nó đi {1} đến hết lượt.</t>
+          <t>Biến Hóa ({0}): Chọn một Cộng Hưởng Giả của đối thủ và giảm Sức Mạnh của nó đi {1} đến hết lượt.</t>
         </is>
       </c>
     </row>
@@ -21589,7 +21589,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>- Khi sử dụng Biến Đổi, Echoes này gây thêm {0} sát thương lên Echoes địch trong Battle Stage ở vòng hiện tại.</t>
+          <t>- Khi sử dụng Transform, Echo này gây thêm {0} DMG lên Echo địch trong Battle Stage ở vòng hiện tại.</t>
         </is>
       </c>
     </row>
@@ -21654,7 +21654,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Biến Hóa ({0}): Increase Sức Mạnh và Thể Trạng của các Resonator lên {1} đến hết lượt.</t>
+          <t>Biến Hóa ({0}): Tăng Sức Mạnh và Thể Trạng của các Cộng Hưởng Giả lên {1} đến hết lượt.</t>
         </is>
       </c>
     </row>
@@ -21719,7 +21719,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Biến Hóa ({0}): Increase Sức Mạnh của các Resonator lên {1} đến hết lượt. Bản sao này sẽ không bị tiêu hao khi Biến Hóa mà sẽ được xáo lại vào bộ bài.</t>
+          <t>Biến Hóa ({0}): Tăng Sức Mạnh của các Cộng Hưởng Giả lên {1} đến hết lượt. Bản sao này sẽ không bị tiêu hao khi Biến Hóa mà sẽ được xáo lại vào bộ bài.</t>
         </is>
       </c>
     </row>
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Khi Triển Khai, Echoes này sẽ nhận thêm Hiệu Ứng Kiên Cường. Nếu nó vẫn ở trong Vùng Triển Khai khi Giai Đoạn Triển Khai kết thúc, sẽ tăng Sức Mạnh và Thể Chất cho tất cả Echoes của bạn có Hiệu Ứng Kiên Cường thêm {0} trong 1 lượt.</t>
+          <t>Khi Triển Khai, Echo này sẽ nhận thêm Hiệu Ứng Kiên Cường. Nếu nó vẫn ở trong Vùng Triển Khai khi Giai Đoạn Triển Khai kết thúc, sẽ tăng Sức Mạnh và Thể Chất cho tất cả Echo của bạn có Hiệu Ứng Kiên Cường thêm {0} trong 1 lượt.</t>
         </is>
       </c>
     </row>
@@ -21914,7 +21914,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Biến Hóa ({0}): Trong lượt này, tăng Sức Mạnh của các Resonator lên {1} và Thể Trạng lên {2}.</t>
+          <t>Biến Hóa ({0}): Trong lượt này, tăng Sức Mạnh của các Cộng Hưởng Giả lên {1} và Thể Trạng lên {2}.</t>
         </is>
       </c>
     </row>
@@ -21979,7 +21979,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Khi Giai Đoạn Triển Khai kết thúc, nếu Trạng Thái Tận Dụng của Echoes này được Kích Hoạt và HP của bạn trên {1}, tăng Sức Mạnh cho tất cả Echoes của bạn thêm {2} cho đến khi lượt kết thúc và giảm HP của bạn đi {3}.</t>
+          <t>Khi Giai Đoạn Triển Khai kết thúc, nếu Trạng Thái Tận Dụng của Echo này được Kích Hoạt và HP của bạn trên {1}, tăng Sức Mạnh cho tất cả Echo của bạn thêm {2} cho đến khi lượt kết thúc và giảm HP của bạn đi {3}.</t>
         </is>
       </c>
     </row>
@@ -22044,7 +22044,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>- Với mỗi Kỹ Năng Special của Echoes khác, toàn bộ Echoes của bạn sẽ tăng {0} Crit. Rate trong Battle Stage, tối đa {1} lần cộng dồn.</t>
+          <t>- Với mỗi Kỹ Năng Đặc Biệt của Echo khác, toàn bộ Echo của bạn sẽ tăng {0} Crit. Rate trong Giai Đoạn Chiến Đấu, tối đa {1} lần cộng dồn.</t>
         </is>
       </c>
     </row>
@@ -22174,7 +22174,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Biến Hình ({0}): Bạn sẽ không bị mất HP trong Giai Đoạn Triển Khai lượt này (không hiệu quả trong Battle Stage).</t>
+          <t>Biến Hình ({0}): Bạn sẽ không bị mất HP trong Giai Đoạn Triển Khai lượt này (không hiệu quả trong Giai Đoạn Chiến Đấu).</t>
         </is>
       </c>
     </row>
@@ -22308,7 +22308,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Khi ngươi Điều Chỉnh Tacet Discord này, với mỗi Kỹ Năng Special mà nó sở hữu, tăng Sát Thương gây ra lên Tacet Discord địch trong Battle Stage thêm {0}, có thể cộng dồn tối đa {1} lần.</t>
+          <t>Khi ngươi Điều Chỉnh Tacet Discord này, với mỗi Kỹ Năng Đặc Biệt mà nó sở hữu, tăng Sát Thương gây ra lên Tacet Discord địch trong Giai Đoạn Chiến Đấu thêm {0}, có thể cộng dồn tối đa {1} lần.</t>
         </is>
       </c>
     </row>
@@ -22373,7 +22373,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Biến Hóa ({0}): Increase Sức Mạnh của các Resonator lên {1} đến hết lượt.</t>
+          <t>Biến Hóa ({0}): Tăng Sức Mạnh của các Cộng Hưởng Giả lên {1} đến hết lượt.</t>
         </is>
       </c>
     </row>
@@ -22503,7 +22503,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>- Khi Modulate Echoes này, nếu Explosion đã được Kích Hoạt, tăng sát thương gây ra bởi Explosion lên Echoes địch thêm {0}.</t>
+          <t>- Khi Modulate Echo này, nếu Explosion đã được Kích Hoạt, tăng DMG gây ra bởi Explosion lên Echo địch thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -22572,9 +22572,9 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>[Resonance Evaluation Report RA-X006]
+          <t>[Báo Cáo Đánh Giá Cộng Hưởng RA-X006]
 Thời điểm thức tỉnh không rõ. Dự đoán do ảnh hưởng đối lập từ &lt;te href=850083&gt;Sentinel&lt;/te&gt; &lt;te href=850105&gt;Imperator&lt;/te&gt; và &lt;te href=850074&gt;Threnodian&lt;/te&gt; Leviathan, dữ liệu Hiệu Suất Phổ của Cartethyia vượt quá giá trị tiêu chuẩn ▇▇▇▇▇▇▇. Không thể tính toán chính xác bằng các phương pháp hiện có.
-Phân tích mẫu thử cho thấy &lt;te href=850067&gt;Rabelle's Curve&lt;/te&gt; không hội tụ với dạng sóng tuần hoàn rõ rệt. Do đó, Cartethyia được phân loại là &lt;te href=850068&gt;Congenital Resonator&lt;/te&gt;.
+Phân tích mẫu thử cho thấy &lt;te href=850067&gt;Đường Cong Rabelle&lt;/te&gt; không hội tụ với dạng sóng tuần hoàn rõ rệt. Do đó, Cartethyia được phân loại là &lt;te href=850068&gt;Resonator Bẩm Sinh&lt;/te&gt;.
 &lt;i&gt;Hệ thống đã phân loại Cartethyia là đối tượng đặc biệt. Hồ sơ của cô đã được niêm phong dưới dự án đặc biệt. Quyền truy cập: ▇▇▇&lt;/i&gt;
 &lt;i&gt;Hệ thống sẽ tiếp tục giám sát Cartethyia.&lt;/i&gt;</t>
         </is>
@@ -22648,12 +22648,12 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>[Trích Đoạn Đánh Giá Resonance Của Đấu Sĩ]
-Name Đấu Sĩ: Lupa
-Gladiator này được phân loại là Resonator Phi Bẩm Sinh, khả năng Resonance lần đầu xuất hiện trong một sự kiện đấu sĩ thời thơ ấu. Thời gian Resonance ước tính vượt quá mười năm.
-Phân tích phổ tần số cho thấy Resonance chính của cô ấy nghiêng về lửa. Tuy nhiên, các đặc điểm chồng chéo trên nhiều dấu hiệu phổ tiêu chuẩn đã khiến việc phân loại nguồn gốc chính xác trở nên bất khả thi.
-Gladiator này đã thể hiện sự gia tăng ổn định cả về sức mạnh lẫn độ chính xác của khả năng trong suốt sự nghiệp thi đấu.
-&lt;te href=850072&gt;Tacet Mark&lt;/te&gt; nằm ở bên trái eo của đấu sĩ. Sự Thức Tỉnh Resonance đi kèm với các đặc điểm biến đổi một phần giống sói. Ngoài chiếc đuôi có thể nhìn thấy, đấu sĩ tự báo cáo về sự nhạy bén gia tăng của khứu giác và thính giác.
+          <t>[Trích Đoạn Đánh Giá Cộng Hưởng Của Đấu Sĩ]
+Tên Đấu Sĩ: Lupa
+Đấu sĩ này được phân loại là Resonator Phi Bẩm Sinh, khả năng Cộng Hưởng lần đầu xuất hiện trong một sự kiện đấu sĩ thời thơ ấu. Thời gian Cộng Hưởng ước tính vượt quá mười năm.
+Phân tích phổ tần số cho thấy Cộng Hưởng chính của cô ấy nghiêng về lửa. Tuy nhiên, các đặc điểm chồng chéo trên nhiều dấu hiệu phổ tiêu chuẩn đã khiến việc phân loại nguồn gốc chính xác trở nên bất khả thi.
+Đấu sĩ này đã thể hiện sự gia tăng ổn định cả về sức mạnh lẫn độ chính xác của khả năng trong suốt sự nghiệp thi đấu.
+&lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; nằm ở bên trái eo của đấu sĩ. Sự Thức Tỉnh Cộng Hưởng đi kèm với các đặc điểm biến đổi một phần giống sói. Ngoài chiếc đuôi có thể nhìn thấy, đấu sĩ tự báo cáo về sự nhạy bén gia tăng của khứu giác và thính giác.
 &lt;i&gt;"Đánh giá hoàn tất. Cảm ơn sự hợp tác của Đấu Sĩ Lupa.
 …À, còn một chuyện nữa... Con gái tôi rất thích xem các trận đấu của cô. Không biết cô có thể cho tôi xin chữ ký được không?"&lt;/i&gt;</t>
         </is>
@@ -22734,10 +22734,10 @@
 Cô đứng đó một lúc, ngẩn người, rồi bước tiếp vào căn phòng tối om. Forte của cô đã ban cho cô nhiều thứ: ngọn lửa, khứu giác nhạy bén, và khả năng nhìn trong bóng tối. Không chút do dự, Lupa tiến đến một chiếc ghế và ngồi xuống, lặng lẽ hòa vào màn đêm.
 "Thôi," cô nghĩ, "Domina hay quản lý sẽ sớm cử người mới tới thôi."
 Trò hề này cuối cùng cũng kết thúc.
-Họ đã tìm ra gián điệp, kẻ đã để lộ bí mật của đội, nguồn cơn của những lời đồn đại. Julia không phải dạng nhân từ. Vì thế, kẻ đồng đội cũ đã phản bội họ chắc chắn sẽ bị cấm đặt chân lên bất kỳ đấu trường nào trên Capitoline Hill trong một thời gian rất dài.
+Họ đã tìm ra gián điệp, kẻ đã để lộ bí mật của đội, nguồn cơn của những lời đồn đại. Julia không phải dạng nhân từ. Vì thế, kẻ đồng đội cũ đã phản bội họ chắc chắn sẽ bị cấm đặt chân lên bất kỳ đấu trường nào trên Đồi Capitoline trong một thời gian rất dài.
 Qua bao năm tháng, danh tiếng của Lupa ngày càng lớn, đồng đội của cô đến rồi đi. Có người không theo kịp cách cô chiến đấu. Số khác bị sa thải chỉ vì Julia không ưa. Một vài kẻ, như đồng đội cũ của cô, ngay từ đầu đã mang theo ý đồ xấu. Và cũng có những người... đơn giản là không thể chịu nổi việc tiếng hò reo của đám đông luôn hướng về cô, để họ chìm trong bóng tối.
 Lupa đã cố nói gì đó về chuyện này, nhưng cô nhanh chóng nhận ra rằng ngay cả việc "cố nói" cũng có thể sắc như lưỡi dao.
-Có lẽ vì cô chưa bao giờ thực sự ở trong hoàn cảnh của họ. Suy cho cùng, cô chưa từng nếm trải thất bại. Hoặc có lẽ là vì cái nhìn "Ngươi sẽ chẳng bao giờ hiểu cảm giác đó đâu", và sự thật rằng, khi khói lửa tan đi, cô luôn là người đứng trên đỉnh.
+Có lẽ vì cô chưa bao giờ thực sự ở trong hoàn cảnh của họ. Suy cho cùng, cô chưa từng nếm trải thất bại. Hoặc có lẽ là vì cái nhìn "Mày sẽ chẳng bao giờ hiểu cảm giác đó đâu", và sự thật rằng, khi khói lửa tan đi, cô luôn là người đứng trên đỉnh.
 Dần dần, Lupa học cách im lặng.
 Ngồi thêm một lúc nữa, cô đứng dậy và đi đến tủ chứa các bản ghi trận đấu. Từ giá sách, cô rút ra một bản ghi mà cô đã xem đi xem lại nhiều lần. Có lẽ đó là một cách tự an ủi bản thân, bám víu vào ý nghĩ rằng ngay cả những kẻ không có tài năng vẫn có thể tìm thấy niềm vui trên đấu trường, dù cho Chiến Binh trong bản ghi đó không trụ được lâu và biến mất khỏi đấu trường quá đột ngột.
 Ánh sáng từ Breen the Screen nhấp nháy trên khuôn mặt Lupa, để lại những khoảng tối sâu thẳm, trống rỗng.</t>
@@ -22808,7 +22808,7 @@
       <c r="M337" t="inlineStr">
         <is>
           <t>Cartethyia truy đuổi kẻ địch từ lồng ấp qua những con phố Septimont bị Hắc Triều tàn phá cho đến khi hắn biến mất.
-Trước mắt cô là Guardian Septimont đã gục ngã, ngọn kích giơ cao trong tiếng hô chiến. Cartethyia rút kiếm, như vô số lần cô đã làm trong Tower Ngược khi đối mặt với những sinh vật dị dạng của Hắc Triều. Cô đánh bại Sư Tử Glory, nhưng sau khi xử lý Hắc Triều trước mặt, cô cảm nhận được ánh mắt lạnh lẽo từ phía sau.
+Trước mắt cô là Người Bảo Vệ Septimont đã gục ngã, ngọn kích giơ cao trong tiếng hô chiến. Cartethyia rút kiếm, như vô số lần cô đã làm trong Tháp Ngược khi đối mặt với những sinh vật dị dạng của Hắc Triều. Cô đánh bại Sư Tử Vinh Quang, nhưng sau khi xử lý Hắc Triều trước mặt, cô cảm nhận được ánh mắt lạnh lẽo từ phía sau.
 Cartethyia quay lại và thấy cô gái Đấu Sĩ, khuôn mặt bị Tidal Blight làm biến dạng, đôi mắt trống rỗng như hồn ma. Cô ta nhìn chằm chằm, không chớp mắt, như một bóng ma.</t>
         </is>
       </c>
@@ -22878,7 +22878,7 @@
         <is>
           <t>Máu sôi lên, thể xác và linh hồn bừng cháy trong lò lửa chiến trận. Ngọn giáo của Lupa đâm xuyên qua sinh vật nửa người nửa biển quái dị, trận chiến của nàng diễn ra trên sân khấu ảo ảnh. Tâm trí nàng bình thản khi thế giới dần tan biến. Chỉ còn kẻ thù, vũ khí và chính mình.
 Nỗi thống khổ của Chiến Binh Đấu Trường, bị gián đoạn hàng thập kỷ trước bởi sự tha hóa của Threnodian, cuối cùng cũng đi đến hồi kết.
-Khoảnh khắc này, Lupa không còn bị gánh nặng của sức mạnh, yếu đuối, Sentinel hay Threnodian đè Dodgen. Chỉ còn một suy nghĩ thuần khiết: Trở thành Chiến Binh Đấu Trường là niềm vui sướng!</t>
+Khoảnh khắc này, Lupa không còn bị gánh nặng của sức mạnh, yếu đuối, Sentinel hay Threnodian đè nén. Chỉ còn một suy nghĩ thuần khiết: Trở thành Chiến Binh Đấu Trường là niềm vui sướng!</t>
         </is>
       </c>
     </row>
@@ -23008,7 +23008,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Kích hoạt hoàn toàn Chuỗi Resonance của Cartethyia</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Cartethyia</t>
         </is>
       </c>
     </row>
@@ -23073,7 +23073,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Kích hoạt đầy đủ Resonance Chain của Lupa</t>
+          <t>Kích hoạt toàn bộ Resonance Chain của Lupa</t>
         </is>
       </c>
     </row>
@@ -23203,7 +23203,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Mỗi lần Resonators hiện tại sử dụng &lt;color=#ffb04a&gt;Echo Skill&lt;/color&gt; sẽ tăng 5% Tấn Công cho tất cả Resonators trong đội, tối đa 6 lần cộng dồn.</t>
+          <t>Mỗi lần Resonator hiện tại sử dụng &lt;color=#ffb04a&gt;Kỹ Năng Echo&lt;/color&gt; sẽ tăng 5% ATK cho tất cả Resonator trong đội, tối đa 6 lần cộng dồn.</t>
         </is>
       </c>
     </row>
@@ -23268,7 +23268,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Fusion DMG Bonus thêm 10%. Khi thi triển &lt;color=#ffb04a&gt;Intro Skill&lt;/color&gt;, gây 600% Fusion DMG lên kẻ địch xung quanh.</t>
+          <t>Tăng Sát Thương Fusion thêm 10%. Khi thi triển &lt;color=#ffb04a&gt;Kỹ Năng Khởi Động&lt;/color&gt;, gây 600% Sát Thương Fusion lên kẻ địch xung quanh.</t>
         </is>
       </c>
     </row>
@@ -23398,7 +23398,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Nhận 1 lần &lt;te href=851012&gt;&lt;color=#c79f49&gt;Echo Recruitment&lt;/color&gt;&lt;/te&gt;. Tối đa 1 lần mỗi Giai Đoạn. Số lần không dùng sẽ không được chuyển sang Giai Đoạn tiếp theo.</t>
+          <t>Nhận 1 lần &lt;te href=851012&gt;&lt;color=#c79f49&gt;Tuyển Mộ Cộng Hưởng&lt;/color&gt;&lt;/te&gt;. Tối đa 1 lần mỗi Giai Đoạn. Số lần không dùng sẽ không được chuyển sang Giai Đoạn tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -23463,7 +23463,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Tạm thời tăng sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; của tất cả Echoes lên một lượng bằng số Giai đoạn hiện tại trong 3 ngày. Tối đa một lần mỗi Giai đoạn. Số lần chưa sử dụng sẽ không được chuyển sang Giai đoạn tiếp theo.</t>
+          <t>Tạm thời tăng sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Phiếu Hằng Ngày&lt;/color&gt;&lt;/te&gt; của tất cả Echo lên một lượng bằng số Phase hiện tại trong 3 ngày. Tối đa một lần mỗi Phase. Số lần chưa sử dụng sẽ không được chuyển sang Phase tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -23528,7 +23528,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Remove tất cả Echoes trên chiến trường và nhận &lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Coupons&lt;/color&gt;&lt;/te&gt; bằng 3 lần tổng sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; của các Echoes bị gỡ, sau đó tái tạo lại 100% Echoes. Tối đa 3 lần mỗi Giai Đoạn.</t>
+          <t>Gỡ bỏ tất cả Echo trên chiến trường và nhận &lt;te href=851010&gt;&lt;color=#c79f49&gt;Phiếu Dreamland&lt;/color&gt;&lt;/te&gt; bằng 3 lần tổng sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Phiếu Hằng Ngày&lt;/color&gt;&lt;/te&gt; của các Echo bị gỡ, sau đó tái tạo lại 100% Echo. Tối đa 3 lần mỗi Giai Đoạn.</t>
         </is>
       </c>
     </row>
@@ -23593,7 +23593,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Xáo trộn ngẫu nhiên vị trí của tất cả Echoes trên chiến trường, và chúng sẽ xuất hiện lại ở vị trí mới vào ngày hôm sau. Tối đa 3 lần mỗi Giai Đoạn. Số lần chưa dùng sẽ không được chuyển sang Giai Đoạn tiếp theo.</t>
+          <t>Xáo trộn ngẫu nhiên vị trí của tất cả Echo trên chiến trường, và chúng sẽ xuất hiện lại ở vị trí mới vào ngày hôm sau. Tối đa 3 lần mỗi Giai Đoạn. Số lần chưa dùng sẽ không được chuyển sang Giai Đoạn tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -23788,7 +23788,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Giới hạn hàng tuần Duel Resonance</t>
+          <t>Giới Hạn Hàng Tuần Cộng Hưởng Đối Kháng</t>
         </is>
       </c>
     </row>
@@ -23918,7 +23918,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Sát thương nhận vào giảm {0}.</t>
+          <t>DMG nhận vào giảm {0}.</t>
         </is>
       </c>
     </row>
@@ -24048,7 +24048,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Tiêu hao tổng cộng 1600 Astrites.</t>
+          <t>Tiêu tốn tổng cộng 1600 Astrites.</t>
         </is>
       </c>
     </row>
@@ -24113,7 +24113,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Mở khóa tổng cộng 5 Resonance Nexus.</t>
+          <t>Mở khóa tổng cộng 5 Resonance Nexus</t>
         </is>
       </c>
     </row>
@@ -24243,7 +24243,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Tiêu hao tổng cộng 240 Waveplates.</t>
+          <t>Tiêu tốn tổng cộng 240 Waveplate.</t>
         </is>
       </c>
     </row>
@@ -24308,7 +24308,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Hoàn thành hướng dẫn Dodge hoặc Outro Skill.</t>
+          <t>Hoàn thành hướng dẫn Né Tránh hoặc Kỹ Năng Outro.</t>
         </is>
       </c>
     </row>
@@ -24373,7 +24373,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Đã hoàn thành Mục Tiêu Giai Đoạn, trừ số Dreamland Coupons tương đương với doanh thu mục tiêu.</t>
+          <t>Đã hoàn thành Mục Tiêu Giai Đoạn, trừ số Dreamland Coupon tương đương với doanh thu mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -24503,7 +24503,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Invisibility&lt;/color&gt; &lt;color=#fb6464&gt;(Unactivated)&lt;/color&gt; - Trong {0} giây đầu Battle Stage và cho đến khi gây sát thương, Echo này không thể bị tấn công. Sau khi Tàng Hình kết thúc, sát thương gây ra bởi Echo này tăng thêm {2} trong {1} giây.</t>
+          <t>&lt;color=#e4c69b&gt;Tàng Hình&lt;/color&gt; &lt;color=#fb6464&gt;(Chưa kích hoạt)&lt;/color&gt; - Trong {0} giây đầu Giai Đoạn Chiến Đấu và cho đến khi gây sát thương, Tổ Tacet này không thể bị tấn công. Sau khi Tàng Hình kết thúc, sát thương gây ra bởi Tổ Tacet này tăng thêm {2} trong {1} giây.</t>
         </is>
       </c>
     </row>
@@ -24568,7 +24568,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Toughness&lt;/color&gt; &lt;color=#fb6464&gt;(Unactivated)&lt;/color&gt; - Khi Resonator bị tấn công trong Battle Stage, sát thương nhận vào giảm {0} trong {1} giây. Cooldown chiêu sẽ được đặt lại thay vì chồng chất nếu kích hoạt lại.</t>
+          <t>&lt;color=#e4c69b&gt;Kiên Cường&lt;/color&gt; &lt;color=#fb6464&gt;(Chưa kích hoạt)&lt;/color&gt; - Khi Cộng Hưởng Giả bị tấn công trong Giai Đoạn Chiến Đấu, DMG nhận vào giảm {0} trong {1} giây. Thời gian hồi chiêu sẽ được đặt lại thay vì chồng chất nếu kích hoạt lại.</t>
         </is>
       </c>
     </row>
@@ -24633,7 +24633,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Mimic&lt;/color&gt; &lt;color=#fb6464&gt;(Unactivated)&lt;/color&gt; - Khi Echo này kích hoạt Kỹ Năng Special tiếp theo thông qua Điều Tần, Bắt Chước sẽ biến thành kỹ năng đó.</t>
+          <t>&lt;color=#e4c69b&gt;Bắt Chước&lt;/color&gt; &lt;color=#fb6464&gt;(Chưa kích hoạt)&lt;/color&gt; - Khi Tổ Tacet này kích hoạt Kỹ Năng Đặc Biệt tiếp theo thông qua Điều Tần, Bắt Chước sẽ biến thành kỹ năng đó.</t>
         </is>
       </c>
     </row>
@@ -24698,7 +24698,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Explosion&lt;/color&gt; &lt;color=#fb6464&gt;(Unactivated)&lt;/color&gt; - Khi Tacet Discord này bị hạ gục trong Battle Stage, nó sẽ phát nổ và gây sát thương lên các Tacet Discord địch xung quanh.</t>
+          <t>&lt;color=#e4c69b&gt;Explosion&lt;/color&gt; &lt;color=#fb6464&gt;(Chưa kích hoạt)&lt;/color&gt; - Khi Tacet Discord này bị hạ gục trong Giai Đoạn Chiến Đấu, nó sẽ phát nổ và gây sát thương lên các Tacet Discord địch xung quanh.</t>
         </is>
       </c>
     </row>
@@ -24763,7 +24763,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Restraint&lt;/color&gt; &lt;color=#fb6464&gt;(Unactivated)&lt;/color&gt; - Khi Giai Đoạn Triển Khai kết thúc, Resonator địch ở cùng vị trí với Resonator này (Hàng Trước hoặc Hàng Sau) sẽ mất {0} Strength trong lượt này.</t>
+          <t>&lt;color=#e4c69b&gt;Kiềm Chế&lt;/color&gt; &lt;color=#fb6464&gt;(Chưa kích hoạt)&lt;/color&gt; - Khi Giai Đoạn Triển Khai kết thúc, Cộng Hưởng Giả địch ở cùng vị trí với Cộng Hưởng Giả này (Hàng Trước hoặc Hàng Sau) sẽ mất {0} Sức Mạnh trong lượt này.</t>
         </is>
       </c>
     </row>
@@ -24828,7 +24828,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Last Stand&lt;/color&gt; &lt;color=#fb6464&gt;(Unactivated)&lt;/color&gt; - Nếu HP của ngươi còn {0} hoặc thấp hơn khi Giai Đoạn Triển Khai kết thúc, Echo này sẽ gây thêm {1} Sát Thương lên Echo địch trong Battle Stage kế tiếp.</t>
+          <t>&lt;color=#e4c69b&gt;Bất Khuất&lt;/color&gt; &lt;color=#fb6464&gt;(Chưa kích hoạt)&lt;/color&gt; - Nếu HP của ngươi còn {0} hoặc thấp hơn khi Giai Đoạn Triển Khai kết thúc, Tổ Tacet này sẽ gây thêm {1} Sát Thương lên Tổ Tacet địch trong Giai Đoạn Chiến Đấu kế tiếp.</t>
         </is>
       </c>
     </row>
@@ -24893,7 +24893,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Berserk&lt;/color&gt; &lt;color=#fb6464&gt;(Unactivated)&lt;/color&gt; - Nếu HP của Tacet Discord này giảm xuống còn {0} hoặc thấp hơn trong Battle Stage, nó sẽ gây thêm {1} Sát Thương lên các Tacet Discord địch trong giai đoạn này.</t>
+          <t>&lt;color=#e4c69b&gt;Berserk&lt;/color&gt; &lt;color=#fb6464&gt;(Chưa kích hoạt)&lt;/color&gt; - Nếu HP của Tacet Discord này giảm xuống còn {0} hoặc thấp hơn trong Giai Đoạn Chiến Đấu, nó sẽ gây thêm {1} Sát Thương lên các Tacet Discord địch trong giai đoạn này.</t>
         </is>
       </c>
     </row>
@@ -24958,7 +24958,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Forestall&lt;/color&gt; &lt;color=#fb6464&gt;(Unactivated)&lt;/color&gt; - Khi Battle Stage bắt đầu, Echo này gây thêm {0} Sát Thương lên Echo địch trong {1} giây.</t>
+          <t>&lt;color=#e4c69b&gt;Chặn Đầu&lt;/color&gt; &lt;color=#fb6464&gt;(Chưa kích hoạt)&lt;/color&gt; - Khi Giai Đoạn Chiến Đấu bắt đầu, Tổ Tacet này gây thêm {0} Sát Thương lên Tổ Tacet địch trong {1} giây.</t>
         </is>
       </c>
     </row>
@@ -25023,7 +25023,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Taunt&lt;/color&gt; &lt;color=#fb6464&gt;(Unactivated)&lt;/color&gt; - Khi ở Hàng Trước, Resonator địch sẽ tấn công Resonator này trước trong Battle Stage.</t>
+          <t>&lt;color=#e4c69b&gt;Khiêu Khích&lt;/color&gt; &lt;color=#fb6464&gt;(Chưa kích hoạt)&lt;/color&gt; - Khi ở Hàng Trước, Cộng Hưởng Giả địch sẽ tấn công Cộng Hưởng Giả này trước trong Giai Đoạn Chiến Đấu.</t>
         </is>
       </c>
     </row>
@@ -25088,7 +25088,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Boost&lt;/color&gt; &lt;color=#fb6464&gt;(Unactivated)&lt;/color&gt; - Khi Giai Đoạn Triển Khai kết thúc, sức mạnh của Tacet Discord này sẽ tăng thêm {0} trong {1} lượt, có thể chồng chất lên đến {2} lần. Hiệu ứng này cũng áp dụng cho các Tacet Discord đã Điều Chỉnh.</t>
+          <t>&lt;color=#e4c69b&gt;Boost&lt;/color&gt; &lt;color=#fb6464&gt;(Chưa kích hoạt)&lt;/color&gt; - Khi Giai Đoạn Triển Khai kết thúc, sức mạnh của Tacet Discord này sẽ tăng thêm {0} trong {1} lượt, có thể chồng chất lên đến {2} lần. Hiệu ứng này cũng áp dụng cho các Tacet Discord đã Điều Chỉnh.</t>
         </is>
       </c>
     </row>
@@ -25153,7 +25153,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Flank Force&lt;/color&gt; &lt;color=#fb6464&gt;(Unactivated)&lt;/color&gt; - Khi Echo này ở Khu Triển Khai (cả Hàng Tiền hoặc Hàng Hậu) cùng hai another Echo, tất cả sẽ nhận {0} Sát Thương khi Giai Đoạn Triển Khai kết thúc, hiệu lực đến hết lượt đấu.</t>
+          <t>&lt;color=#e4c69b&gt;Lực Lượng Cánh&lt;/color&gt; &lt;color=#fb6464&gt;(Chưa kích hoạt)&lt;/color&gt; - Khi Tổ Tacet này ở Khu Triển Khai (cả Hàng Tiền hoặc Hàng Hậu) cùng hai Tổ Tacet khác, tất cả sẽ nhận {0} Sát Thương khi Giai Đoạn Triển Khai kết thúc, hiệu lực đến hết lượt đấu.</t>
         </is>
       </c>
     </row>
@@ -25218,7 +25218,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Superpower&lt;/color&gt; &lt;color=#fb6464&gt;(Unactivated)&lt;/color&gt; - Với mỗi Kỹ Năng Special mà Resonator này sở hữu, nó gây thêm {0} Sát Thương lên Resonator địch trong Battle Stage, cộng dồn tối đa {1} lần.</t>
+          <t>&lt;color=#e4c69b&gt;Siêu Năng Lực&lt;/color&gt; &lt;color=#fb6464&gt;(Chưa kích hoạt)&lt;/color&gt; - Với mỗi Kỹ Năng Đặc Biệt mà Cộng Hưởng Giả này sở hữu, nó gây thêm {0} Sát Thương lên Cộng Hưởng Giả địch trong Giai Đoạn Chiến Đấu, cộng dồn tối đa {1} lần.</t>
         </is>
       </c>
     </row>
@@ -25283,7 +25283,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Mỗi khi sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; của các loại another Echo trên chiến trường tăng lên, sản lượng Daily Coupon của chính nó cũng tăng thêm {0}. Hiệu ứng này có thể kích hoạt tối đa {1} lần mỗi ngày.</t>
+          <t>Mỗi khi sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Phiếu Hằng Ngày&lt;/color&gt;&lt;/te&gt; của các loại Tổ Tacet khác trên chiến trường tăng lên, sản lượng Phiếu Hằng Ngày của chính nó cũng tăng thêm {0}. Hiệu ứng này có thể kích hoạt tối đa {1} lần mỗi ngày.</t>
         </is>
       </c>
     </row>
@@ -25413,7 +25413,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>&lt;te href=851006&gt;&lt;color=#c79f49&gt;Devour&lt;/color&gt;&lt;/te&gt;: Mỗi ngày, Devour &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=Echoes P=Echoes SapTag=0} &lt;te href=851055&gt;&lt;color=#c79f49&gt;adjacent&lt;/color&gt;&lt;/te&gt; và nhận sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; của mục tiêu bị Devour. Khi Devour Echoes cùng thuộc tính Dream, có {1}% cơ hội Devour tiếp. Mỗi ngày có thể Devour tối đa &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2}.</t>
+          <t>&lt;te href=851006&gt;&lt;color=#c79f49&gt;Devour&lt;/color&gt;&lt;/te&gt;: Mỗi ngày, Devour &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=Echo P=Echoes SapTag=0} &lt;te href=851055&gt;&lt;color=#c79f49&gt;liền kề&lt;/color&gt;&lt;/te&gt; và nhận sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; của mục tiêu bị Devour. Khi Devour Echo cùng thuộc tính Dream, có {1}% cơ hội Devour tiếp. Mỗi ngày có thể Devour tối đa &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2}.</t>
         </is>
       </c>
     </row>
@@ -25478,7 +25478,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>&lt;te href=851006&gt;&lt;color=#c79f49&gt;Devour&lt;/color&gt;&lt;/te&gt;: Mỗi ngày, Devour từ {0} đến {1} Echo &lt;te href=851055&gt;&lt;color=#c79f49&gt;adjacent&lt;/color&gt;&lt;/te&gt; hiếm cấp xám hoặc xanh dương và nhận {2}% sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; của mục tiêu bị Devour.</t>
+          <t>&lt;te href=851006&gt;&lt;color=#c79f49&gt;Devour&lt;/color&gt;&lt;/te&gt;: Mỗi ngày, Devour từ {0} đến {1} Echo &lt;te href=851055&gt;&lt;color=#c79f49&gt;liền kề&lt;/color&gt;&lt;/te&gt; hiếm cấp xám hoặc xanh dương và nhận {2}% sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; của mục tiêu bị Devour.</t>
         </is>
       </c>
     </row>
@@ -25543,7 +25543,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>&lt;te href=851006&gt;&lt;color=#c79f49&gt;Devour&lt;/color&gt;&lt;/te&gt;: Mỗi ngày, Devour &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=Echoes P=Echoes SapTag=0} &lt;te href=851055&gt;&lt;color=#c79f49&gt;adjacent&lt;/color&gt;&lt;/te&gt; hiếm cấp xám hoặc xanh dương và nhận sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; của mục tiêu bị Devour. Echoes &lt;te href=851050&gt;&lt;color=#c79f49&gt;Prism&lt;/color&gt;&lt;/te&gt; sẽ được ưu tiên Devour trước.</t>
+          <t>&lt;te href=851006&gt;&lt;color=#c79f49&gt;Devour&lt;/color&gt;&lt;/te&gt;: Mỗi ngày, Devour &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=Echo P=Echoes SapTag=0} &lt;te href=851055&gt;&lt;color=#c79f49&gt;liền kề&lt;/color&gt;&lt;/te&gt; hiếm cấp xám hoặc xanh dương và nhận sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; của mục tiêu bị Devour. Echo &lt;te href=851050&gt;&lt;color=#c79f49&gt;Prism&lt;/color&gt;&lt;/te&gt; sẽ được ưu tiên Devour trước.</t>
         </is>
       </c>
     </row>
@@ -25608,7 +25608,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Khi &lt;te href=851006&gt;&lt;color=#c79f49&gt;Devoured&lt;/color&gt;&lt;/te&gt;, sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; của các &lt;te href=851055&gt;&lt;color=#c79f49&gt;adjacent&lt;/color&gt;&lt;/te&gt; &lt;te href=851050&gt;&lt;color=#c79f49&gt;Prism&lt;/color&gt;&lt;/te&gt; tăng thêm {0}.</t>
+          <t>Khi &lt;te href=851006&gt;&lt;color=#c79f49&gt;Bị Tiêu Hóa&lt;/color&gt;&lt;/te&gt;, sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Phiếu Hằng Ngày&lt;/color&gt;&lt;/te&gt; của các &lt;te href=851055&gt;&lt;color=#c79f49&gt;Prism Echo&lt;/color&gt;&lt;/te&gt; &lt;te href=851050&gt;&lt;color=#c79f49&gt;lân cận&lt;/color&gt;&lt;/te&gt; tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -25673,7 +25673,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Khi một &lt;te href=851055&gt;&lt;color=#c79f49&gt;adjacent&lt;/color&gt;&lt;/te&gt; &lt;te href=851050&gt;&lt;color=#c79f49&gt;Prism&lt;/color&gt;&lt;/te&gt; bị &lt;te href=851006&gt;&lt;color=#c79f49&gt;Devoured&lt;/color&gt;&lt;/te&gt;, tăng sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; của Echo này lên {0}.</t>
+          <t>Khi một &lt;te href=851055&gt;&lt;color=#c79f49&gt;Echo Lân Cận&lt;/color&gt;&lt;/te&gt; &lt;te href=851050&gt;&lt;color=#c79f49&gt;Prism&lt;/color&gt;&lt;/te&gt; bị &lt;te href=851006&gt;&lt;color=#c79f49&gt;Nuốt Chửng&lt;/color&gt;&lt;/te&gt;, tăng sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Phiếu Hằng Ngày&lt;/color&gt;&lt;/te&gt; của Echo này lên {0}.</t>
         </is>
       </c>
     </row>
@@ -25740,9 +25740,9 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Hồi Âm này không thể bị &lt;te href=851006&gt;&lt;color=#c79f49&gt;Devoured&lt;/color&gt;&lt;/te&gt;.
-&lt;te href=851005&gt;&lt;color=#c79f49&gt;Gradation&lt;/color&gt;&lt;/te&gt;: Thăng Cấp diễn ra mỗi {0} ngày và tăng sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; của Hồi Âm này lên {1}.
-&lt;te href=851006&gt;&lt;color=#c79f49&gt;Devour&lt;/color&gt;&lt;/te&gt;: Mỗi ngày, Nuốt Chửng &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; &lt;te href=851055&gt;&lt;color=#c79f49&gt;adjacent&lt;/color&gt;&lt;/te&gt; {Cus:Sap,S=Echoes P=Echoes SapTag=2} và nhận sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; từ mục tiêu bị Nuốt Chửng. Khi Nuốt Chửng Hồi Âm cùng thuộc tính Giấc Mơ, có {3}% cơ hội Nuốt Chửng thêm lần nữa. Mỗi ngày có thể Nuốt Chửng tối đa {4} lần và kế thừa tiến trình Thăng Cấp của mục tiêu bị Nuốt Chửng.</t>
+          <t>Hồi Âm này không thể bị &lt;te href=851006&gt;&lt;color=#c79f49&gt;Nuốt Chửng&lt;/color&gt;&lt;/te&gt;.
+&lt;te href=851005&gt;&lt;color=#c79f49&gt;Thăng Cấp&lt;/color&gt;&lt;/te&gt;: Thăng Cấp diễn ra mỗi {0} ngày và tăng sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Phiếu Hằng Ngày&lt;/color&gt;&lt;/te&gt; của Hồi Âm này lên {1}.
+&lt;te href=851006&gt;&lt;color=#c79f49&gt;Nuốt Chửng&lt;/color&gt;&lt;/te&gt;: Mỗi ngày, Nuốt Chửng &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; &lt;te href=851055&gt;&lt;color=#c79f49&gt;Hồi Âm kế cận&lt;/color&gt;&lt;/te&gt; {Cus:Sap,S=Echo P=Echoes SapTag=2} và nhận sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Phiếu Hằng Ngày&lt;/color&gt;&lt;/te&gt; từ mục tiêu bị Nuốt Chửng. Khi Nuốt Chửng Hồi Âm cùng thuộc tính Giấc Mơ, có {3}% cơ hội Nuốt Chửng thêm lần nữa. Mỗi ngày có thể Nuốt Chửng tối đa {4} lần và kế thừa tiến trình Thăng Cấp của mục tiêu bị Nuốt Chửng.</t>
         </is>
       </c>
     </row>
@@ -25807,7 +25807,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>&lt;te href=851006&gt;&lt;color=#c79f49&gt;Devour&lt;/color&gt;&lt;/te&gt;: Mỗi ngày, Devour &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=Echoes P=Echoes SapTag=0} và nhận sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; của mục tiêu bị Devour. Khi Devour Echoes, nhận &lt;te href=851011&gt;&lt;color=#c79f49&gt;Frequency Crystals&lt;/color&gt;&lt;/te&gt; dựa trên độ hiếm của mục tiêu (Xám: 1, Xanh dương: 1, Purple: 2, Vàng: 3).</t>
+          <t>&lt;te href=851006&gt;&lt;color=#c79f49&gt;Devour&lt;/color&gt;&lt;/te&gt;: Mỗi ngày, Devour &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=Echo P=Echoes SapTag=0} và nhận sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; của mục tiêu bị Devour. Khi Devour Echo, nhận &lt;te href=851011&gt;&lt;color=#c79f49&gt;Frequency Crystal&lt;/color&gt;&lt;/te&gt; dựa trên độ hiếm của mục tiêu (Xám: 1, Xanh dương: 1, Tím: 2, Vàng: 3).</t>
         </is>
       </c>
     </row>
@@ -25872,7 +25872,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>&lt;te href=851007&gt;&lt;color=#c79f49&gt;Exchange&lt;/color&gt;&lt;/te&gt;: Sau &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=ngày P=ngày SapTag=0}, tự &lt;te href=851041&gt;&lt;color=#c79f49&gt;Remove&lt;/color&gt;&lt;/te&gt; chính mình dưới dạng &lt;te href=851013&gt;&lt;color=#c79f49&gt;Item of Exchange&lt;/color&gt;&lt;/te&gt;. Khi bị &lt;te href=851006&gt;&lt;color=#c79f49&gt;Devoured&lt;/color&gt;&lt;/te&gt; hoặc Exchange, tạo một &lt;te href=851063&gt;&lt;color=#c79f49&gt;Dream Block: Watermirror&lt;/color&gt;&lt;/te&gt; tại ô trống và tăng sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; của &lt;te href=851049&gt;&lt;color=#c79f49&gt;Chop Chops&lt;/color&gt;&lt;/te&gt; thêm {1}% sản lượng Daily Coupon của Echo này.</t>
+          <t>Trao Đổi: Sau &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=ngày P=ngày SapTag=0}, tự &lt;te href=851041&gt;&lt;color=#c79f49&gt;loại bỏ&lt;/color&gt;&lt;/te&gt; khỏi danh sách &lt;te href=851013&gt;&lt;color=#c79f49&gt;Vật Phẩm Trao Đổi&lt;/color&gt;&lt;/te&gt;. Khi bị &lt;te href=851006&gt;&lt;color=#c79f49&gt;Nuốt Chửng&lt;/color&gt;&lt;/te&gt; hoặc Trao Đổi, tạo ra một &lt;te href=851063&gt;&lt;color=#c79f49&gt;Khối Mộng Ảnh: Gương Nước&lt;/color&gt;&lt;/te&gt; ở ô trống và tăng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Phiếu Hằng Ngày&lt;/color&gt;&lt;/te&gt; thu được từ &lt;te href=851049&gt;&lt;color=#c79f49&gt;Chop Chops&lt;/color&gt;&lt;/te&gt; lên {1}% sản lượng Phiếu Hằng Ngày của Tiếng Vọng này.</t>
         </is>
       </c>
     </row>
@@ -25937,7 +25937,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>&lt;te href=851007&gt;&lt;color=#c79f49&gt;Exchange&lt;/color&gt;&lt;/te&gt;: Sau &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=ngày P=ngày SapTag=0}, tự &lt;te href=851041&gt;&lt;color=#c79f49&gt;Remove&lt;/color&gt;&lt;/te&gt; bản thân khỏi danh sách &lt;te href=851013&gt;&lt;color=#c79f49&gt;Item of Exchange&lt;/color&gt;&lt;/te&gt;. Khi được Exchange, tăng sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; của các Echoes &lt;te href=851055&gt;&lt;color=#c79f49&gt;adjacent&lt;/color&gt;&lt;/te&gt; liền kề thêm {1}% sản lượng Daily Coupon của Echoes này. Echoes này không thể nhận được thông qua &lt;te href=851012&gt;&lt;color=#c79f49&gt;Echo Recruitment&lt;/color&gt;&lt;/te&gt;.</t>
+          <t>Trao Đổi: Sau &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=ngày P=ngày SapTag=0}, tự &lt;te href=851041&gt;&lt;color=#c79f49&gt;loại bỏ&lt;/color&gt;&lt;/te&gt; khỏi danh sách &lt;te href=851013&gt;&lt;color=#c79f49&gt;Vật Phẩm Trao Đổi&lt;/color&gt;&lt;/te&gt;. Khi được Trao Đổi, tăng sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Phiếu Hằng Ngày&lt;/color&gt;&lt;/te&gt; của các Tiếng Vọng &lt;te href=851055&gt;&lt;color=#c79f49&gt;lân cận&lt;/color&gt;&lt;/te&gt; lên {1}% sản lượng Phiếu Hằng Ngày của Tiếng Vọng này. Không thể nhận được Tiếng Vọng này qua &lt;te href=851012&gt;&lt;color=#c79f49&gt;Tuyển Mộ Tiếng Vọng&lt;/color&gt;&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -26002,7 +26002,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Mỗi khi một Echo &lt;te href=851041&gt;&lt;color=#c79f49&gt;Removes&lt;/color&gt;&lt;/te&gt;, sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; của các Echo &lt;te href=851055&gt;&lt;color=#c79f49&gt;adjacent&lt;/color&gt;&lt;/te&gt; sẽ tạm thời tăng thêm {0} trong &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=ngày P=ngày SapTag=1}.</t>
+          <t>Mỗi khi một Tổ Tacet &lt;te href=851041&gt;&lt;color=#c79f49&gt;biến mất&lt;/color&gt;&lt;/te&gt;, sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Phiếu Hằng Ngày&lt;/color&gt;&lt;/te&gt; của các Tổ Tacet &lt;te href=851055&gt;&lt;color=#c79f49&gt;lân cận&lt;/color&gt;&lt;/te&gt; sẽ tạm thời tăng thêm {0} trong &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=ngày P=ngày SapTag=1}.</t>
         </is>
       </c>
     </row>
@@ -26067,7 +26067,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>&lt;te href=851007&gt;&lt;color=#c79f49&gt;Exchange&lt;/color&gt;&lt;/te&gt;: Sau &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=ngày P=ngày SapTag=0}, tự &lt;te href=851041&gt;&lt;color=#c79f49&gt;Remove&lt;/color&gt;&lt;/te&gt; bản thân khỏi tư cách &lt;te href=851013&gt;&lt;color=#c79f49&gt;Item of Exchange&lt;/color&gt;&lt;/te&gt;. Khi được Exchange, tăng sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; của các Echoes &lt;te href=851055&gt;&lt;color=#c79f49&gt;adjacent&lt;/color&gt;&lt;/te&gt; liền kề thêm {1}% sản lượng Daily Coupon của Echoes này.</t>
+          <t>Trao Đổi: Sau &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=ngày P=ngày SapTag=0}, tự &lt;te href=851041&gt;&lt;color=#c79f49&gt;loại bỏ&lt;/color&gt;&lt;/te&gt; khỏi danh sách &lt;te href=851013&gt;&lt;color=#c79f49&gt;Vật Phẩm Trao Đổi&lt;/color&gt;&lt;/te&gt;. Khi được Trao Đổi, tăng sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Phiếu Hằng Ngày&lt;/color&gt;&lt;/te&gt; của các Tiếng Vọng &lt;te href=851055&gt;&lt;color=#c79f49&gt;lân cận&lt;/color&gt;&lt;/te&gt; lên {1}% sản lượng Phiếu Hằng Ngày của Tiếng Vọng này.</t>
         </is>
       </c>
     </row>
@@ -26132,7 +26132,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Mỗi ngày, có {0}% cơ hội tạo ra &lt;te href=851013&gt;&lt;color=#c79f49&gt;Item of Exchange&lt;/color&gt;&lt;/te&gt; trên ô trống. Xác suất tăng dựa trên số lượng &lt;te href=851055&gt;&lt;color=#c79f49&gt;adjacent&lt;/color&gt;&lt;/te&gt; &lt;te href=851049&gt;&lt;color=#c79f49&gt;Chop Chops&lt;/color&gt;&lt;/te&gt;. Mỗi Chop Chop kề bên sẽ tăng {1}% xác suất, tối đa {2}%.</t>
+          <t>Mỗi ngày, có {0}% cơ hội tạo ra &lt;te href=851013&gt;&lt;color=#c79f49&gt;Vật Phẩm Trao Đổi&lt;/color&gt;&lt;/te&gt; trên ô trống. Xác suất tăng dựa trên số lượng &lt;te href=851055&gt;&lt;color=#c79f49&gt;Chop Chop&lt;/color&gt;&lt;/te&gt; &lt;te href=851049&gt;&lt;color=#c79f49&gt;kề nhau&lt;/color&gt;&lt;/te&gt;. Mỗi Chop Chop kề bên sẽ tăng {1}% xác suất, tối đa {2}%.</t>
         </is>
       </c>
     </row>
@@ -26197,7 +26197,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Hoàn thành Challenge và khôi phục các Điểm Mộng Ảnh Septimont</t>
+          <t>Hoàn thành Thử Thách và khôi phục các Điểm Mộng Ảnh Septimont</t>
         </is>
       </c>
     </row>
@@ -26262,7 +26262,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Chưa chọn mục tiêu tuyển dụng</t>
+          <t>Chưa chọn mục tiêu chiêu mộ</t>
         </is>
       </c>
     </row>
@@ -26392,7 +26392,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Kích hoạt hoàn toàn Chuỗi Resonance của Phrolova</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Phrolova</t>
         </is>
       </c>
     </row>
@@ -26522,7 +26522,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Sát thương Basic Attack</t>
+          <t>DMG Basic Attack</t>
         </is>
       </c>
     </row>
@@ -26587,7 +26587,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -26977,7 +26977,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>DMG dựa trên HP</t>
+          <t>Sát thương dựa trên HP</t>
         </is>
       </c>
     </row>
@@ -27042,7 +27042,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Status Tiêu cực</t>
+          <t>Negative Status</t>
         </is>
       </c>
     </row>
@@ -27172,7 +27172,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Tần suất kích hoạt</t>
+          <t>Tần Số Kích Hoạt</t>
         </is>
       </c>
     </row>
@@ -27432,7 +27432,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>PHÒNG NGỤ</t>
+          <t>DEF</t>
         </is>
       </c>
     </row>
@@ -27566,7 +27566,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Tiêu chí đánh giá: [Báo cáo Resonance RA-F2005-G]</t>
+          <t>Tiêu chí đánh giá: [Báo cáo Cộng Hưởng RA-F2005-G]</t>
         </is>
       </c>
     </row>
@@ -27634,7 +27634,7 @@
       <c r="M411" t="inlineStr">
         <is>
           <t>Đại sảnh đỏ thẫm thường vắng lặng, chỉ có những lá cờ của Giám Sát viên phấp phới trong gió lạnh. Trong số đó, lá cờ mang biểu tượng Lycoris đã phai màu từ lâu, nhưng vẫn bám trụ một cách ngoan cố, không hề rơi xuống. Như hầu hết thành viên Fractsidus đều nhớ, các Giám Sát viên đến rồi đi như những cái bóng, ít ai chọn ở lại nơi này. Nhưng cô ta là người khó nắm bắt nhất trong số họ, và lá cờ chính là dấu vết duy nhất chứng minh sự tồn tại của cô. Cô đã từ bỏ mọi thứ mà một Giám Sát viên có thể đòi hỏi ở đây—không đồ đạc trong phòng, không lời nói thừa thãi. Cô không thuộc về nơi này. Sự lặng lẽ tách biệt khiến cô có vẻ như chẳng đáng để ý, nhưng mỗi khi có ý nghĩ rằng cô có thể bị Fractsidus vứt bỏ—hay Fractsidus đối với cô cũng vậy—thì Lycoris lặng lẽ ấy lại bất ngờ xuất hiện từ bóng tối. Như một đóa hoa sắc nhọn, cô đâm xuyên trái tim kẻ thù, hoàn thành nhiệm vụ, rồi biến mất lần nữa. Không gì ở đây dường như khiến cô quan tâm, và ít ai biết tại sao cô lại gia nhập.
-Chỉ có một nơi trong Fractsidus có thể níu chân cô. Đôi khi, cô đứng trên tầng cao của phòng thí nghiệm, lặng lẽ quan sát quá trình con người hòa nhập với thịt và chi của &lt;te href=850081&gt;Tacet Discords&lt;/te&gt;, hay những tiến bộ của công nghệ &lt;te href=850073&gt;Overclocking&lt;/te&gt;. Cô nhìn ngọn lửa khát khao trong mắt những người tích cực tìm kiếm sự tiến hóa, những cuộc vật lộn để tái sinh. Tiếng reo hò của thành công, tiếng than khóc của thất bại. Như thể cô đang nhìn thấy nhiều hơn thế.
+Chỉ có một nơi trong Fractsidus có thể níu chân cô. Đôi khi, cô đứng trên tầng cao của phòng thí nghiệm, lặng lẽ quan sát quá trình con người hòa nhập với thịt và chi của &lt;te href=850081&gt;Tacet Discord&lt;/te&gt;, hay những tiến bộ của công nghệ &lt;te href=850073&gt;Overclocking&lt;/te&gt;. Cô nhìn ngọn lửa khát khao trong mắt những người tích cực tìm kiếm sự tiến hóa, những cuộc vật lộn để tái sinh. Tiếng reo hò của thành công, tiếng than khóc của thất bại. Như thể cô đang nhìn thấy nhiều hơn thế.
 Nhiều lúc khác, cô lại hiện ra như một bóng ma vào đêm khuya, cầm đèn lướt qua những kết quả nghiên cứu mới nhất. Nhưng cô không lấy đi một trang giấy nào, như thể mọi thứ đều chỉ kết thúc trong thất vọng. Những ai vô tình chứng kiến cảnh này đều bối rối, tự hỏi cô thực sự đang tìm kiếm điều gì.</t>
         </is>
       </c>
@@ -27842,7 +27842,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>&lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Coupons&lt;/color&gt;&lt;/te&gt; nhận được từ các nguồn khác ngoài sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; của Echoes sẽ tăng thêm {0}%.</t>
+          <t>&lt;te href=851010&gt;&lt;color=#c79f49&gt;Phiếu Giấc Mơ&lt;/color&gt;&lt;/te&gt; nhận được từ các nguồn khác ngoài sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Phiếu Hằng Ngày&lt;/color&gt;&lt;/te&gt; của Echo sẽ tăng thêm {0}%.</t>
         </is>
       </c>
     </row>
@@ -27907,7 +27907,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Khi một Echo trải qua &lt;te href=851005&gt;&lt;color=#c79f49&gt;Gradation&lt;/color&gt;&lt;/te&gt;, có {0}% khả năng tăng lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; tạo ra thêm {1}%.</t>
+          <t>Khi một Tổ Tacet trải qua &lt;te href=851005&gt;&lt;color=#c79f49&gt;Tiến Hóa&lt;/color&gt;&lt;/te&gt;, có {0}% khả năng tăng lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Phiếu Hằng Ngày&lt;/color&gt;&lt;/te&gt; tạo ra thêm {1}%.</t>
         </is>
       </c>
     </row>
@@ -27972,7 +27972,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Havoc RES của địch giảm 10%.</t>
+          <t>Kháng Havoc của địch giảm 10%.</t>
         </is>
       </c>
     </row>
@@ -28037,7 +28037,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Fusion RES của địch giảm 10%.</t>
+          <t>Kháng Fusion của địch giảm 10%.</t>
         </is>
       </c>
     </row>
@@ -28102,7 +28102,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Electro RES của địch giảm 10%.</t>
+          <t>Kháng Electro của địch giảm 10%.</t>
         </is>
       </c>
     </row>
@@ -28167,7 +28167,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Khi bất kỳ Echo nào trên chiến trường bị &lt;te href=851041&gt;&lt;color=#c79f49&gt;Removed&lt;/color&gt;&lt;/te&gt;, sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; sẽ tăng thêm {0}, tối đa &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=1} mỗi ngày.</t>
+          <t>Khi bất kỳ Echo nào trên chiến trường bị &lt;te href=851041&gt;&lt;color=#c79f49&gt;Loại Bỏ&lt;/color&gt;&lt;/te&gt;, sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Phiếu Hằng Ngày&lt;/color&gt;&lt;/te&gt; sẽ tăng thêm {0}, tối đa &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=1} mỗi ngày.</t>
         </is>
       </c>
     </row>
@@ -28232,7 +28232,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Cooldown triển khai</t>
+          <t>Thời gian hồi triển khai</t>
         </is>
       </c>
     </row>
@@ -28297,7 +28297,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Fusion RES</t>
+          <t>Kháng Hợp Thể</t>
         </is>
       </c>
     </row>
@@ -28427,7 +28427,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Discord này có Lớp Shield ngăn sát thương. Khi có Shield, nó miễn nhiễm với hiệu ứng Làm Chậm.</t>
+          <t>Tacet Discord này có Lớp Khiên ngăn sát thương. Khi có Khiên, nó miễn nhiễm với hiệu ứng Làm Chậm.</t>
         </is>
       </c>
     </row>
@@ -28492,7 +28492,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Discord này bắt đầu với Movement Speed chậm. HP càng thấp, nó di chuyển càng nhanh.</t>
+          <t>Tacet Discord này bắt đầu với Tốc Độ Di Chuyển chậm. HP càng thấp, nó di chuyển càng nhanh.</t>
         </is>
       </c>
     </row>
@@ -28557,7 +28557,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Discord này định kỳ tăng Phòng Ngự cho một số Discord gần đó.</t>
+          <t>Tacet Discord này định kỳ tăng Phòng Ngự cho một số Tacet Discord gần đó.</t>
         </is>
       </c>
     </row>
@@ -28622,7 +28622,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Discord này có lượng HP cao hơn nhưng liên tục mất máu theo thời gian.</t>
+          <t>Tacet Discord này có lượng HP cao hơn nhưng liên tục mất máu theo thời gian.</t>
         </is>
       </c>
     </row>
@@ -28687,7 +28687,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Lần đầu HP của Discord này giảm xuống dưới &lt;color=#fde7a1ff&gt;50%&lt;/color&gt;, nó sẽ miễn nhiễm với Tê Liệt/Đóng Băng/Mê Hoặc.</t>
+          <t>Lần đầu HP của Tacet Discord này giảm xuống dưới &lt;color=#fde7a1ff&gt;50%&lt;/color&gt;, nó sẽ miễn nhiễm với Tê Liệt/Đóng Băng/Mê Hoặc.</t>
         </is>
       </c>
     </row>
@@ -28752,7 +28752,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Discord này không kích hoạt Combat Machines trên tường và trần.</t>
+          <t>Tacet Discord này không kích hoạt Máy Chiến Đấu trên tường và trần.</t>
         </is>
       </c>
     </row>
@@ -28817,7 +28817,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Tất cả sát thương Echo này nhận được đều cố định ở mức &lt;color=#fde7a1ff&gt;1&lt;/color&gt;.</t>
+          <t>Tất cả DMG Tổ Tacet này nhận được đều cố định ở mức &lt;color=#fde7a1ff&gt;1&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -28884,7 +28884,7 @@
       <c r="M430" t="inlineStr">
         <is>
           <t>Kháng Điện
-Echo này có Kháng Điện cao hơn.</t>
+Tổ Tacet này có Kháng Điện cao hơn.</t>
         </is>
       </c>
     </row>
@@ -28950,8 +28950,8 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Fusion RES
-Echo này có Fusion RES cao hơn.</t>
+          <t>Kháng Hợp Thể
+Tổ Tacet này có Kháng Hợp Thể cao hơn.</t>
         </is>
       </c>
     </row>
@@ -29017,8 +29017,8 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Shield
-Echo này có Shield ngăn chặn sát thương. Khi được Shield bảo vệ, nó miễn nhiễm với trạng thái Chậm.</t>
+          <t>Khiên
+Tổ Tacet này có Khiên ngăn chặn sát thương. Khi được Khiên bảo vệ, nó miễn nhiễm với trạng thái Chậm.</t>
         </is>
       </c>
     </row>
@@ -29084,8 +29084,8 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Wrath
-HP của Discord này càng thấp, tốc độ di chuyển của nó càng nhanh.</t>
+          <t>Thịnh Nộ
+HP của Tacet Discord này càng thấp, tốc độ di chuyển của nó càng nhanh.</t>
         </is>
       </c>
     </row>
@@ -29152,7 +29152,7 @@
       <c r="M434" t="inlineStr">
         <is>
           <t>Thiêu đốt
-Echo này có lượng HP cao nhưng sẽ mất dần theo thời gian.</t>
+Tổ Tacet này có lượng HP cao nhưng sẽ mất dần theo thời gian.</t>
         </is>
       </c>
     </row>
@@ -29218,8 +29218,8 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Domain - Shelter
-Tacet Discords trong phạm vi nhất định sẽ tăng Phòng Ngự.</t>
+          <t>Tổ Tacet - Nơi Trú Ẩn
+Các Tacet Discord trong phạm vi nhất định sẽ tăng Phòng Ngự.</t>
         </is>
       </c>
     </row>
@@ -29288,9 +29288,9 @@
       <c r="M436" t="inlineStr">
         <is>
           <t>Được gia cố
-Echo này còn rất ít HP, nhưng mọi sát thương nhận vào đều bị cố định ở mức 1.
+Tổ Tacet này còn rất ít HP, nhưng mọi DMG nhận vào đều bị cố định ở mức 1.
 Thích ứng
-Khi bị ảnh hưởng bởi Tê Liệt/Đóng Băng/Mất Phương Hướng, Echo này sẽ miễn nhiễm với các hiệu ứng suy yếu đó trong một khoảng thời gian ngắn.</t>
+Khi bị ảnh hưởng bởi Tê Liệt/Đóng Băng/Mất Phương Hướng, Tổ Tacet này sẽ miễn nhiễm với các hiệu ứng suy yếu đó trong một khoảng thời gian ngắn.</t>
         </is>
       </c>
     </row>
@@ -29355,7 +29355,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Tactic Set kích nổ Combat Machines trên mặt đất để tạo ra ngọn lửa sát thương cao, với sự hỗ trợ của Combat Machines trên tường và trần.</t>
+          <t>Bộ Chiến Thuật kích nổ Máy Chiến Đấu trên mặt đất để tạo ra ngọn lửa sát thương cao, với sự hỗ trợ của Máy Chiến Đấu trên tường và trần.</t>
         </is>
       </c>
     </row>
@@ -29420,7 +29420,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Tactic Set tạo ra Chuỗi Sét nảy giữa các mục tiêu, tăng Electro DMG và gia tăng hiệu ứng Tê Liệt.</t>
+          <t>Bộ Chiến Thuật tạo ra Chuỗi Sét nảy giữa các mục tiêu, tăng Sát Thương Electro và gia tăng hiệu ứng Tê Liệt.</t>
         </is>
       </c>
     </row>
@@ -29485,7 +29485,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Tăng cường Paralysis (Crit. Rate)</t>
+          <t>Tê Liệt Nâng Cao (Crit. Rate)</t>
         </is>
       </c>
     </row>
@@ -29550,7 +29550,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Tê liệt Nâng cao (Crit. DMG)</t>
+          <t>Tê Liệt Nâng Cao (Crit. DMG)</t>
         </is>
       </c>
     </row>
@@ -29617,9 +29617,9 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750028&gt;Silent Lightning&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750025&gt;Máy Combat Loại Electro&lt;/te&gt;]&lt;/color&gt;
-Khi HP của Discord giảm xuống còn &lt;color=Highlight&gt;{0}&lt;/color&gt;, một &lt;color=Highlight&gt;Sấm Chớp Liên Hoàn&lt;/color&gt; bổ sung sẽ xuất hiện, cố định nảy &lt;color=Highlight&gt;{1}&lt;/color&gt; lần, gây sát thương bằng &lt;color=Highlight&gt;{2}&lt;/color&gt; Electro DMG.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750028&gt;Tia Chớp Vô Thanh&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750025&gt;Máy Chiến Đấu Loại Electro&lt;/te&gt;]&lt;/color&gt;
+Khi HP của Tacet Discord giảm xuống còn &lt;color=Highlight&gt;{0}&lt;/color&gt;, một &lt;color=Highlight&gt;Sấm Chớp Liên Hoàn&lt;/color&gt; bổ sung sẽ xuất hiện, cố định nảy &lt;color=Highlight&gt;{1}&lt;/color&gt; lần, gây DMG bằng &lt;color=Highlight&gt;{2}&lt;/color&gt; Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -29686,9 +29686,9 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750028&gt;Silent Lightning&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750025&gt;Electro-Type Combat Machine&lt;/te&gt;]&lt;/color&gt;
-Mỗi lần &lt;color=Highlight&gt;Chain Lightning&lt;/color&gt; nảy, sát thương gây ra tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750028&gt;Tia Chớp Vô Thanh&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750025&gt;Máy Chiến Đấu Loại Electro&lt;/te&gt;]&lt;/color&gt;
+Mỗi lần &lt;color=Highlight&gt;Sấm Chớp Liên Hoàn&lt;/color&gt; nảy, sát thương gây ra tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -29755,9 +29755,9 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750028&gt;Silent Lightning&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750025&gt;Electro-Type Combat Machine&lt;/te&gt;]&lt;/color&gt;
-&lt;color=Highlight&gt;Chain Lightning&lt;/color&gt; làm giảm Electro RES của Tacet Discord &lt;color=Highlight&gt;{0}&lt;/color&gt; mỗi khi nảy.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750028&gt;Tia Chớp Vô Thanh&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750025&gt;Máy Chiến Đấu Loại Electro&lt;/te&gt;]&lt;/color&gt;
+&lt;color=Highlight&gt;Sấm Chớp Liên Hoàn&lt;/color&gt; làm giảm Kháng Electro của Tacet Discord &lt;color=Highlight&gt;{0}&lt;/color&gt; mỗi khi nảy.</t>
         </is>
       </c>
     </row>
@@ -29824,9 +29824,9 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750028&gt;Silent Lightning&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750031&gt;Core&lt;/te&gt;]&lt;/color&gt;
-Khi Tacet Discord bị Choáng chịu Electro DMG, một &lt;color=Highlight&gt;Chain Lightning&lt;/color&gt; sẽ xuất hiện ngay lập tức tấn công mục tiêu gần đó, gây &lt;color=Highlight&gt;{0}&lt;/color&gt; Electro DMG. &lt;color=Highlight&gt;Chain Lightning&lt;/color&gt; gây thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750028&gt;Tia Chớp Vô Thanh&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750031&gt;Lõi&lt;/te&gt;]&lt;/color&gt;
+Khi Tacet Discord bị Choáng chịu Sát Thương Electro, một &lt;color=Highlight&gt;Sấm Chớp Liên Hoàn&lt;/color&gt; sẽ xuất hiện ngay lập tức tấn công mục tiêu gần đó, gây &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương Electro. &lt;color=Highlight&gt;Sấm Chớp Liên Hoàn&lt;/color&gt; gây thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -29893,9 +29893,9 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750028&gt;Silent Lightning&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750025&gt;Electro-Type Combat Machine&lt;/te&gt;]&lt;/color&gt;
-&lt;color=Highlight&gt;Chain Lightning&lt;/color&gt; nảy thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; lần và gây thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750028&gt;Tia Chớp Vô Thanh&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750025&gt;Máy Chiến Đấu Loại Electro&lt;/te&gt;]&lt;/color&gt;
+&lt;color=Highlight&gt;Sấm Chớp Liên Hoàn&lt;/color&gt; nảy thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; lần và gây thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -29962,9 +29962,9 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750028&gt;Silent Lightning&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750031&gt;Core&lt;/te&gt;]&lt;/color&gt;
-Khi Tacet Discord bị Tê Liệt chịu Electro DMG, một &lt;color=Highlight&gt;Chain Lightning&lt;/color&gt; sẽ xuất hiện ngay tại chỗ, tấn công mục tiêu gần đó, gây &lt;color=Highlight&gt;{0}&lt;/color&gt; Electro DMG. Tấn Công của Combat Machines loại Electro tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750028&gt;Tia Chớp Lặng&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750031&gt;Lõi&lt;/te&gt;]&lt;/color&gt;
+Khi Tacet Discord bị Tê Liệt chịu Sát Thương Electro, một &lt;color=Highlight&gt;Tia Sét Liên Hoàn&lt;/color&gt; sẽ xuất hiện ngay tại chỗ, tấn công mục tiêu gần đó, gây &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương Electro. ATK của Máy Chiến Đấu loại Electro tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -30030,8 +30030,8 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;DMG Enhancement&lt;/te&gt;]&lt;/color&gt;
-Tacet Discord bị Tê Liệt sẽ giảm &lt;color=Highlight&gt;{0}&lt;/color&gt; Electro RES.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;Tăng Sát Thương&lt;/te&gt;]&lt;/color&gt;
+Tacet Discord bị Tê Liệt sẽ giảm &lt;color=Highlight&gt;{0}&lt;/color&gt; Kháng Electro.</t>
         </is>
       </c>
     </row>
@@ -30097,8 +30097,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750034&gt;Hunting Trap&lt;/te&gt;]&lt;/color&gt;
-Thời gian &lt;color=Highlight&gt;Paralysis&lt;/color&gt; được kéo dài thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>Thời gian Tê Liệt kéo dài thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -30165,8 +30164,8 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;DMG Enhancement&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750034&gt;Hunting Trap&lt;/te&gt;]&lt;/color&gt;
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;Tăng Sát Thương&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750034&gt;Bẫy Săn Mồi&lt;/te&gt;]&lt;/color&gt;
 Crit. Rate khi tấn công Tacet Discord bị Choáng tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
@@ -30234,8 +30233,8 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;DMG Enhancement&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750034&gt;Hunting Trap&lt;/te&gt;]&lt;/color&gt;
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;Tăng Sát Thương&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750034&gt;Bẫy Săn Mồi&lt;/te&gt;]&lt;/color&gt;
 Crit. DMG khi tấn công Tacet Discord bị Choáng tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
@@ -30301,7 +30300,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Tăng cường Paralysis: (Crit. Rate)</t>
+          <t>Tê Liệt Cường Hóa: (Crit. Rate)</t>
         </is>
       </c>
     </row>
@@ -30366,7 +30365,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Tê liệt Nâng cao (Crit. DMG)</t>
+          <t>Tê Liệt Nâng Cao (Crit. DMG)</t>
         </is>
       </c>
     </row>
@@ -30433,9 +30432,9 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750028&gt;Silent Lightning&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750025&gt;Máy Combat Loại Electro&lt;/te&gt;]&lt;/color&gt;
-Khi HP của Discord giảm xuống còn &lt;color=Highlight&gt;{0}&lt;/color&gt;, một &lt;color=Highlight&gt;Sấm Chớp Liên Hoàn&lt;/color&gt; bổ sung sẽ xuất hiện, cố định nảy &lt;color=Highlight&gt;{1}&lt;/color&gt; lần, gây sát thương bằng &lt;color=Highlight&gt;{2}&lt;/color&gt; Electro DMG.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750028&gt;Tia Chớp Vô Thanh&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750025&gt;Máy Chiến Đấu Loại Electro&lt;/te&gt;]&lt;/color&gt;
+Khi HP của Tacet Discord giảm xuống còn &lt;color=Highlight&gt;{0}&lt;/color&gt;, một &lt;color=Highlight&gt;Sấm Chớp Liên Hoàn&lt;/color&gt; bổ sung sẽ xuất hiện, cố định nảy &lt;color=Highlight&gt;{1}&lt;/color&gt; lần, gây DMG bằng &lt;color=Highlight&gt;{2}&lt;/color&gt; Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -30502,9 +30501,9 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750028&gt;Silent Lightning&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750025&gt;Electro-Type Combat Machine&lt;/te&gt;]&lt;/color&gt;
-Mỗi lần &lt;color=Highlight&gt;Chain Lightning&lt;/color&gt; nảy, sát thương gây ra tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750028&gt;Tia Chớp Vô Thanh&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750025&gt;Máy Chiến Đấu Loại Electro&lt;/te&gt;]&lt;/color&gt;
+Mỗi lần &lt;color=Highlight&gt;Sấm Chớp Liên Hoàn&lt;/color&gt; nảy, sát thương gây ra tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -30571,9 +30570,9 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750028&gt;Silent Lightning&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750025&gt;Electro-Type Combat Machine&lt;/te&gt;]&lt;/color&gt;
-&lt;color=Highlight&gt;Chain Lightning&lt;/color&gt; làm giảm Electro RES của Tacet Discord &lt;color=Highlight&gt;{0}&lt;/color&gt; mỗi khi nảy.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750028&gt;Tia Chớp Vô Thanh&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750025&gt;Máy Chiến Đấu Loại Electro&lt;/te&gt;]&lt;/color&gt;
+&lt;color=Highlight&gt;Sấm Chớp Liên Hoàn&lt;/color&gt; làm giảm Kháng Electro của Tacet Discord &lt;color=Highlight&gt;{0}&lt;/color&gt; mỗi khi nảy.</t>
         </is>
       </c>
     </row>
@@ -30640,9 +30639,9 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750028&gt;Silent Lightning&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750031&gt;Core&lt;/te&gt;]&lt;/color&gt;
-Khi Tacet Discord bị Choáng chịu Electro DMG, một &lt;color=Highlight&gt;Chain Lightning&lt;/color&gt; sẽ xuất hiện ngay lập tức tấn công mục tiêu gần đó, gây &lt;color=Highlight&gt;{0}&lt;/color&gt; Electro DMG. &lt;color=Highlight&gt;Chain Lightning&lt;/color&gt; gây thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750028&gt;Tia Chớp Vô Thanh&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750031&gt;Lõi&lt;/te&gt;]&lt;/color&gt;
+Khi Tacet Discord bị Choáng chịu Sát Thương Electro, một &lt;color=Highlight&gt;Sấm Chớp Liên Hoàn&lt;/color&gt; sẽ xuất hiện ngay lập tức tấn công mục tiêu gần đó, gây &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương Electro. &lt;color=Highlight&gt;Sấm Chớp Liên Hoàn&lt;/color&gt; gây thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -30709,9 +30708,9 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750028&gt;Silent Lightning&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750025&gt;Electro-Type Combat Machine&lt;/te&gt;]&lt;/color&gt;
-&lt;color=Highlight&gt;Chain Lightning&lt;/color&gt; nảy thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; lần và gây thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750028&gt;Tia Chớp Vô Thanh&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750025&gt;Máy Chiến Đấu Loại Electro&lt;/te&gt;]&lt;/color&gt;
+&lt;color=Highlight&gt;Sấm Chớp Liên Hoàn&lt;/color&gt; nảy thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; lần và gây thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -30778,9 +30777,9 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750028&gt;Silent Lightning&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750031&gt;Core&lt;/te&gt;]&lt;/color&gt;
-Khi Tacet Discord bị Tê Liệt chịu Electro DMG, một &lt;color=Highlight&gt;Chain Lightning&lt;/color&gt; sẽ xuất hiện ngay tại chỗ, tấn công mục tiêu gần đó, gây &lt;color=Highlight&gt;{0}&lt;/color&gt; Electro DMG. Tấn Công của Combat Machines loại Electro tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750028&gt;Tia Chớp Lặng&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750031&gt;Lõi&lt;/te&gt;]&lt;/color&gt;
+Khi Tacet Discord bị Tê Liệt chịu Sát Thương Electro, một &lt;color=Highlight&gt;Tia Sét Liên Hoàn&lt;/color&gt; sẽ xuất hiện ngay tại chỗ, tấn công mục tiêu gần đó, gây &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương Electro. ATK của Máy Chiến Đấu loại Electro tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -30846,8 +30845,8 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;DMG Enhancement&lt;/te&gt;]&lt;/color&gt;
-Tacet Discord bị Tê Liệt sẽ giảm &lt;color=Highlight&gt;{0}&lt;/color&gt; Electro RES.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;Tăng Sát Thương&lt;/te&gt;]&lt;/color&gt;
+Tacet Discord bị Tê Liệt sẽ giảm &lt;color=Highlight&gt;{0}&lt;/color&gt; Kháng Electro.</t>
         </is>
       </c>
     </row>
@@ -30913,8 +30912,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750034&gt;Hunting Trap&lt;/te&gt;]&lt;/color&gt;
-Thời gian &lt;color=Highlight&gt;Paralysis&lt;/color&gt; được kéo dài thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>Thời gian Tê Liệt kéo dài thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -30981,8 +30979,8 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;DMG Enhancement&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750034&gt;Hunting Trap&lt;/te&gt;]&lt;/color&gt;
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;Tăng Sát Thương&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750034&gt;Bẫy Săn Mồi&lt;/te&gt;]&lt;/color&gt;
 Crit. Rate khi tấn công Tacet Discord bị Choáng tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
@@ -31050,8 +31048,8 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;DMG Enhancement&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750034&gt;Hunting Trap&lt;/te&gt;]&lt;/color&gt;
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750032&gt;Tăng Sát Thương&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750034&gt;Bẫy Săn Mồi&lt;/te&gt;]&lt;/color&gt;
 Crit. DMG khi tấn công Tacet Discord bị Choáng tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
@@ -31117,7 +31115,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng phóng Gai Tacetite, gây Sát Thương Physical lên Tacet Discord.</t>
+          <t>Thỉnh thoảng phóng Gai Tacetite, gây Sát Thương Vật Lý lên Tacet Discord.</t>
         </is>
       </c>
     </row>
@@ -31182,7 +31180,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng phóng Gai Tacetite, gây Sát Thương Physical lên Tacet Discord.</t>
+          <t>Thỉnh thoảng phóng Gai Tacetite, gây Sát Thương Vật Lý lên Tacet Discord.</t>
         </is>
       </c>
     </row>
@@ -31247,7 +31245,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng phóng Gai Tacetite, gây Sát Thương Physical lên Tacet Discord.</t>
+          <t>Thỉnh thoảng phóng Gai Tacetite, gây Sát Thương Vật Lý lên Tacet Discord.</t>
         </is>
       </c>
     </row>
@@ -31312,7 +31310,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng phóng Gai Tacetite, gây Sát Thương Physical lên Tacet Discord.</t>
+          <t>Thỉnh thoảng phóng Gai Tacetite, gây Sát Thương Vật Lý lên Tacet Discord.</t>
         </is>
       </c>
     </row>
@@ -31377,7 +31375,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng phóng Gai Tacetite, gây Sát Thương Physical lên Tacet Discord.</t>
+          <t>Thỉnh thoảng phóng Gai Tacetite, gây Sát Thương Vật Lý lên Tacet Discord.</t>
         </is>
       </c>
     </row>
@@ -31442,7 +31440,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Drake, gây Fusion DMG lên các Tacet Discord phía trước.</t>
+          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Drake, gây Sát Thương Fusion lên các Tacet Discord phía trước.</t>
         </is>
       </c>
     </row>
@@ -31507,7 +31505,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Drake, gây Fusion DMG lên các Tacet Discord phía trước.</t>
+          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Drake, gây Sát Thương Fusion lên các Tacet Discord phía trước.</t>
         </is>
       </c>
     </row>
@@ -31572,7 +31570,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Drake, gây Fusion DMG lên các Tacet Discord phía trước.</t>
+          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Drake, gây Sát Thương Fusion lên các Tacet Discord phía trước.</t>
         </is>
       </c>
     </row>
@@ -31637,7 +31635,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Drake, gây Fusion DMG lên các Tacet Discord phía trước.</t>
+          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Drake, gây Sát Thương Fusion lên các Tacet Discord phía trước.</t>
         </is>
       </c>
     </row>
@@ -31702,7 +31700,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Drake, gây Fusion DMG lên các Tacet Discord phía trước.</t>
+          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Drake, gây Sát Thương Fusion lên các Tacet Discord phía trước.</t>
         </is>
       </c>
     </row>
@@ -31767,7 +31765,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Junrock phát nổ khi Tacet Discord đến gần, gây Sát Thương Physical diện rộng.</t>
+          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Junrock phát nổ khi Tacet Discord đến gần, gây Sát Thương Vật Lý diện rộng.</t>
         </is>
       </c>
     </row>
@@ -31832,7 +31830,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Junrock phát nổ khi Tacet Discord đến gần, gây Sát Thương Physical diện rộng.</t>
+          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Junrock phát nổ khi Tacet Discord đến gần, gây Sát Thương Vật Lý diện rộng.</t>
         </is>
       </c>
     </row>
@@ -31897,7 +31895,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Junrock phát nổ khi Tacet Discord đến gần, gây Sát Thương Physical diện rộng.</t>
+          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Junrock phát nổ khi Tacet Discord đến gần, gây Sát Thương Vật Lý diện rộng.</t>
         </is>
       </c>
     </row>
@@ -31962,7 +31960,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Junrock phát nổ khi Tacet Discord đến gần, gây Sát Thương Physical diện rộng.</t>
+          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Junrock phát nổ khi Tacet Discord đến gần, gây Sát Thương Vật Lý diện rộng.</t>
         </is>
       </c>
     </row>
@@ -32027,7 +32025,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Junrock phát nổ khi Tacet Discord đến gần, gây Sát Thương Physical diện rộng.</t>
+          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Junrock phát nổ khi Tacet Discord đến gần, gây Sát Thương Vật Lý diện rộng.</t>
         </is>
       </c>
     </row>
@@ -32092,7 +32090,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng bắn ra một ngọn thương sét xuyên qua Tacet Discord với tầm vô hạn, gây Electro DMG.</t>
+          <t>Thỉnh thoảng bắn ra một ngọn thương sét xuyên qua Tacet Discord với tầm vô hạn, gây Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -32157,7 +32155,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng bắn ra một ngọn thương sét xuyên qua Tacet Discord với tầm vô hạn, gây Electro DMG.</t>
+          <t>Thỉnh thoảng bắn ra một ngọn thương sét xuyên qua Tacet Discord với tầm vô hạn, gây Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -32222,7 +32220,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng bắn ra một ngọn thương sét xuyên qua Tacet Discord với tầm vô hạn, gây Electro DMG.</t>
+          <t>Thỉnh thoảng bắn ra một ngọn thương sét xuyên qua Tacet Discord với tầm vô hạn, gây Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -32287,7 +32285,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng bắn ra một ngọn thương sét xuyên qua Tacet Discord với tầm vô hạn, gây Electro DMG.</t>
+          <t>Thỉnh thoảng bắn ra một ngọn thương sét xuyên qua Tacet Discord với tầm vô hạn, gây Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -32352,7 +32350,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng bắn ra một ngọn thương sét xuyên qua Tacet Discord với tầm vô hạn, gây Electro DMG.</t>
+          <t>Thỉnh thoảng bắn ra một ngọn thương sét xuyên qua Tacet Discord với tầm vô hạn, gây Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -32417,7 +32415,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Khi Tacet Discord đến gần, bắn mảnh Echo gây Sát Thương Physical lên mục tiêu gần nhất.</t>
+          <t>Khi Tacet Discord đến gần, bắn mảnh Tổ Tacet gây Sát Thương Vật Lý lên mục tiêu gần nhất.</t>
         </is>
       </c>
     </row>
@@ -32482,7 +32480,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Khi Tacet Discord đến gần, bắn mảnh Echo gây Sát Thương Physical lên mục tiêu gần nhất.</t>
+          <t>Khi Tacet Discord đến gần, bắn mảnh Tổ Tacet gây Sát Thương Vật Lý lên mục tiêu gần nhất.</t>
         </is>
       </c>
     </row>
@@ -32547,7 +32545,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Khi Tacet Discord đến gần, bắn mảnh Echo gây Sát Thương Physical lên mục tiêu gần nhất.</t>
+          <t>Khi Tacet Discord đến gần, bắn mảnh Tổ Tacet gây Sát Thương Vật Lý lên mục tiêu gần nhất.</t>
         </is>
       </c>
     </row>
@@ -32612,7 +32610,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Khi Tacet Discord đến gần, bắn mảnh Echo gây Sát Thương Physical lên mục tiêu gần nhất.</t>
+          <t>Khi Tacet Discord đến gần, bắn mảnh Tổ Tacet gây Sát Thương Vật Lý lên mục tiêu gần nhất.</t>
         </is>
       </c>
     </row>
@@ -32677,7 +32675,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Khi Tacet Discord đến gần, bắn mảnh Echo gây Sát Thương Physical lên mục tiêu gần nhất.</t>
+          <t>Khi Tacet Discord đến gần, bắn mảnh Tổ Tacet gây Sát Thương Vật Lý lên mục tiêu gần nhất.</t>
         </is>
       </c>
     </row>
@@ -32742,7 +32740,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Định kỳ phun ra luồng khí lạnh, gây Glacio DMG và làm chậm Tacet Discord trong phạm vi.</t>
+          <t>Định kỳ phun ra luồng khí lạnh, gây Sát Thương Glacio và làm chậm Tacet Discord trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -32807,7 +32805,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Định kỳ phun ra luồng khí lạnh, gây Glacio DMG và làm chậm Tacet Discord trong phạm vi.</t>
+          <t>Định kỳ phun ra luồng khí lạnh, gây Sát Thương Glacio và làm chậm Tacet Discord trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -32872,7 +32870,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Định kỳ phun ra luồng khí lạnh, gây Glacio DMG và làm chậm Tacet Discord trong phạm vi.</t>
+          <t>Định kỳ phun ra luồng khí lạnh, gây Sát Thương Glacio và làm chậm Tacet Discord trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -32937,7 +32935,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Định kỳ phun ra luồng khí lạnh, gây Glacio DMG và làm chậm Tacet Discord trong phạm vi.</t>
+          <t>Định kỳ phun ra luồng khí lạnh, gây Sát Thương Glacio và làm chậm Tacet Discord trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -33002,7 +33000,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Định kỳ phun ra luồng khí lạnh, gây Glacio DMG và làm chậm Tacet Discord trong phạm vi.</t>
+          <t>Định kỳ phun ra luồng khí lạnh, gây Sát Thương Glacio và làm chậm Tacet Discord trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -33067,7 +33065,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Triệu hồi một Hoartoise Echo xoay tròn, gây Sát Thương Physical và đẩy lùi Tacet Discord trên đường đi.</t>
+          <t>Triệu hồi một Hoartoise Echo xoay tròn, gây Sát Thương Vật Lý và đẩy lùi Tacet Discord trên đường đi.</t>
         </is>
       </c>
     </row>
@@ -33132,7 +33130,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Triệu hồi một Hoartoise Echo xoay tròn, gây Sát Thương Physical và đẩy lùi Tacet Discord trên đường đi.</t>
+          <t>Triệu hồi một Hoartoise Echo xoay tròn, gây Sát Thương Vật Lý và đẩy lùi Tacet Discord trên đường đi.</t>
         </is>
       </c>
     </row>
@@ -33197,7 +33195,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Triệu hồi một Hoartoise Echo xoay tròn, gây Sát Thương Physical và đẩy lùi Tacet Discord trên đường đi.</t>
+          <t>Triệu hồi một Hoartoise Echo xoay tròn, gây Sát Thương Vật Lý và đẩy lùi Tacet Discord trên đường đi.</t>
         </is>
       </c>
     </row>
@@ -33262,7 +33260,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Triệu hồi một Hoartoise Echo xoay tròn, gây Sát Thương Physical và đẩy lùi Tacet Discord trên đường đi.</t>
+          <t>Triệu hồi một Hoartoise Echo xoay tròn, gây Sát Thương Vật Lý và đẩy lùi Tacet Discord trên đường đi.</t>
         </is>
       </c>
     </row>
@@ -33327,7 +33325,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Triệu hồi một Hoartoise Echo xoay tròn, gây Sát Thương Physical và đẩy lùi Tacet Discord trên đường đi.</t>
+          <t>Triệu hồi một Hoartoise Echo xoay tròn, gây Sát Thương Vật Lý và đẩy lùi Tacet Discord trên đường đi.</t>
         </is>
       </c>
     </row>
@@ -33392,7 +33390,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng giật sét một Discord trong phạm vi, gây Electro DMG.</t>
+          <t>Thỉnh thoảng giật sét một Tacet Discord trong phạm vi, gây Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -33457,7 +33455,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng giật sét một Discord trong phạm vi, gây Electro DMG.</t>
+          <t>Thỉnh thoảng giật sét một Tacet Discord trong phạm vi, gây Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -33522,7 +33520,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng giật sét một Discord trong phạm vi, gây Electro DMG.</t>
+          <t>Thỉnh thoảng giật sét một Tacet Discord trong phạm vi, gây Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -33587,7 +33585,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng giật sét một Discord trong phạm vi, gây Electro DMG.</t>
+          <t>Thỉnh thoảng giật sét một Tacet Discord trong phạm vi, gây Sát Thương Electro.</t>
         </is>
       </c>
     </row>
